--- a/AAII_Financials/Yearly/TMICY_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/TMICY_YR_FIN.xlsx
@@ -5,7 +5,7 @@
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Stocks_Automation\AAII_Financials\Yearly\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Private\Investing\Automation\AAII\AAII_Financials\Yearly\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -17,12 +17,12 @@
   <definedNames>
     <definedName name="Ticker">#REF!</definedName>
   </definedNames>
-  <calcPr calcId="152511" calcMode="manual" concurrentCalc="0"/>
+  <calcPr calcId="152511" calcMode="manual"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="97" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="99" uniqueCount="92">
   <si>
     <t>TMICY</t>
   </si>
@@ -656,195 +656,207 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:P102"/>
+  <dimension ref="A5:Q102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="8.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:17" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E7" s="2">
         <v>44926</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>44561</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>44196</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>43830</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>43465</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>43100</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>42735</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>42369</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>42004</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>41639</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>41274</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>40908</v>
       </c>
-      <c r="P7" s="2"/>
-    </row>
-    <row r="8" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q7" s="2"/>
+    </row>
+    <row r="8" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
-        <v>1486000</v>
+        <v>1676200</v>
       </c>
       <c r="E8" s="3">
-        <v>1264000</v>
+        <v>1508400</v>
       </c>
       <c r="F8" s="3">
-        <v>1155800</v>
+        <v>1283000</v>
       </c>
       <c r="G8" s="3">
-        <v>1096900</v>
+        <v>1173200</v>
       </c>
       <c r="H8" s="3">
-        <v>1065100</v>
+        <v>1113400</v>
       </c>
       <c r="I8" s="3">
-        <v>988100</v>
+        <v>1081200</v>
       </c>
       <c r="J8" s="3">
+        <v>1003000</v>
+      </c>
+      <c r="K8" s="3">
         <v>876100</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>881400</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>1015000</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>1040900</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>853000</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>855000</v>
       </c>
-      <c r="P8" s="3"/>
-    </row>
-    <row r="9" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q8" s="3"/>
+    </row>
+    <row r="9" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
-        <v>360600</v>
+        <v>429100</v>
       </c>
       <c r="E9" s="3">
-        <v>279000</v>
+        <v>366000</v>
       </c>
       <c r="F9" s="3">
-        <v>253400</v>
+        <v>283200</v>
       </c>
       <c r="G9" s="3">
-        <v>214500</v>
+        <v>257200</v>
       </c>
       <c r="H9" s="3">
-        <v>217300</v>
+        <v>217700</v>
       </c>
       <c r="I9" s="3">
-        <v>186800</v>
+        <v>220600</v>
       </c>
       <c r="J9" s="3">
+        <v>189700</v>
+      </c>
+      <c r="K9" s="3">
         <v>153000</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>150800</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>180000</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>186200</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>159200</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>158700</v>
       </c>
-      <c r="P9" s="3"/>
-    </row>
-    <row r="10" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q9" s="3"/>
+    </row>
+    <row r="10" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
-        <v>1125400</v>
+        <v>1247100</v>
       </c>
       <c r="E10" s="3">
-        <v>985000</v>
+        <v>1142400</v>
       </c>
       <c r="F10" s="3">
-        <v>902300</v>
+        <v>999800</v>
       </c>
       <c r="G10" s="3">
-        <v>882400</v>
+        <v>915900</v>
       </c>
       <c r="H10" s="3">
-        <v>847800</v>
+        <v>895700</v>
       </c>
       <c r="I10" s="3">
-        <v>801300</v>
+        <v>860600</v>
       </c>
       <c r="J10" s="3">
+        <v>813300</v>
+      </c>
+      <c r="K10" s="3">
         <v>723100</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>730600</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>835000</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>854700</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>693800</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>696300</v>
       </c>
-      <c r="P10" s="3"/>
-    </row>
-    <row r="11" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q10" s="3"/>
+    </row>
+    <row r="11" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -861,50 +873,54 @@
       <c r="N11" s="3"/>
       <c r="O11" s="3"/>
       <c r="P11" s="3"/>
-    </row>
-    <row r="12" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q11" s="3"/>
+    </row>
+    <row r="12" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="D12" s="3">
-        <v>35900</v>
+      <c r="D12" s="3" t="s">
+        <v>91</v>
       </c>
       <c r="E12" s="3">
-        <v>31100</v>
+        <v>36400</v>
       </c>
       <c r="F12" s="3">
-        <v>48700</v>
+        <v>31500</v>
       </c>
       <c r="G12" s="3">
-        <v>54700</v>
+        <v>49500</v>
       </c>
       <c r="H12" s="3">
-        <v>49400</v>
+        <v>55500</v>
       </c>
       <c r="I12" s="3">
-        <v>51700</v>
+        <v>50200</v>
       </c>
       <c r="J12" s="3">
+        <v>52500</v>
+      </c>
+      <c r="K12" s="3">
         <v>35000</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>26800</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>25800</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>40200</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>34400</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>30800</v>
       </c>
-      <c r="P12" s="3"/>
-    </row>
-    <row r="13" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q12" s="3"/>
+    </row>
+    <row r="13" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>8</v>
       </c>
@@ -944,51 +960,57 @@
       <c r="O13" s="3">
         <v>0</v>
       </c>
-      <c r="P13" s="3"/>
-    </row>
-    <row r="14" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="P13" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q13" s="3"/>
+    </row>
+    <row r="14" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>9</v>
       </c>
       <c r="D14" s="3">
-        <v>-2500</v>
+        <v>29200</v>
       </c>
       <c r="E14" s="3">
+        <v>-2600</v>
+      </c>
+      <c r="F14" s="3">
         <v>1500</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>1300</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>500</v>
       </c>
-      <c r="H14" s="3">
-        <v>2200</v>
-      </c>
       <c r="I14" s="3">
+        <v>2300</v>
+      </c>
+      <c r="J14" s="3">
         <v>300</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>2500</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>5300</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>2000</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>8200</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>-31300</v>
       </c>
-      <c r="O14" s="3">
+      <c r="P14" s="3">
         <v>-42100</v>
       </c>
-      <c r="P14" s="3"/>
-    </row>
-    <row r="15" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q14" s="3"/>
+    </row>
+    <row r="15" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>10</v>
       </c>
@@ -1028,9 +1050,12 @@
       <c r="O15" s="3">
         <v>0</v>
       </c>
-      <c r="P15" s="3"/>
-    </row>
-    <row r="16" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="P15" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q15" s="3"/>
+    </row>
+    <row r="16" spans="1:17" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1044,92 +1069,99 @@
       <c r="N16" s="3"/>
       <c r="O16" s="3"/>
       <c r="P16" s="3"/>
-    </row>
-    <row r="17" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q16" s="3"/>
+    </row>
+    <row r="17" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D17" s="3">
-        <v>1275400</v>
+        <v>1485600</v>
       </c>
       <c r="E17" s="3">
-        <v>975700</v>
+        <v>1294600</v>
       </c>
       <c r="F17" s="3">
-        <v>895000</v>
+        <v>990400</v>
       </c>
       <c r="G17" s="3">
-        <v>847100</v>
+        <v>908500</v>
       </c>
       <c r="H17" s="3">
-        <v>829400</v>
+        <v>859900</v>
       </c>
       <c r="I17" s="3">
-        <v>746400</v>
+        <v>841900</v>
       </c>
       <c r="J17" s="3">
+        <v>757700</v>
+      </c>
+      <c r="K17" s="3">
         <v>650400</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>667100</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>720500</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>766100</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>618000</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>579000</v>
       </c>
-      <c r="P17" s="3"/>
-    </row>
-    <row r="18" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q17" s="3"/>
+    </row>
+    <row r="18" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D18" s="3">
-        <v>210600</v>
+        <v>190500</v>
       </c>
       <c r="E18" s="3">
-        <v>288300</v>
+        <v>213800</v>
       </c>
       <c r="F18" s="3">
-        <v>260700</v>
+        <v>292600</v>
       </c>
       <c r="G18" s="3">
-        <v>249800</v>
+        <v>264700</v>
       </c>
       <c r="H18" s="3">
-        <v>235700</v>
+        <v>253500</v>
       </c>
       <c r="I18" s="3">
-        <v>241700</v>
+        <v>239300</v>
       </c>
       <c r="J18" s="3">
+        <v>245300</v>
+      </c>
+      <c r="K18" s="3">
         <v>225700</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>214300</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>294500</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>274800</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>235000</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>276000</v>
       </c>
-      <c r="P18" s="3"/>
-    </row>
-    <row r="19" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q18" s="3"/>
+    </row>
+    <row r="19" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>13</v>
       </c>
@@ -1146,109 +1178,116 @@
       <c r="N19" s="3"/>
       <c r="O19" s="3"/>
       <c r="P19" s="3"/>
-    </row>
-    <row r="20" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q19" s="3"/>
+    </row>
+    <row r="20" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>14</v>
       </c>
       <c r="D20" s="3">
-        <v>67900</v>
+        <v>25000</v>
       </c>
       <c r="E20" s="3">
-        <v>59500</v>
+        <v>68900</v>
       </c>
       <c r="F20" s="3">
+        <v>60400</v>
+      </c>
+      <c r="G20" s="3">
         <v>3900</v>
       </c>
-      <c r="G20" s="3">
-        <v>10100</v>
-      </c>
       <c r="H20" s="3">
-        <v>11200</v>
+        <v>10300</v>
       </c>
       <c r="I20" s="3">
+        <v>11400</v>
+      </c>
+      <c r="J20" s="3">
         <v>4700</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>11500</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>27000</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>23100</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>32800</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>-13100</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>-22100</v>
       </c>
-      <c r="P20" s="3"/>
-    </row>
-    <row r="21" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q20" s="3"/>
+    </row>
+    <row r="21" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D21" s="3">
-        <v>445000</v>
+        <v>407200</v>
       </c>
       <c r="E21" s="3">
-        <v>485900</v>
+        <v>453200</v>
       </c>
       <c r="F21" s="3">
-        <v>414500</v>
+        <v>494500</v>
       </c>
       <c r="G21" s="3">
-        <v>364400</v>
+        <v>422100</v>
       </c>
       <c r="H21" s="3">
-        <v>352100</v>
+        <v>370900</v>
       </c>
       <c r="I21" s="3">
-        <v>338500</v>
+        <v>358400</v>
       </c>
       <c r="J21" s="3">
+        <v>344500</v>
+      </c>
+      <c r="K21" s="3">
         <v>311200</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>297700</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>384800</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>377100</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>290200</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>319000</v>
       </c>
-      <c r="P21" s="3"/>
-    </row>
-    <row r="22" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q21" s="3"/>
+    </row>
+    <row r="22" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="D22" s="3">
+      <c r="D22" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="E22" s="3">
         <v>300</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>100</v>
-      </c>
-      <c r="F22" s="3" t="s">
-        <v>91</v>
       </c>
       <c r="G22" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="H22" s="3">
-        <v>0</v>
+      <c r="H22" s="3" t="s">
+        <v>91</v>
       </c>
       <c r="I22" s="3">
         <v>0</v>
@@ -1260,104 +1299,113 @@
         <v>0</v>
       </c>
       <c r="L22" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="M22" s="3">
         <v>100</v>
       </c>
       <c r="N22" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="O22" s="3">
         <v>0</v>
       </c>
-      <c r="P22" s="3"/>
-    </row>
-    <row r="23" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P22" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q22" s="3"/>
+    </row>
+    <row r="23" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D23" s="3">
-        <v>278200</v>
+        <v>215500</v>
       </c>
       <c r="E23" s="3">
-        <v>347700</v>
+        <v>282400</v>
       </c>
       <c r="F23" s="3">
-        <v>264600</v>
+        <v>353000</v>
       </c>
       <c r="G23" s="3">
-        <v>259900</v>
+        <v>268600</v>
       </c>
       <c r="H23" s="3">
-        <v>246900</v>
+        <v>263800</v>
       </c>
       <c r="I23" s="3">
-        <v>246300</v>
+        <v>250700</v>
       </c>
       <c r="J23" s="3">
+        <v>250000</v>
+      </c>
+      <c r="K23" s="3">
         <v>237200</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>241300</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>317400</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>307600</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>221800</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>253900</v>
       </c>
-      <c r="P23" s="3"/>
-    </row>
-    <row r="24" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q23" s="3"/>
+    </row>
+    <row r="24" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D24" s="3">
-        <v>85900</v>
+        <v>143000</v>
       </c>
       <c r="E24" s="3">
-        <v>98000</v>
+        <v>87200</v>
       </c>
       <c r="F24" s="3">
-        <v>89500</v>
+        <v>99400</v>
       </c>
       <c r="G24" s="3">
-        <v>75200</v>
+        <v>90800</v>
       </c>
       <c r="H24" s="3">
-        <v>59000</v>
+        <v>76300</v>
       </c>
       <c r="I24" s="3">
-        <v>75700</v>
+        <v>59900</v>
       </c>
       <c r="J24" s="3">
+        <v>76900</v>
+      </c>
+      <c r="K24" s="3">
         <v>73500</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>89300</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>120900</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>119300</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>99600</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>100000</v>
       </c>
-      <c r="P24" s="3"/>
-    </row>
-    <row r="25" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q24" s="3"/>
+    </row>
+    <row r="25" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>19</v>
       </c>
@@ -1397,93 +1445,102 @@
       <c r="O25" s="3">
         <v>0</v>
       </c>
-      <c r="P25" s="3"/>
-    </row>
-    <row r="26" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P25" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q25" s="3"/>
+    </row>
+    <row r="26" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>20</v>
       </c>
       <c r="D26" s="3">
-        <v>192200</v>
+        <v>72500</v>
       </c>
       <c r="E26" s="3">
-        <v>249800</v>
+        <v>195100</v>
       </c>
       <c r="F26" s="3">
-        <v>175100</v>
+        <v>253500</v>
       </c>
       <c r="G26" s="3">
-        <v>184700</v>
+        <v>177800</v>
       </c>
       <c r="H26" s="3">
-        <v>187900</v>
+        <v>187500</v>
       </c>
       <c r="I26" s="3">
-        <v>170600</v>
+        <v>190700</v>
       </c>
       <c r="J26" s="3">
+        <v>173200</v>
+      </c>
+      <c r="K26" s="3">
         <v>163700</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>152000</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>196500</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>188300</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>122200</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>153900</v>
       </c>
-      <c r="P26" s="3"/>
-    </row>
-    <row r="27" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q26" s="3"/>
+    </row>
+    <row r="27" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D27" s="3">
-        <v>198200</v>
+        <v>72300</v>
       </c>
       <c r="E27" s="3">
-        <v>254800</v>
+        <v>201100</v>
       </c>
       <c r="F27" s="3">
-        <v>178600</v>
+        <v>258600</v>
       </c>
       <c r="G27" s="3">
-        <v>185600</v>
+        <v>181300</v>
       </c>
       <c r="H27" s="3">
-        <v>188000</v>
+        <v>188400</v>
       </c>
       <c r="I27" s="3">
-        <v>170600</v>
+        <v>190800</v>
       </c>
       <c r="J27" s="3">
+        <v>173200</v>
+      </c>
+      <c r="K27" s="3">
         <v>163700</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>152000</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>196500</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>188300</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>122200</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>153800</v>
       </c>
-      <c r="P27" s="3"/>
-    </row>
-    <row r="28" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q27" s="3"/>
+    </row>
+    <row r="28" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>22</v>
       </c>
@@ -1523,9 +1580,12 @@
       <c r="O28" s="3">
         <v>0</v>
       </c>
-      <c r="P28" s="3"/>
-    </row>
-    <row r="29" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P28" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q28" s="3"/>
+    </row>
+    <row r="29" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>23</v>
       </c>
@@ -1565,9 +1625,12 @@
       <c r="O29" s="3">
         <v>0</v>
       </c>
-      <c r="P29" s="3"/>
-    </row>
-    <row r="30" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P29" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q29" s="3"/>
+    </row>
+    <row r="30" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>24</v>
       </c>
@@ -1607,9 +1670,12 @@
       <c r="O30" s="3">
         <v>0</v>
       </c>
-      <c r="P30" s="3"/>
-    </row>
-    <row r="31" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P30" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q30" s="3"/>
+    </row>
+    <row r="31" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>25</v>
       </c>
@@ -1649,93 +1715,102 @@
       <c r="O31" s="3">
         <v>0</v>
       </c>
-      <c r="P31" s="3"/>
-    </row>
-    <row r="32" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P31" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q31" s="3"/>
+    </row>
+    <row r="32" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>26</v>
       </c>
       <c r="D32" s="3">
-        <v>-67900</v>
+        <v>-25000</v>
       </c>
       <c r="E32" s="3">
-        <v>-59500</v>
+        <v>-68900</v>
       </c>
       <c r="F32" s="3">
+        <v>-60400</v>
+      </c>
+      <c r="G32" s="3">
         <v>-3900</v>
       </c>
-      <c r="G32" s="3">
-        <v>-10100</v>
-      </c>
       <c r="H32" s="3">
-        <v>-11200</v>
+        <v>-10300</v>
       </c>
       <c r="I32" s="3">
+        <v>-11400</v>
+      </c>
+      <c r="J32" s="3">
         <v>-4700</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>-11500</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-27000</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-23100</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-32800</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>13100</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>22100</v>
       </c>
-      <c r="P32" s="3"/>
-    </row>
-    <row r="33" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q32" s="3"/>
+    </row>
+    <row r="33" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D33" s="3">
-        <v>198200</v>
+        <v>72300</v>
       </c>
       <c r="E33" s="3">
-        <v>254800</v>
+        <v>201100</v>
       </c>
       <c r="F33" s="3">
-        <v>178600</v>
+        <v>258600</v>
       </c>
       <c r="G33" s="3">
-        <v>185600</v>
+        <v>181300</v>
       </c>
       <c r="H33" s="3">
-        <v>188000</v>
+        <v>188400</v>
       </c>
       <c r="I33" s="3">
-        <v>170600</v>
+        <v>190800</v>
       </c>
       <c r="J33" s="3">
+        <v>173200</v>
+      </c>
+      <c r="K33" s="3">
         <v>163700</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>152000</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>196500</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>188300</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>122200</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>153800</v>
       </c>
-      <c r="P33" s="3"/>
-    </row>
-    <row r="34" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q33" s="3"/>
+    </row>
+    <row r="34" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>28</v>
       </c>
@@ -1775,98 +1850,107 @@
       <c r="O34" s="3">
         <v>0</v>
       </c>
-      <c r="P34" s="3"/>
-    </row>
-    <row r="35" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P34" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q34" s="3"/>
+    </row>
+    <row r="35" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>29</v>
       </c>
       <c r="D35" s="3">
-        <v>198200</v>
+        <v>72300</v>
       </c>
       <c r="E35" s="3">
-        <v>254800</v>
+        <v>201100</v>
       </c>
       <c r="F35" s="3">
-        <v>178600</v>
+        <v>258600</v>
       </c>
       <c r="G35" s="3">
-        <v>185600</v>
+        <v>181300</v>
       </c>
       <c r="H35" s="3">
-        <v>188000</v>
+        <v>188400</v>
       </c>
       <c r="I35" s="3">
-        <v>170600</v>
+        <v>190800</v>
       </c>
       <c r="J35" s="3">
+        <v>173200</v>
+      </c>
+      <c r="K35" s="3">
         <v>163700</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>152000</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>196500</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>188300</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>122200</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>153800</v>
       </c>
-      <c r="P35" s="3"/>
-    </row>
-    <row r="37" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q35" s="3"/>
+    </row>
+    <row r="37" spans="2:17" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="38" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E38" s="2">
         <v>44926</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>44561</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>44196</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>43830</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>43465</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>43100</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>42735</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>42369</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>42004</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>41639</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>41274</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>40908</v>
       </c>
-      <c r="P38" s="2"/>
-    </row>
-    <row r="39" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q38" s="2"/>
+    </row>
+    <row r="39" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>31</v>
       </c>
@@ -1883,8 +1967,9 @@
       <c r="N39" s="3"/>
       <c r="O39" s="3"/>
       <c r="P39" s="3"/>
-    </row>
-    <row r="40" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q39" s="3"/>
+    </row>
+    <row r="40" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>32</v>
       </c>
@@ -1901,386 +1986,414 @@
       <c r="N40" s="3"/>
       <c r="O40" s="3"/>
       <c r="P40" s="3"/>
-    </row>
-    <row r="41" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q40" s="3"/>
+    </row>
+    <row r="41" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>33</v>
       </c>
       <c r="D41" s="3">
-        <v>1271800</v>
+        <v>1670500</v>
       </c>
       <c r="E41" s="3">
-        <v>1312900</v>
+        <v>1291000</v>
       </c>
       <c r="F41" s="3">
-        <v>1034100</v>
+        <v>1332700</v>
       </c>
       <c r="G41" s="3">
-        <v>829900</v>
+        <v>1049700</v>
       </c>
       <c r="H41" s="3">
-        <v>773500</v>
+        <v>842400</v>
       </c>
       <c r="I41" s="3">
-        <v>570400</v>
+        <v>785200</v>
       </c>
       <c r="J41" s="3">
+        <v>578900</v>
+      </c>
+      <c r="K41" s="3">
         <v>561100</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>523500</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>556000</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>765300</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>497500</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>637600</v>
       </c>
-      <c r="P41" s="3"/>
-    </row>
-    <row r="42" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q41" s="3"/>
+    </row>
+    <row r="42" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D42" s="3">
-        <v>340700</v>
+        <v>344900</v>
       </c>
       <c r="E42" s="3">
-        <v>392200</v>
+        <v>345800</v>
       </c>
       <c r="F42" s="3">
-        <v>375300</v>
+        <v>398100</v>
       </c>
       <c r="G42" s="3">
-        <v>316200</v>
+        <v>381000</v>
       </c>
       <c r="H42" s="3">
-        <v>407000</v>
+        <v>320900</v>
       </c>
       <c r="I42" s="3">
-        <v>441800</v>
+        <v>413100</v>
       </c>
       <c r="J42" s="3">
+        <v>448400</v>
+      </c>
+      <c r="K42" s="3">
         <v>333000</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>509900</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>654800</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>585800</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>582800</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>334700</v>
       </c>
-      <c r="P42" s="3"/>
-    </row>
-    <row r="43" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q42" s="3"/>
+    </row>
+    <row r="43" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D43" s="3">
-        <v>420300</v>
+        <v>464600</v>
       </c>
       <c r="E43" s="3">
-        <v>353300</v>
+        <v>426600</v>
       </c>
       <c r="F43" s="3">
-        <v>312200</v>
+        <v>358600</v>
       </c>
       <c r="G43" s="3">
-        <v>298400</v>
+        <v>316900</v>
       </c>
       <c r="H43" s="3">
-        <v>258800</v>
+        <v>302900</v>
       </c>
       <c r="I43" s="3">
-        <v>264100</v>
+        <v>262700</v>
       </c>
       <c r="J43" s="3">
+        <v>268100</v>
+      </c>
+      <c r="K43" s="3">
         <v>236100</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>212500</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>229700</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>233800</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>189900</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>185900</v>
       </c>
-      <c r="P43" s="3"/>
-    </row>
-    <row r="44" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q43" s="3"/>
+    </row>
+    <row r="44" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D44" s="3">
-        <v>28300</v>
+        <v>44900</v>
       </c>
       <c r="E44" s="3">
-        <v>24600</v>
+        <v>28700</v>
       </c>
       <c r="F44" s="3">
-        <v>22600</v>
+        <v>24900</v>
       </c>
       <c r="G44" s="3">
-        <v>27300</v>
+        <v>22900</v>
       </c>
       <c r="H44" s="3">
-        <v>48800</v>
+        <v>27700</v>
       </c>
       <c r="I44" s="3">
-        <v>19800</v>
+        <v>49500</v>
       </c>
       <c r="J44" s="3">
+        <v>20100</v>
+      </c>
+      <c r="K44" s="3">
         <v>11400</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>5700</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>4600</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>3900</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>3400</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>3800</v>
       </c>
-      <c r="P44" s="3"/>
-    </row>
-    <row r="45" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q44" s="3"/>
+    </row>
+    <row r="45" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D45" s="3">
-        <v>63300</v>
+        <v>96200</v>
       </c>
       <c r="E45" s="3">
-        <v>53400</v>
+        <v>64300</v>
       </c>
       <c r="F45" s="3">
-        <v>39600</v>
+        <v>54200</v>
       </c>
       <c r="G45" s="3">
-        <v>37900</v>
+        <v>40200</v>
       </c>
       <c r="H45" s="3">
-        <v>142600</v>
+        <v>38400</v>
       </c>
       <c r="I45" s="3">
-        <v>143400</v>
+        <v>144700</v>
       </c>
       <c r="J45" s="3">
+        <v>145600</v>
+      </c>
+      <c r="K45" s="3">
         <v>153400</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>176900</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>174100</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>185300</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>174100</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>179300</v>
       </c>
-      <c r="P45" s="3"/>
-    </row>
-    <row r="46" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q45" s="3"/>
+    </row>
+    <row r="46" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D46" s="3">
-        <v>2124400</v>
+        <v>2621100</v>
       </c>
       <c r="E46" s="3">
-        <v>2136400</v>
+        <v>2156400</v>
       </c>
       <c r="F46" s="3">
-        <v>1783800</v>
+        <v>2168600</v>
       </c>
       <c r="G46" s="3">
-        <v>1509600</v>
+        <v>1810700</v>
       </c>
       <c r="H46" s="3">
-        <v>1499100</v>
+        <v>1532300</v>
       </c>
       <c r="I46" s="3">
-        <v>1439500</v>
+        <v>1521700</v>
       </c>
       <c r="J46" s="3">
+        <v>1461200</v>
+      </c>
+      <c r="K46" s="3">
         <v>1295000</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>1428500</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>1619300</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>1774100</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>1447700</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>1341300</v>
       </c>
-      <c r="P46" s="3"/>
-    </row>
-    <row r="47" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q46" s="3"/>
+    </row>
+    <row r="47" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D47" s="3">
-        <v>494300</v>
+        <v>123800</v>
       </c>
       <c r="E47" s="3">
-        <v>175900</v>
+        <v>501700</v>
       </c>
       <c r="F47" s="3">
-        <v>240500</v>
+        <v>178600</v>
       </c>
       <c r="G47" s="3">
-        <v>331900</v>
+        <v>244100</v>
       </c>
       <c r="H47" s="3">
-        <v>297000</v>
+        <v>336900</v>
       </c>
       <c r="I47" s="3">
-        <v>347900</v>
+        <v>301500</v>
       </c>
       <c r="J47" s="3">
+        <v>353100</v>
+      </c>
+      <c r="K47" s="3">
         <v>336800</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>445300</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>608300</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>491400</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>322500</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>208300</v>
       </c>
-      <c r="P47" s="3"/>
-    </row>
-    <row r="48" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q47" s="3"/>
+    </row>
+    <row r="48" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D48" s="3">
-        <v>47100</v>
+        <v>43700</v>
       </c>
       <c r="E48" s="3">
-        <v>52700</v>
+        <v>47800</v>
       </c>
       <c r="F48" s="3">
-        <v>52900</v>
+        <v>53500</v>
       </c>
       <c r="G48" s="3">
-        <v>65500</v>
+        <v>53700</v>
       </c>
       <c r="H48" s="3">
-        <v>58200</v>
+        <v>66500</v>
       </c>
       <c r="I48" s="3">
-        <v>54600</v>
+        <v>59100</v>
       </c>
       <c r="J48" s="3">
+        <v>55400</v>
+      </c>
+      <c r="K48" s="3">
         <v>43500</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>41000</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>43600</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>44000</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>40300</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>45700</v>
       </c>
-      <c r="P48" s="3"/>
-    </row>
-    <row r="49" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q48" s="3"/>
+    </row>
+    <row r="49" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D49" s="3">
-        <v>161300</v>
+        <v>214900</v>
       </c>
       <c r="E49" s="3">
-        <v>168900</v>
+        <v>163700</v>
       </c>
       <c r="F49" s="3">
-        <v>172000</v>
+        <v>171400</v>
       </c>
       <c r="G49" s="3">
-        <v>240200</v>
+        <v>174600</v>
       </c>
       <c r="H49" s="3">
-        <v>233100</v>
+        <v>243800</v>
       </c>
       <c r="I49" s="3">
-        <v>267600</v>
+        <v>236700</v>
       </c>
       <c r="J49" s="3">
+        <v>271600</v>
+      </c>
+      <c r="K49" s="3">
         <v>282400</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>58200</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>83100</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>88000</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>71500</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>84400</v>
       </c>
-      <c r="P49" s="3"/>
-    </row>
-    <row r="50" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q49" s="3"/>
+    </row>
+    <row r="50" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>42</v>
       </c>
@@ -2320,9 +2433,12 @@
       <c r="O50" s="3">
         <v>0</v>
       </c>
-      <c r="P50" s="3"/>
-    </row>
-    <row r="51" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P50" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q50" s="3"/>
+    </row>
+    <row r="51" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>43</v>
       </c>
@@ -2362,51 +2478,57 @@
       <c r="O51" s="3">
         <v>0</v>
       </c>
-      <c r="P51" s="3"/>
-    </row>
-    <row r="52" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P51" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q51" s="3"/>
+    </row>
+    <row r="52" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>44</v>
       </c>
       <c r="D52" s="3">
-        <v>299100</v>
+        <v>316800</v>
       </c>
       <c r="E52" s="3">
-        <v>258000</v>
+        <v>303600</v>
       </c>
       <c r="F52" s="3">
-        <v>252000</v>
+        <v>261800</v>
       </c>
       <c r="G52" s="3">
-        <v>241300</v>
+        <v>255800</v>
       </c>
       <c r="H52" s="3">
-        <v>211000</v>
+        <v>244900</v>
       </c>
       <c r="I52" s="3">
-        <v>89300</v>
+        <v>214200</v>
       </c>
       <c r="J52" s="3">
+        <v>90700</v>
+      </c>
+      <c r="K52" s="3">
         <v>90900</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>86700</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>112000</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>115400</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>108700</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>109900</v>
       </c>
-      <c r="P52" s="3"/>
-    </row>
-    <row r="53" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q52" s="3"/>
+    </row>
+    <row r="53" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>45</v>
       </c>
@@ -2446,51 +2568,57 @@
       <c r="O53" s="3">
         <v>0</v>
       </c>
-      <c r="P53" s="3"/>
-    </row>
-    <row r="54" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P53" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q53" s="3"/>
+    </row>
+    <row r="54" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>46</v>
       </c>
       <c r="D54" s="3">
-        <v>3126100</v>
+        <v>3320300</v>
       </c>
       <c r="E54" s="3">
-        <v>2791800</v>
+        <v>3173200</v>
       </c>
       <c r="F54" s="3">
-        <v>2501300</v>
+        <v>2833900</v>
       </c>
       <c r="G54" s="3">
-        <v>2388500</v>
+        <v>2539000</v>
       </c>
       <c r="H54" s="3">
-        <v>2298500</v>
+        <v>2424400</v>
       </c>
       <c r="I54" s="3">
-        <v>2198900</v>
+        <v>2333100</v>
       </c>
       <c r="J54" s="3">
+        <v>2232000</v>
+      </c>
+      <c r="K54" s="3">
         <v>2048700</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>2059800</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>2466300</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>2512900</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>1990800</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>1789600</v>
       </c>
-      <c r="P54" s="3"/>
-    </row>
-    <row r="55" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q54" s="3"/>
+    </row>
+    <row r="55" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>47</v>
       </c>
@@ -2507,8 +2635,9 @@
       <c r="N55" s="3"/>
       <c r="O55" s="3"/>
       <c r="P55" s="3"/>
-    </row>
-    <row r="56" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q55" s="3"/>
+    </row>
+    <row r="56" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>48</v>
       </c>
@@ -2525,50 +2654,54 @@
       <c r="N56" s="3"/>
       <c r="O56" s="3"/>
       <c r="P56" s="3"/>
-    </row>
-    <row r="57" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q56" s="3"/>
+    </row>
+    <row r="57" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>49</v>
       </c>
       <c r="D57" s="3">
-        <v>14400</v>
+        <v>18400</v>
       </c>
       <c r="E57" s="3">
-        <v>7700</v>
+        <v>14600</v>
       </c>
       <c r="F57" s="3">
-        <v>6100</v>
+        <v>7900</v>
       </c>
       <c r="G57" s="3">
-        <v>8000</v>
+        <v>6200</v>
       </c>
       <c r="H57" s="3">
-        <v>10800</v>
+        <v>8100</v>
       </c>
       <c r="I57" s="3">
-        <v>4800</v>
+        <v>10900</v>
       </c>
       <c r="J57" s="3">
+        <v>4900</v>
+      </c>
+      <c r="K57" s="3">
         <v>5900</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>4000</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>5900</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>4700</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>6600</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>7900</v>
       </c>
-      <c r="P57" s="3"/>
-    </row>
-    <row r="58" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q57" s="3"/>
+    </row>
+    <row r="58" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>50</v>
       </c>
@@ -2608,93 +2741,102 @@
       <c r="O58" s="3">
         <v>0</v>
       </c>
-      <c r="P58" s="3"/>
-    </row>
-    <row r="59" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P58" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q58" s="3"/>
+    </row>
+    <row r="59" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D59" s="3">
-        <v>1528100</v>
+        <v>1768200</v>
       </c>
       <c r="E59" s="3">
-        <v>879500</v>
+        <v>1551100</v>
       </c>
       <c r="F59" s="3">
-        <v>866900</v>
+        <v>892800</v>
       </c>
       <c r="G59" s="3">
-        <v>785900</v>
+        <v>879900</v>
       </c>
       <c r="H59" s="3">
-        <v>729400</v>
+        <v>797700</v>
       </c>
       <c r="I59" s="3">
-        <v>717300</v>
+        <v>740300</v>
       </c>
       <c r="J59" s="3">
+        <v>728100</v>
+      </c>
+      <c r="K59" s="3">
         <v>669300</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>666300</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>811500</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>832000</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>702800</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>625500</v>
       </c>
-      <c r="P59" s="3"/>
-    </row>
-    <row r="60" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q59" s="3"/>
+    </row>
+    <row r="60" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D60" s="3">
-        <v>1542500</v>
+        <v>1786600</v>
       </c>
       <c r="E60" s="3">
-        <v>887300</v>
+        <v>1565700</v>
       </c>
       <c r="F60" s="3">
-        <v>872900</v>
+        <v>900600</v>
       </c>
       <c r="G60" s="3">
-        <v>793900</v>
+        <v>886100</v>
       </c>
       <c r="H60" s="3">
-        <v>740100</v>
+        <v>805800</v>
       </c>
       <c r="I60" s="3">
-        <v>722200</v>
+        <v>751300</v>
       </c>
       <c r="J60" s="3">
+        <v>733100</v>
+      </c>
+      <c r="K60" s="3">
         <v>675200</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>670300</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>817400</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>836700</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>709400</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>633300</v>
       </c>
-      <c r="P60" s="3"/>
-    </row>
-    <row r="61" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q60" s="3"/>
+    </row>
+    <row r="61" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>53</v>
       </c>
@@ -2734,51 +2876,57 @@
       <c r="O61" s="3">
         <v>0</v>
       </c>
-      <c r="P61" s="3"/>
-    </row>
-    <row r="62" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P61" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q61" s="3"/>
+    </row>
+    <row r="62" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D62" s="3">
-        <v>65200</v>
+        <v>88500</v>
       </c>
       <c r="E62" s="3">
-        <v>434200</v>
+        <v>66200</v>
       </c>
       <c r="F62" s="3">
-        <v>371000</v>
+        <v>440800</v>
       </c>
       <c r="G62" s="3">
-        <v>350100</v>
+        <v>376600</v>
       </c>
       <c r="H62" s="3">
-        <v>316200</v>
+        <v>355400</v>
       </c>
       <c r="I62" s="3">
-        <v>300900</v>
+        <v>320900</v>
       </c>
       <c r="J62" s="3">
+        <v>305400</v>
+      </c>
+      <c r="K62" s="3">
         <v>268100</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>257300</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>300100</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>306400</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>249700</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>204000</v>
       </c>
-      <c r="P62" s="3"/>
-    </row>
-    <row r="63" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q62" s="3"/>
+    </row>
+    <row r="63" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>55</v>
       </c>
@@ -2818,9 +2966,12 @@
       <c r="O63" s="3">
         <v>0</v>
       </c>
-      <c r="P63" s="3"/>
-    </row>
-    <row r="64" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P63" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q63" s="3"/>
+    </row>
+    <row r="64" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>19</v>
       </c>
@@ -2860,9 +3011,12 @@
       <c r="O64" s="3">
         <v>0</v>
       </c>
-      <c r="P64" s="3"/>
-    </row>
-    <row r="65" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P64" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q64" s="3"/>
+    </row>
+    <row r="65" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>56</v>
       </c>
@@ -2902,51 +3056,57 @@
       <c r="O65" s="3">
         <v>0</v>
       </c>
-      <c r="P65" s="3"/>
-    </row>
-    <row r="66" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P65" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q65" s="3"/>
+    </row>
+    <row r="66" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>57</v>
       </c>
       <c r="D66" s="3">
-        <v>1607800</v>
+        <v>1875300</v>
       </c>
       <c r="E66" s="3">
-        <v>1326800</v>
+        <v>1632000</v>
       </c>
       <c r="F66" s="3">
-        <v>1249400</v>
+        <v>1346700</v>
       </c>
       <c r="G66" s="3">
-        <v>1145000</v>
+        <v>1268300</v>
       </c>
       <c r="H66" s="3">
-        <v>1056800</v>
+        <v>1162200</v>
       </c>
       <c r="I66" s="3">
-        <v>1023100</v>
+        <v>1072700</v>
       </c>
       <c r="J66" s="3">
+        <v>1038500</v>
+      </c>
+      <c r="K66" s="3">
         <v>943300</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>927600</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>1117600</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>1143200</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>959200</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>837800</v>
       </c>
-      <c r="P66" s="3"/>
-    </row>
-    <row r="67" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q66" s="3"/>
+    </row>
+    <row r="67" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>58</v>
       </c>
@@ -2963,8 +3123,9 @@
       <c r="N67" s="3"/>
       <c r="O67" s="3"/>
       <c r="P67" s="3"/>
-    </row>
-    <row r="68" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q67" s="3"/>
+    </row>
+    <row r="68" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>59</v>
       </c>
@@ -3004,9 +3165,12 @@
       <c r="O68" s="3">
         <v>0</v>
       </c>
-      <c r="P68" s="3"/>
-    </row>
-    <row r="69" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P68" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q68" s="3"/>
+    </row>
+    <row r="69" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>60</v>
       </c>
@@ -3046,9 +3210,12 @@
       <c r="O69" s="3">
         <v>0</v>
       </c>
-      <c r="P69" s="3"/>
-    </row>
-    <row r="70" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P69" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q69" s="3"/>
+    </row>
+    <row r="70" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>61</v>
       </c>
@@ -3088,9 +3255,12 @@
       <c r="O70" s="3">
         <v>0</v>
       </c>
-      <c r="P70" s="3"/>
-    </row>
-    <row r="71" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P70" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q70" s="3"/>
+    </row>
+    <row r="71" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>62</v>
       </c>
@@ -3130,51 +3300,57 @@
       <c r="O71" s="3">
         <v>0</v>
       </c>
-      <c r="P71" s="3"/>
-    </row>
-    <row r="72" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P71" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q71" s="3"/>
+    </row>
+    <row r="72" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>63</v>
       </c>
       <c r="D72" s="3">
-        <v>1119000</v>
+        <v>1069600</v>
       </c>
       <c r="E72" s="3">
-        <v>1175700</v>
+        <v>1135800</v>
       </c>
       <c r="F72" s="3">
-        <v>1060100</v>
+        <v>1193400</v>
       </c>
       <c r="G72" s="3">
-        <v>1028500</v>
+        <v>1076000</v>
       </c>
       <c r="H72" s="3">
-        <v>993500</v>
+        <v>1044000</v>
       </c>
       <c r="I72" s="3">
-        <v>945900</v>
+        <v>1008500</v>
       </c>
       <c r="J72" s="3">
+        <v>960200</v>
+      </c>
+      <c r="K72" s="3">
         <v>903400</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>897200</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>1070500</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>1113200</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>969600</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>889800</v>
       </c>
-      <c r="P72" s="3"/>
-    </row>
-    <row r="73" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q72" s="3"/>
+    </row>
+    <row r="73" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>64</v>
       </c>
@@ -3214,9 +3390,12 @@
       <c r="O73" s="3">
         <v>0</v>
       </c>
-      <c r="P73" s="3"/>
-    </row>
-    <row r="74" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P73" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q73" s="3"/>
+    </row>
+    <row r="74" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>65</v>
       </c>
@@ -3256,9 +3435,12 @@
       <c r="O74" s="3">
         <v>0</v>
       </c>
-      <c r="P74" s="3"/>
-    </row>
-    <row r="75" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P74" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q74" s="3"/>
+    </row>
+    <row r="75" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>66</v>
       </c>
@@ -3298,51 +3480,57 @@
       <c r="O75" s="3">
         <v>0</v>
       </c>
-      <c r="P75" s="3"/>
-    </row>
-    <row r="76" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P75" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q75" s="3"/>
+    </row>
+    <row r="76" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>67</v>
       </c>
       <c r="D76" s="3">
-        <v>1518300</v>
+        <v>1445000</v>
       </c>
       <c r="E76" s="3">
-        <v>1465100</v>
+        <v>1541200</v>
       </c>
       <c r="F76" s="3">
-        <v>1251800</v>
+        <v>1487100</v>
       </c>
       <c r="G76" s="3">
-        <v>1243500</v>
+        <v>1270700</v>
       </c>
       <c r="H76" s="3">
-        <v>1241700</v>
+        <v>1262200</v>
       </c>
       <c r="I76" s="3">
-        <v>1175800</v>
+        <v>1260400</v>
       </c>
       <c r="J76" s="3">
+        <v>1193500</v>
+      </c>
+      <c r="K76" s="3">
         <v>1105300</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>1132200</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>1348700</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>1369700</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>1031600</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>951800</v>
       </c>
-      <c r="P76" s="3"/>
-    </row>
-    <row r="77" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q76" s="3"/>
+    </row>
+    <row r="77" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>68</v>
       </c>
@@ -3382,98 +3570,107 @@
       <c r="O77" s="3">
         <v>0</v>
       </c>
-      <c r="P77" s="3"/>
-    </row>
-    <row r="79" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P77" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q77" s="3"/>
+    </row>
+    <row r="79" spans="2:17" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="80" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E80" s="2">
         <v>44926</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>44561</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>44196</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>43830</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>43465</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>43100</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>42735</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>42369</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>42004</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>41639</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>41274</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>40908</v>
       </c>
-      <c r="P80" s="2"/>
-    </row>
-    <row r="81" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q80" s="2"/>
+    </row>
+    <row r="81" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D81" s="3">
-        <v>198200</v>
+        <v>72300</v>
       </c>
       <c r="E81" s="3">
-        <v>254800</v>
+        <v>201100</v>
       </c>
       <c r="F81" s="3">
-        <v>178600</v>
+        <v>258600</v>
       </c>
       <c r="G81" s="3">
-        <v>185600</v>
+        <v>181300</v>
       </c>
       <c r="H81" s="3">
-        <v>188000</v>
+        <v>188400</v>
       </c>
       <c r="I81" s="3">
-        <v>170600</v>
+        <v>190800</v>
       </c>
       <c r="J81" s="3">
+        <v>173200</v>
+      </c>
+      <c r="K81" s="3">
         <v>163700</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>152000</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>196500</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>188300</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>122200</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>153800</v>
       </c>
-      <c r="P81" s="3"/>
-    </row>
-    <row r="82" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q81" s="3"/>
+    </row>
+    <row r="82" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>70</v>
       </c>
@@ -3490,50 +3687,54 @@
       <c r="N82" s="3"/>
       <c r="O82" s="3"/>
       <c r="P82" s="3"/>
-    </row>
-    <row r="83" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q82" s="3"/>
+    </row>
+    <row r="83" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>71</v>
       </c>
       <c r="D83" s="3">
-        <v>167200</v>
+        <v>190800</v>
       </c>
       <c r="E83" s="3">
-        <v>138700</v>
+        <v>169700</v>
       </c>
       <c r="F83" s="3">
-        <v>150600</v>
+        <v>140800</v>
       </c>
       <c r="G83" s="3">
-        <v>105000</v>
+        <v>152800</v>
       </c>
       <c r="H83" s="3">
-        <v>105700</v>
+        <v>106600</v>
       </c>
       <c r="I83" s="3">
-        <v>92600</v>
+        <v>107300</v>
       </c>
       <c r="J83" s="3">
+        <v>94000</v>
+      </c>
+      <c r="K83" s="3">
         <v>74300</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>58500</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>67100</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>69600</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>68100</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>65100</v>
       </c>
-      <c r="P83" s="3"/>
-    </row>
-    <row r="84" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q83" s="3"/>
+    </row>
+    <row r="84" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>72</v>
       </c>
@@ -3573,9 +3774,12 @@
       <c r="O84" s="3">
         <v>0</v>
       </c>
-      <c r="P84" s="3"/>
-    </row>
-    <row r="85" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P84" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q84" s="3"/>
+    </row>
+    <row r="85" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>73</v>
       </c>
@@ -3615,9 +3819,12 @@
       <c r="O85" s="3">
         <v>0</v>
       </c>
-      <c r="P85" s="3"/>
-    </row>
-    <row r="86" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P85" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q85" s="3"/>
+    </row>
+    <row r="86" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>74</v>
       </c>
@@ -3657,9 +3864,12 @@
       <c r="O86" s="3">
         <v>0</v>
       </c>
-      <c r="P86" s="3"/>
-    </row>
-    <row r="87" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P86" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q86" s="3"/>
+    </row>
+    <row r="87" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>75</v>
       </c>
@@ -3699,9 +3909,12 @@
       <c r="O87" s="3">
         <v>0</v>
       </c>
-      <c r="P87" s="3"/>
-    </row>
-    <row r="88" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P87" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q87" s="3"/>
+    </row>
+    <row r="88" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>76</v>
       </c>
@@ -3741,51 +3954,57 @@
       <c r="O88" s="3">
         <v>0</v>
       </c>
-      <c r="P88" s="3"/>
-    </row>
-    <row r="89" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P88" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q88" s="3"/>
+    </row>
+    <row r="89" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>77</v>
       </c>
       <c r="D89" s="3">
-        <v>373200</v>
+        <v>385700</v>
       </c>
       <c r="E89" s="3">
-        <v>367000</v>
+        <v>378800</v>
       </c>
       <c r="F89" s="3">
-        <v>360600</v>
+        <v>372500</v>
       </c>
       <c r="G89" s="3">
-        <v>299500</v>
+        <v>366000</v>
       </c>
       <c r="H89" s="3">
-        <v>331700</v>
+        <v>304000</v>
       </c>
       <c r="I89" s="3">
-        <v>311500</v>
+        <v>336700</v>
       </c>
       <c r="J89" s="3">
+        <v>316200</v>
+      </c>
+      <c r="K89" s="3">
         <v>222500</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>216200</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>281400</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>295400</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>286600</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>231700</v>
       </c>
-      <c r="P89" s="3"/>
-    </row>
-    <row r="90" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q89" s="3"/>
+    </row>
+    <row r="90" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>78</v>
       </c>
@@ -3802,50 +4021,54 @@
       <c r="N90" s="3"/>
       <c r="O90" s="3"/>
       <c r="P90" s="3"/>
-    </row>
-    <row r="91" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q90" s="3"/>
+    </row>
+    <row r="91" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>79</v>
       </c>
       <c r="D91" s="3">
-        <v>-9300</v>
+        <v>-14700</v>
       </c>
       <c r="E91" s="3">
-        <v>-14300</v>
+        <v>-9400</v>
       </c>
       <c r="F91" s="3">
-        <v>-10400</v>
+        <v>-14500</v>
       </c>
       <c r="G91" s="3">
-        <v>-26800</v>
+        <v>-10500</v>
       </c>
       <c r="H91" s="3">
-        <v>-23600</v>
+        <v>-27200</v>
       </c>
       <c r="I91" s="3">
-        <v>-30500</v>
+        <v>-24000</v>
       </c>
       <c r="J91" s="3">
+        <v>-31000</v>
+      </c>
+      <c r="K91" s="3">
         <v>-19800</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-25000</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-18000</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-17600</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-10800</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-61900</v>
       </c>
-      <c r="P91" s="3"/>
-    </row>
-    <row r="92" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q91" s="3"/>
+    </row>
+    <row r="92" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>80</v>
       </c>
@@ -3885,9 +4108,12 @@
       <c r="O92" s="3">
         <v>0</v>
       </c>
-      <c r="P92" s="3"/>
-    </row>
-    <row r="93" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P92" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q92" s="3"/>
+    </row>
+    <row r="93" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>81</v>
       </c>
@@ -3927,51 +4153,57 @@
       <c r="O93" s="3">
         <v>0</v>
       </c>
-      <c r="P93" s="3"/>
-    </row>
-    <row r="94" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P93" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q93" s="3"/>
+    </row>
+    <row r="94" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>82</v>
       </c>
       <c r="D94" s="3">
-        <v>-449600</v>
+        <v>208900</v>
       </c>
       <c r="E94" s="3">
-        <v>17100</v>
+        <v>-456400</v>
       </c>
       <c r="F94" s="3">
-        <v>-38400</v>
+        <v>17400</v>
       </c>
       <c r="G94" s="3">
-        <v>-9800</v>
+        <v>-38900</v>
       </c>
       <c r="H94" s="3">
-        <v>5400</v>
+        <v>-9900</v>
       </c>
       <c r="I94" s="3">
-        <v>-224500</v>
+        <v>5500</v>
       </c>
       <c r="J94" s="3">
+        <v>-227900</v>
+      </c>
+      <c r="K94" s="3">
         <v>85800</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-34900</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-290000</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-155200</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-414900</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-23200</v>
       </c>
-      <c r="P94" s="3"/>
-    </row>
-    <row r="95" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q94" s="3"/>
+    </row>
+    <row r="95" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>83</v>
       </c>
@@ -3988,50 +4220,54 @@
       <c r="N95" s="3"/>
       <c r="O95" s="3"/>
       <c r="P95" s="3"/>
-    </row>
-    <row r="96" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q95" s="3"/>
+    </row>
+    <row r="96" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>84</v>
       </c>
       <c r="D96" s="3">
-        <v>-176200</v>
+        <v>-136500</v>
       </c>
       <c r="E96" s="3">
-        <v>-137900</v>
+        <v>-178900</v>
       </c>
       <c r="F96" s="3">
-        <v>-143900</v>
+        <v>-140000</v>
       </c>
       <c r="G96" s="3">
-        <v>-146000</v>
+        <v>-146100</v>
       </c>
       <c r="H96" s="3">
-        <v>-131400</v>
+        <v>-148200</v>
       </c>
       <c r="I96" s="3">
-        <v>-124000</v>
+        <v>-133400</v>
       </c>
       <c r="J96" s="3">
+        <v>-125900</v>
+      </c>
+      <c r="K96" s="3">
         <v>-96200</v>
       </c>
-      <c r="K96" s="3">
+      <c r="L96" s="3">
         <v>-105200</v>
       </c>
-      <c r="L96" s="3">
+      <c r="M96" s="3">
         <v>-138900</v>
       </c>
-      <c r="M96" s="3">
+      <c r="N96" s="3">
         <v>-80800</v>
       </c>
-      <c r="N96" s="3">
+      <c r="O96" s="3">
         <v>-98200</v>
       </c>
-      <c r="O96" s="3">
+      <c r="P96" s="3">
         <v>-79200</v>
       </c>
-      <c r="P96" s="3"/>
-    </row>
-    <row r="97" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q96" s="3"/>
+    </row>
+    <row r="97" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>85</v>
       </c>
@@ -4071,9 +4307,12 @@
       <c r="O97" s="3">
         <v>0</v>
       </c>
-      <c r="P97" s="3"/>
-    </row>
-    <row r="98" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P97" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q97" s="3"/>
+    </row>
+    <row r="98" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>86</v>
       </c>
@@ -4113,9 +4352,12 @@
       <c r="O98" s="3">
         <v>0</v>
       </c>
-      <c r="P98" s="3"/>
-    </row>
-    <row r="99" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P98" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q98" s="3"/>
+    </row>
+    <row r="99" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>87</v>
       </c>
@@ -4155,133 +4397,145 @@
       <c r="O99" s="3">
         <v>0</v>
       </c>
-      <c r="P99" s="3"/>
-    </row>
-    <row r="100" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P99" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q99" s="3"/>
+    </row>
+    <row r="100" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>88</v>
       </c>
       <c r="D100" s="3">
-        <v>-202100</v>
+        <v>-292700</v>
       </c>
       <c r="E100" s="3">
-        <v>-109200</v>
+        <v>-205100</v>
       </c>
       <c r="F100" s="3">
-        <v>-140400</v>
+        <v>-110800</v>
       </c>
       <c r="G100" s="3">
-        <v>-172400</v>
+        <v>-142500</v>
       </c>
       <c r="H100" s="3">
-        <v>-87800</v>
+        <v>-175000</v>
       </c>
       <c r="I100" s="3">
-        <v>-112300</v>
+        <v>-89100</v>
       </c>
       <c r="J100" s="3">
+        <v>-114000</v>
+      </c>
+      <c r="K100" s="3">
         <v>-99900</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-66100</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-148800</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-2000</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-101200</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-120300</v>
       </c>
-      <c r="P100" s="3"/>
-    </row>
-    <row r="101" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q100" s="3"/>
+    </row>
+    <row r="101" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D101" s="3">
-        <v>158700</v>
+        <v>59500</v>
       </c>
       <c r="E101" s="3">
-        <v>67200</v>
+        <v>161100</v>
       </c>
       <c r="F101" s="3">
-        <v>-9000</v>
+        <v>68200</v>
       </c>
       <c r="G101" s="3">
-        <v>-7800</v>
+        <v>-9100</v>
       </c>
       <c r="H101" s="3">
-        <v>-29000</v>
+        <v>-8000</v>
       </c>
       <c r="I101" s="3">
+        <v>-29400</v>
+      </c>
+      <c r="J101" s="3">
         <v>-800</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>2100</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>-30000</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>22700</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>87700</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>41100</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>-25800</v>
       </c>
-      <c r="P101" s="3"/>
-    </row>
-    <row r="102" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q101" s="3"/>
+    </row>
+    <row r="102" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D102" s="3">
-        <v>-119800</v>
+        <v>361400</v>
       </c>
       <c r="E102" s="3">
-        <v>342100</v>
+        <v>-121600</v>
       </c>
       <c r="F102" s="3">
-        <v>172900</v>
+        <v>347200</v>
       </c>
       <c r="G102" s="3">
-        <v>109600</v>
+        <v>175500</v>
       </c>
       <c r="H102" s="3">
-        <v>220400</v>
+        <v>111200</v>
       </c>
       <c r="I102" s="3">
-        <v>-26100</v>
+        <v>223700</v>
       </c>
       <c r="J102" s="3">
+        <v>-26500</v>
+      </c>
+      <c r="K102" s="3">
         <v>210500</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>85200</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-134700</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>225900</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-188400</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>62400</v>
       </c>
-      <c r="P102" s="3"/>
+      <c r="Q102" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/AAII_Financials/Yearly/TMICY_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/TMICY_YR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="99" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="98" uniqueCount="92">
   <si>
     <t>TMICY</t>
   </si>
@@ -726,25 +726,25 @@
         <v>3</v>
       </c>
       <c r="D8" s="3">
-        <v>1676200</v>
+        <v>1586600</v>
       </c>
       <c r="E8" s="3">
-        <v>1508400</v>
+        <v>1427800</v>
       </c>
       <c r="F8" s="3">
-        <v>1283000</v>
+        <v>1214500</v>
       </c>
       <c r="G8" s="3">
-        <v>1173200</v>
+        <v>1110500</v>
       </c>
       <c r="H8" s="3">
-        <v>1113400</v>
+        <v>1053900</v>
       </c>
       <c r="I8" s="3">
-        <v>1081200</v>
+        <v>1023400</v>
       </c>
       <c r="J8" s="3">
-        <v>1003000</v>
+        <v>949400</v>
       </c>
       <c r="K8" s="3">
         <v>876100</v>
@@ -771,25 +771,25 @@
         <v>4</v>
       </c>
       <c r="D9" s="3">
-        <v>429100</v>
+        <v>406200</v>
       </c>
       <c r="E9" s="3">
-        <v>366000</v>
+        <v>346400</v>
       </c>
       <c r="F9" s="3">
-        <v>283200</v>
+        <v>268100</v>
       </c>
       <c r="G9" s="3">
-        <v>257200</v>
+        <v>243500</v>
       </c>
       <c r="H9" s="3">
-        <v>217700</v>
+        <v>206100</v>
       </c>
       <c r="I9" s="3">
-        <v>220600</v>
+        <v>208800</v>
       </c>
       <c r="J9" s="3">
-        <v>189700</v>
+        <v>179500</v>
       </c>
       <c r="K9" s="3">
         <v>153000</v>
@@ -816,25 +816,25 @@
         <v>5</v>
       </c>
       <c r="D10" s="3">
-        <v>1247100</v>
+        <v>1180500</v>
       </c>
       <c r="E10" s="3">
-        <v>1142400</v>
+        <v>1081400</v>
       </c>
       <c r="F10" s="3">
-        <v>999800</v>
+        <v>946400</v>
       </c>
       <c r="G10" s="3">
-        <v>915900</v>
+        <v>867000</v>
       </c>
       <c r="H10" s="3">
-        <v>895700</v>
+        <v>847900</v>
       </c>
       <c r="I10" s="3">
-        <v>860600</v>
+        <v>814600</v>
       </c>
       <c r="J10" s="3">
-        <v>813300</v>
+        <v>769900</v>
       </c>
       <c r="K10" s="3">
         <v>723100</v>
@@ -879,26 +879,26 @@
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="D12" s="3" t="s">
-        <v>91</v>
+      <c r="D12" s="3">
+        <v>29700</v>
       </c>
       <c r="E12" s="3">
-        <v>36400</v>
+        <v>34500</v>
       </c>
       <c r="F12" s="3">
-        <v>31500</v>
+        <v>29900</v>
       </c>
       <c r="G12" s="3">
-        <v>49500</v>
+        <v>46800</v>
       </c>
       <c r="H12" s="3">
-        <v>55500</v>
+        <v>52500</v>
       </c>
       <c r="I12" s="3">
-        <v>50200</v>
+        <v>47500</v>
       </c>
       <c r="J12" s="3">
-        <v>52500</v>
+        <v>49700</v>
       </c>
       <c r="K12" s="3">
         <v>35000</v>
@@ -970,22 +970,22 @@
         <v>9</v>
       </c>
       <c r="D14" s="3">
-        <v>29200</v>
+        <v>27600</v>
       </c>
       <c r="E14" s="3">
-        <v>-2600</v>
+        <v>-2400</v>
       </c>
       <c r="F14" s="3">
-        <v>1500</v>
+        <v>1400</v>
       </c>
       <c r="G14" s="3">
         <v>1300</v>
       </c>
       <c r="H14" s="3">
-        <v>500</v>
+        <v>400</v>
       </c>
       <c r="I14" s="3">
-        <v>2300</v>
+        <v>2200</v>
       </c>
       <c r="J14" s="3">
         <v>300</v>
@@ -1076,25 +1076,25 @@
         <v>11</v>
       </c>
       <c r="D17" s="3">
-        <v>1485600</v>
+        <v>1406300</v>
       </c>
       <c r="E17" s="3">
-        <v>1294600</v>
+        <v>1225400</v>
       </c>
       <c r="F17" s="3">
-        <v>990400</v>
+        <v>937500</v>
       </c>
       <c r="G17" s="3">
-        <v>908500</v>
+        <v>860000</v>
       </c>
       <c r="H17" s="3">
-        <v>859900</v>
+        <v>813900</v>
       </c>
       <c r="I17" s="3">
-        <v>841900</v>
+        <v>796900</v>
       </c>
       <c r="J17" s="3">
-        <v>757700</v>
+        <v>717200</v>
       </c>
       <c r="K17" s="3">
         <v>650400</v>
@@ -1121,25 +1121,25 @@
         <v>12</v>
       </c>
       <c r="D18" s="3">
-        <v>190500</v>
+        <v>180400</v>
       </c>
       <c r="E18" s="3">
-        <v>213800</v>
+        <v>202400</v>
       </c>
       <c r="F18" s="3">
-        <v>292600</v>
+        <v>277000</v>
       </c>
       <c r="G18" s="3">
-        <v>264700</v>
+        <v>250500</v>
       </c>
       <c r="H18" s="3">
-        <v>253500</v>
+        <v>240000</v>
       </c>
       <c r="I18" s="3">
-        <v>239300</v>
+        <v>226500</v>
       </c>
       <c r="J18" s="3">
-        <v>245300</v>
+        <v>232200</v>
       </c>
       <c r="K18" s="3">
         <v>225700</v>
@@ -1185,25 +1185,25 @@
         <v>14</v>
       </c>
       <c r="D20" s="3">
-        <v>25000</v>
+        <v>23700</v>
       </c>
       <c r="E20" s="3">
-        <v>68900</v>
+        <v>65200</v>
       </c>
       <c r="F20" s="3">
-        <v>60400</v>
+        <v>57200</v>
       </c>
       <c r="G20" s="3">
-        <v>3900</v>
+        <v>3700</v>
       </c>
       <c r="H20" s="3">
-        <v>10300</v>
+        <v>9700</v>
       </c>
       <c r="I20" s="3">
-        <v>11400</v>
+        <v>10800</v>
       </c>
       <c r="J20" s="3">
-        <v>4700</v>
+        <v>4500</v>
       </c>
       <c r="K20" s="3">
         <v>11500</v>
@@ -1230,25 +1230,25 @@
         <v>15</v>
       </c>
       <c r="D21" s="3">
-        <v>407200</v>
+        <v>384400</v>
       </c>
       <c r="E21" s="3">
-        <v>453200</v>
+        <v>428000</v>
       </c>
       <c r="F21" s="3">
-        <v>494500</v>
+        <v>467300</v>
       </c>
       <c r="G21" s="3">
-        <v>422100</v>
+        <v>398700</v>
       </c>
       <c r="H21" s="3">
-        <v>370900</v>
+        <v>350500</v>
       </c>
       <c r="I21" s="3">
-        <v>358400</v>
+        <v>338700</v>
       </c>
       <c r="J21" s="3">
-        <v>344500</v>
+        <v>325600</v>
       </c>
       <c r="K21" s="3">
         <v>311200</v>
@@ -1320,25 +1320,25 @@
         <v>17</v>
       </c>
       <c r="D23" s="3">
-        <v>215500</v>
+        <v>204000</v>
       </c>
       <c r="E23" s="3">
-        <v>282400</v>
+        <v>267300</v>
       </c>
       <c r="F23" s="3">
-        <v>353000</v>
+        <v>334100</v>
       </c>
       <c r="G23" s="3">
-        <v>268600</v>
+        <v>254300</v>
       </c>
       <c r="H23" s="3">
-        <v>263800</v>
+        <v>249700</v>
       </c>
       <c r="I23" s="3">
-        <v>250700</v>
+        <v>237300</v>
       </c>
       <c r="J23" s="3">
-        <v>250000</v>
+        <v>236700</v>
       </c>
       <c r="K23" s="3">
         <v>237200</v>
@@ -1365,25 +1365,25 @@
         <v>18</v>
       </c>
       <c r="D24" s="3">
-        <v>143000</v>
+        <v>135400</v>
       </c>
       <c r="E24" s="3">
-        <v>87200</v>
+        <v>82600</v>
       </c>
       <c r="F24" s="3">
-        <v>99400</v>
+        <v>94100</v>
       </c>
       <c r="G24" s="3">
-        <v>90800</v>
+        <v>86000</v>
       </c>
       <c r="H24" s="3">
-        <v>76300</v>
+        <v>72200</v>
       </c>
       <c r="I24" s="3">
-        <v>59900</v>
+        <v>56700</v>
       </c>
       <c r="J24" s="3">
-        <v>76900</v>
+        <v>72800</v>
       </c>
       <c r="K24" s="3">
         <v>73500</v>
@@ -1455,25 +1455,25 @@
         <v>20</v>
       </c>
       <c r="D26" s="3">
-        <v>72500</v>
+        <v>68600</v>
       </c>
       <c r="E26" s="3">
-        <v>195100</v>
+        <v>184700</v>
       </c>
       <c r="F26" s="3">
-        <v>253500</v>
+        <v>240000</v>
       </c>
       <c r="G26" s="3">
-        <v>177800</v>
+        <v>168300</v>
       </c>
       <c r="H26" s="3">
-        <v>187500</v>
+        <v>177500</v>
       </c>
       <c r="I26" s="3">
-        <v>190700</v>
+        <v>180600</v>
       </c>
       <c r="J26" s="3">
-        <v>173200</v>
+        <v>163900</v>
       </c>
       <c r="K26" s="3">
         <v>163700</v>
@@ -1500,25 +1500,25 @@
         <v>21</v>
       </c>
       <c r="D27" s="3">
-        <v>72300</v>
+        <v>68500</v>
       </c>
       <c r="E27" s="3">
-        <v>201100</v>
+        <v>190400</v>
       </c>
       <c r="F27" s="3">
-        <v>258600</v>
+        <v>244800</v>
       </c>
       <c r="G27" s="3">
-        <v>181300</v>
+        <v>171600</v>
       </c>
       <c r="H27" s="3">
-        <v>188400</v>
+        <v>178300</v>
       </c>
       <c r="I27" s="3">
-        <v>190800</v>
+        <v>180600</v>
       </c>
       <c r="J27" s="3">
-        <v>173200</v>
+        <v>163900</v>
       </c>
       <c r="K27" s="3">
         <v>163700</v>
@@ -1725,25 +1725,25 @@
         <v>26</v>
       </c>
       <c r="D32" s="3">
-        <v>-25000</v>
+        <v>-23700</v>
       </c>
       <c r="E32" s="3">
-        <v>-68900</v>
+        <v>-65200</v>
       </c>
       <c r="F32" s="3">
-        <v>-60400</v>
+        <v>-57200</v>
       </c>
       <c r="G32" s="3">
-        <v>-3900</v>
+        <v>-3700</v>
       </c>
       <c r="H32" s="3">
-        <v>-10300</v>
+        <v>-9700</v>
       </c>
       <c r="I32" s="3">
-        <v>-11400</v>
+        <v>-10800</v>
       </c>
       <c r="J32" s="3">
-        <v>-4700</v>
+        <v>-4500</v>
       </c>
       <c r="K32" s="3">
         <v>-11500</v>
@@ -1770,25 +1770,25 @@
         <v>27</v>
       </c>
       <c r="D33" s="3">
-        <v>72300</v>
+        <v>68500</v>
       </c>
       <c r="E33" s="3">
-        <v>201100</v>
+        <v>190400</v>
       </c>
       <c r="F33" s="3">
-        <v>258600</v>
+        <v>244800</v>
       </c>
       <c r="G33" s="3">
-        <v>181300</v>
+        <v>171600</v>
       </c>
       <c r="H33" s="3">
-        <v>188400</v>
+        <v>178300</v>
       </c>
       <c r="I33" s="3">
-        <v>190800</v>
+        <v>180600</v>
       </c>
       <c r="J33" s="3">
-        <v>173200</v>
+        <v>163900</v>
       </c>
       <c r="K33" s="3">
         <v>163700</v>
@@ -1860,25 +1860,25 @@
         <v>29</v>
       </c>
       <c r="D35" s="3">
-        <v>72300</v>
+        <v>68500</v>
       </c>
       <c r="E35" s="3">
-        <v>201100</v>
+        <v>190400</v>
       </c>
       <c r="F35" s="3">
-        <v>258600</v>
+        <v>244800</v>
       </c>
       <c r="G35" s="3">
-        <v>181300</v>
+        <v>171600</v>
       </c>
       <c r="H35" s="3">
-        <v>188400</v>
+        <v>178300</v>
       </c>
       <c r="I35" s="3">
-        <v>190800</v>
+        <v>180600</v>
       </c>
       <c r="J35" s="3">
-        <v>173200</v>
+        <v>163900</v>
       </c>
       <c r="K35" s="3">
         <v>163700</v>
@@ -1993,25 +1993,25 @@
         <v>33</v>
       </c>
       <c r="D41" s="3">
-        <v>1670500</v>
+        <v>1581300</v>
       </c>
       <c r="E41" s="3">
-        <v>1291000</v>
+        <v>1222000</v>
       </c>
       <c r="F41" s="3">
-        <v>1332700</v>
+        <v>1261500</v>
       </c>
       <c r="G41" s="3">
-        <v>1049700</v>
+        <v>993600</v>
       </c>
       <c r="H41" s="3">
-        <v>842400</v>
+        <v>797400</v>
       </c>
       <c r="I41" s="3">
-        <v>785200</v>
+        <v>743200</v>
       </c>
       <c r="J41" s="3">
-        <v>578900</v>
+        <v>548000</v>
       </c>
       <c r="K41" s="3">
         <v>561100</v>
@@ -2038,25 +2038,25 @@
         <v>34</v>
       </c>
       <c r="D42" s="3">
-        <v>344900</v>
+        <v>326500</v>
       </c>
       <c r="E42" s="3">
-        <v>345800</v>
+        <v>327300</v>
       </c>
       <c r="F42" s="3">
-        <v>398100</v>
+        <v>376900</v>
       </c>
       <c r="G42" s="3">
-        <v>381000</v>
+        <v>360600</v>
       </c>
       <c r="H42" s="3">
-        <v>320900</v>
+        <v>303800</v>
       </c>
       <c r="I42" s="3">
-        <v>413100</v>
+        <v>391000</v>
       </c>
       <c r="J42" s="3">
-        <v>448400</v>
+        <v>424500</v>
       </c>
       <c r="K42" s="3">
         <v>333000</v>
@@ -2083,25 +2083,25 @@
         <v>35</v>
       </c>
       <c r="D43" s="3">
-        <v>464600</v>
+        <v>439700</v>
       </c>
       <c r="E43" s="3">
-        <v>426600</v>
+        <v>403800</v>
       </c>
       <c r="F43" s="3">
-        <v>358600</v>
+        <v>339500</v>
       </c>
       <c r="G43" s="3">
-        <v>316900</v>
+        <v>300000</v>
       </c>
       <c r="H43" s="3">
-        <v>302900</v>
+        <v>286700</v>
       </c>
       <c r="I43" s="3">
-        <v>262700</v>
+        <v>248700</v>
       </c>
       <c r="J43" s="3">
-        <v>268100</v>
+        <v>253800</v>
       </c>
       <c r="K43" s="3">
         <v>236100</v>
@@ -2128,25 +2128,25 @@
         <v>36</v>
       </c>
       <c r="D44" s="3">
-        <v>44900</v>
+        <v>42500</v>
       </c>
       <c r="E44" s="3">
-        <v>28700</v>
+        <v>27100</v>
       </c>
       <c r="F44" s="3">
-        <v>24900</v>
+        <v>23600</v>
       </c>
       <c r="G44" s="3">
-        <v>22900</v>
+        <v>21700</v>
       </c>
       <c r="H44" s="3">
-        <v>27700</v>
+        <v>26200</v>
       </c>
       <c r="I44" s="3">
-        <v>49500</v>
+        <v>46900</v>
       </c>
       <c r="J44" s="3">
-        <v>20100</v>
+        <v>19000</v>
       </c>
       <c r="K44" s="3">
         <v>11400</v>
@@ -2173,25 +2173,25 @@
         <v>37</v>
       </c>
       <c r="D45" s="3">
-        <v>96200</v>
+        <v>91100</v>
       </c>
       <c r="E45" s="3">
-        <v>64300</v>
+        <v>60800</v>
       </c>
       <c r="F45" s="3">
-        <v>54200</v>
+        <v>51300</v>
       </c>
       <c r="G45" s="3">
-        <v>40200</v>
+        <v>38000</v>
       </c>
       <c r="H45" s="3">
-        <v>38400</v>
+        <v>36400</v>
       </c>
       <c r="I45" s="3">
-        <v>144700</v>
+        <v>137000</v>
       </c>
       <c r="J45" s="3">
-        <v>145600</v>
+        <v>137800</v>
       </c>
       <c r="K45" s="3">
         <v>153400</v>
@@ -2218,25 +2218,25 @@
         <v>38</v>
       </c>
       <c r="D46" s="3">
-        <v>2621100</v>
+        <v>2481100</v>
       </c>
       <c r="E46" s="3">
-        <v>2156400</v>
+        <v>2041200</v>
       </c>
       <c r="F46" s="3">
-        <v>2168600</v>
+        <v>2052800</v>
       </c>
       <c r="G46" s="3">
-        <v>1810700</v>
+        <v>1714000</v>
       </c>
       <c r="H46" s="3">
-        <v>1532300</v>
+        <v>1450500</v>
       </c>
       <c r="I46" s="3">
-        <v>1521700</v>
+        <v>1440400</v>
       </c>
       <c r="J46" s="3">
-        <v>1461200</v>
+        <v>1383100</v>
       </c>
       <c r="K46" s="3">
         <v>1295000</v>
@@ -2263,25 +2263,25 @@
         <v>39</v>
       </c>
       <c r="D47" s="3">
-        <v>123800</v>
+        <v>117200</v>
       </c>
       <c r="E47" s="3">
-        <v>501700</v>
+        <v>474900</v>
       </c>
       <c r="F47" s="3">
-        <v>178600</v>
+        <v>169000</v>
       </c>
       <c r="G47" s="3">
-        <v>244100</v>
+        <v>231100</v>
       </c>
       <c r="H47" s="3">
-        <v>336900</v>
+        <v>318900</v>
       </c>
       <c r="I47" s="3">
-        <v>301500</v>
+        <v>285400</v>
       </c>
       <c r="J47" s="3">
-        <v>353100</v>
+        <v>334300</v>
       </c>
       <c r="K47" s="3">
         <v>336800</v>
@@ -2308,25 +2308,25 @@
         <v>40</v>
       </c>
       <c r="D48" s="3">
-        <v>43700</v>
+        <v>41400</v>
       </c>
       <c r="E48" s="3">
-        <v>47800</v>
+        <v>45200</v>
       </c>
       <c r="F48" s="3">
-        <v>53500</v>
+        <v>50600</v>
       </c>
       <c r="G48" s="3">
-        <v>53700</v>
+        <v>50900</v>
       </c>
       <c r="H48" s="3">
-        <v>66500</v>
+        <v>62900</v>
       </c>
       <c r="I48" s="3">
-        <v>59100</v>
+        <v>55900</v>
       </c>
       <c r="J48" s="3">
-        <v>55400</v>
+        <v>52500</v>
       </c>
       <c r="K48" s="3">
         <v>43500</v>
@@ -2353,25 +2353,25 @@
         <v>41</v>
       </c>
       <c r="D49" s="3">
-        <v>214900</v>
+        <v>203400</v>
       </c>
       <c r="E49" s="3">
-        <v>163700</v>
+        <v>155000</v>
       </c>
       <c r="F49" s="3">
-        <v>171400</v>
+        <v>162300</v>
       </c>
       <c r="G49" s="3">
-        <v>174600</v>
+        <v>165300</v>
       </c>
       <c r="H49" s="3">
-        <v>243800</v>
+        <v>230800</v>
       </c>
       <c r="I49" s="3">
-        <v>236700</v>
+        <v>224000</v>
       </c>
       <c r="J49" s="3">
-        <v>271600</v>
+        <v>257100</v>
       </c>
       <c r="K49" s="3">
         <v>282400</v>
@@ -2488,25 +2488,25 @@
         <v>44</v>
       </c>
       <c r="D52" s="3">
-        <v>316800</v>
+        <v>299800</v>
       </c>
       <c r="E52" s="3">
-        <v>303600</v>
+        <v>287400</v>
       </c>
       <c r="F52" s="3">
-        <v>261800</v>
+        <v>247900</v>
       </c>
       <c r="G52" s="3">
-        <v>255800</v>
+        <v>242200</v>
       </c>
       <c r="H52" s="3">
-        <v>244900</v>
+        <v>231800</v>
       </c>
       <c r="I52" s="3">
-        <v>214200</v>
+        <v>202700</v>
       </c>
       <c r="J52" s="3">
-        <v>90700</v>
+        <v>85800</v>
       </c>
       <c r="K52" s="3">
         <v>90900</v>
@@ -2578,25 +2578,25 @@
         <v>46</v>
       </c>
       <c r="D54" s="3">
-        <v>3320300</v>
+        <v>3143000</v>
       </c>
       <c r="E54" s="3">
-        <v>3173200</v>
+        <v>3003700</v>
       </c>
       <c r="F54" s="3">
-        <v>2833900</v>
+        <v>2682500</v>
       </c>
       <c r="G54" s="3">
-        <v>2539000</v>
+        <v>2403400</v>
       </c>
       <c r="H54" s="3">
-        <v>2424400</v>
+        <v>2294900</v>
       </c>
       <c r="I54" s="3">
-        <v>2333100</v>
+        <v>2208500</v>
       </c>
       <c r="J54" s="3">
-        <v>2232000</v>
+        <v>2112800</v>
       </c>
       <c r="K54" s="3">
         <v>2048700</v>
@@ -2661,25 +2661,25 @@
         <v>49</v>
       </c>
       <c r="D57" s="3">
-        <v>18400</v>
+        <v>17400</v>
       </c>
       <c r="E57" s="3">
-        <v>14600</v>
+        <v>13800</v>
       </c>
       <c r="F57" s="3">
-        <v>7900</v>
+        <v>7400</v>
       </c>
       <c r="G57" s="3">
-        <v>6200</v>
+        <v>5900</v>
       </c>
       <c r="H57" s="3">
-        <v>8100</v>
+        <v>7700</v>
       </c>
       <c r="I57" s="3">
-        <v>10900</v>
+        <v>10300</v>
       </c>
       <c r="J57" s="3">
-        <v>4900</v>
+        <v>4700</v>
       </c>
       <c r="K57" s="3">
         <v>5900</v>
@@ -2751,25 +2751,25 @@
         <v>51</v>
       </c>
       <c r="D59" s="3">
-        <v>1768200</v>
+        <v>1673800</v>
       </c>
       <c r="E59" s="3">
-        <v>1551100</v>
+        <v>1468200</v>
       </c>
       <c r="F59" s="3">
-        <v>892800</v>
+        <v>845100</v>
       </c>
       <c r="G59" s="3">
-        <v>879900</v>
+        <v>832900</v>
       </c>
       <c r="H59" s="3">
-        <v>797700</v>
+        <v>755100</v>
       </c>
       <c r="I59" s="3">
-        <v>740300</v>
+        <v>700800</v>
       </c>
       <c r="J59" s="3">
-        <v>728100</v>
+        <v>689300</v>
       </c>
       <c r="K59" s="3">
         <v>669300</v>
@@ -2796,25 +2796,25 @@
         <v>52</v>
       </c>
       <c r="D60" s="3">
-        <v>1786600</v>
+        <v>1691200</v>
       </c>
       <c r="E60" s="3">
-        <v>1565700</v>
+        <v>1482100</v>
       </c>
       <c r="F60" s="3">
-        <v>900600</v>
+        <v>852500</v>
       </c>
       <c r="G60" s="3">
-        <v>886100</v>
+        <v>838800</v>
       </c>
       <c r="H60" s="3">
-        <v>805800</v>
+        <v>762800</v>
       </c>
       <c r="I60" s="3">
-        <v>751300</v>
+        <v>711100</v>
       </c>
       <c r="J60" s="3">
-        <v>733100</v>
+        <v>693900</v>
       </c>
       <c r="K60" s="3">
         <v>675200</v>
@@ -2886,25 +2886,25 @@
         <v>54</v>
       </c>
       <c r="D62" s="3">
-        <v>88500</v>
+        <v>83800</v>
       </c>
       <c r="E62" s="3">
-        <v>66200</v>
+        <v>62700</v>
       </c>
       <c r="F62" s="3">
-        <v>440800</v>
+        <v>417200</v>
       </c>
       <c r="G62" s="3">
-        <v>376600</v>
+        <v>356500</v>
       </c>
       <c r="H62" s="3">
-        <v>355400</v>
+        <v>336400</v>
       </c>
       <c r="I62" s="3">
-        <v>320900</v>
+        <v>303800</v>
       </c>
       <c r="J62" s="3">
-        <v>305400</v>
+        <v>289100</v>
       </c>
       <c r="K62" s="3">
         <v>268100</v>
@@ -3066,25 +3066,25 @@
         <v>57</v>
       </c>
       <c r="D66" s="3">
-        <v>1875300</v>
+        <v>1775200</v>
       </c>
       <c r="E66" s="3">
-        <v>1632000</v>
+        <v>1544800</v>
       </c>
       <c r="F66" s="3">
-        <v>1346700</v>
+        <v>1274800</v>
       </c>
       <c r="G66" s="3">
-        <v>1268300</v>
+        <v>1200500</v>
       </c>
       <c r="H66" s="3">
-        <v>1162200</v>
+        <v>1100100</v>
       </c>
       <c r="I66" s="3">
-        <v>1072700</v>
+        <v>1015400</v>
       </c>
       <c r="J66" s="3">
-        <v>1038500</v>
+        <v>983100</v>
       </c>
       <c r="K66" s="3">
         <v>943300</v>
@@ -3310,25 +3310,25 @@
         <v>63</v>
       </c>
       <c r="D72" s="3">
-        <v>1069600</v>
+        <v>1012400</v>
       </c>
       <c r="E72" s="3">
-        <v>1135800</v>
+        <v>1075200</v>
       </c>
       <c r="F72" s="3">
-        <v>1193400</v>
+        <v>1129700</v>
       </c>
       <c r="G72" s="3">
-        <v>1076000</v>
+        <v>1018600</v>
       </c>
       <c r="H72" s="3">
-        <v>1044000</v>
+        <v>988200</v>
       </c>
       <c r="I72" s="3">
-        <v>1008500</v>
+        <v>954600</v>
       </c>
       <c r="J72" s="3">
-        <v>960200</v>
+        <v>908900</v>
       </c>
       <c r="K72" s="3">
         <v>903400</v>
@@ -3490,25 +3490,25 @@
         <v>67</v>
       </c>
       <c r="D76" s="3">
-        <v>1445000</v>
+        <v>1367800</v>
       </c>
       <c r="E76" s="3">
-        <v>1541200</v>
+        <v>1458900</v>
       </c>
       <c r="F76" s="3">
-        <v>1487100</v>
+        <v>1407700</v>
       </c>
       <c r="G76" s="3">
-        <v>1270700</v>
+        <v>1202800</v>
       </c>
       <c r="H76" s="3">
-        <v>1262200</v>
+        <v>1194800</v>
       </c>
       <c r="I76" s="3">
-        <v>1260400</v>
+        <v>1193100</v>
       </c>
       <c r="J76" s="3">
-        <v>1193500</v>
+        <v>1129700</v>
       </c>
       <c r="K76" s="3">
         <v>1105300</v>
@@ -3630,25 +3630,25 @@
         <v>27</v>
       </c>
       <c r="D81" s="3">
-        <v>72300</v>
+        <v>68500</v>
       </c>
       <c r="E81" s="3">
-        <v>201100</v>
+        <v>190400</v>
       </c>
       <c r="F81" s="3">
-        <v>258600</v>
+        <v>244800</v>
       </c>
       <c r="G81" s="3">
-        <v>181300</v>
+        <v>171600</v>
       </c>
       <c r="H81" s="3">
-        <v>188400</v>
+        <v>178300</v>
       </c>
       <c r="I81" s="3">
-        <v>190800</v>
+        <v>180600</v>
       </c>
       <c r="J81" s="3">
-        <v>173200</v>
+        <v>163900</v>
       </c>
       <c r="K81" s="3">
         <v>163700</v>
@@ -3694,25 +3694,25 @@
         <v>71</v>
       </c>
       <c r="D83" s="3">
-        <v>190800</v>
+        <v>180600</v>
       </c>
       <c r="E83" s="3">
-        <v>169700</v>
+        <v>160700</v>
       </c>
       <c r="F83" s="3">
-        <v>140800</v>
+        <v>133300</v>
       </c>
       <c r="G83" s="3">
-        <v>152800</v>
+        <v>144700</v>
       </c>
       <c r="H83" s="3">
-        <v>106600</v>
+        <v>100900</v>
       </c>
       <c r="I83" s="3">
-        <v>107300</v>
+        <v>101500</v>
       </c>
       <c r="J83" s="3">
-        <v>94000</v>
+        <v>89000</v>
       </c>
       <c r="K83" s="3">
         <v>74300</v>
@@ -3964,25 +3964,25 @@
         <v>77</v>
       </c>
       <c r="D89" s="3">
-        <v>385700</v>
+        <v>365100</v>
       </c>
       <c r="E89" s="3">
-        <v>378800</v>
+        <v>358600</v>
       </c>
       <c r="F89" s="3">
-        <v>372500</v>
+        <v>352600</v>
       </c>
       <c r="G89" s="3">
-        <v>366000</v>
+        <v>346500</v>
       </c>
       <c r="H89" s="3">
-        <v>304000</v>
+        <v>287800</v>
       </c>
       <c r="I89" s="3">
-        <v>336700</v>
+        <v>318700</v>
       </c>
       <c r="J89" s="3">
-        <v>316200</v>
+        <v>299300</v>
       </c>
       <c r="K89" s="3">
         <v>222500</v>
@@ -4028,25 +4028,25 @@
         <v>79</v>
       </c>
       <c r="D91" s="3">
-        <v>-14700</v>
+        <v>-13900</v>
       </c>
       <c r="E91" s="3">
-        <v>-9400</v>
+        <v>-8900</v>
       </c>
       <c r="F91" s="3">
-        <v>-14500</v>
+        <v>-13800</v>
       </c>
       <c r="G91" s="3">
-        <v>-10500</v>
+        <v>-9900</v>
       </c>
       <c r="H91" s="3">
-        <v>-27200</v>
+        <v>-25700</v>
       </c>
       <c r="I91" s="3">
-        <v>-24000</v>
+        <v>-22700</v>
       </c>
       <c r="J91" s="3">
-        <v>-31000</v>
+        <v>-29300</v>
       </c>
       <c r="K91" s="3">
         <v>-19800</v>
@@ -4163,25 +4163,25 @@
         <v>82</v>
       </c>
       <c r="D94" s="3">
-        <v>208900</v>
+        <v>197800</v>
       </c>
       <c r="E94" s="3">
-        <v>-456400</v>
+        <v>-432000</v>
       </c>
       <c r="F94" s="3">
-        <v>17400</v>
+        <v>16400</v>
       </c>
       <c r="G94" s="3">
-        <v>-38900</v>
+        <v>-36900</v>
       </c>
       <c r="H94" s="3">
-        <v>-9900</v>
+        <v>-9400</v>
       </c>
       <c r="I94" s="3">
-        <v>5500</v>
+        <v>5200</v>
       </c>
       <c r="J94" s="3">
-        <v>-227900</v>
+        <v>-215800</v>
       </c>
       <c r="K94" s="3">
         <v>85800</v>
@@ -4227,25 +4227,25 @@
         <v>84</v>
       </c>
       <c r="D96" s="3">
-        <v>-136500</v>
+        <v>-129200</v>
       </c>
       <c r="E96" s="3">
-        <v>-178900</v>
+        <v>-169300</v>
       </c>
       <c r="F96" s="3">
-        <v>-140000</v>
+        <v>-132500</v>
       </c>
       <c r="G96" s="3">
-        <v>-146100</v>
+        <v>-138300</v>
       </c>
       <c r="H96" s="3">
-        <v>-148200</v>
+        <v>-140300</v>
       </c>
       <c r="I96" s="3">
-        <v>-133400</v>
+        <v>-126200</v>
       </c>
       <c r="J96" s="3">
-        <v>-125900</v>
+        <v>-119200</v>
       </c>
       <c r="K96" s="3">
         <v>-96200</v>
@@ -4407,25 +4407,25 @@
         <v>88</v>
       </c>
       <c r="D100" s="3">
-        <v>-292700</v>
+        <v>-277100</v>
       </c>
       <c r="E100" s="3">
-        <v>-205100</v>
+        <v>-194200</v>
       </c>
       <c r="F100" s="3">
-        <v>-110800</v>
+        <v>-104900</v>
       </c>
       <c r="G100" s="3">
-        <v>-142500</v>
+        <v>-134900</v>
       </c>
       <c r="H100" s="3">
-        <v>-175000</v>
+        <v>-165600</v>
       </c>
       <c r="I100" s="3">
-        <v>-89100</v>
+        <v>-84400</v>
       </c>
       <c r="J100" s="3">
-        <v>-114000</v>
+        <v>-107900</v>
       </c>
       <c r="K100" s="3">
         <v>-99900</v>
@@ -4452,22 +4452,22 @@
         <v>89</v>
       </c>
       <c r="D101" s="3">
-        <v>59500</v>
+        <v>56300</v>
       </c>
       <c r="E101" s="3">
-        <v>161100</v>
+        <v>152500</v>
       </c>
       <c r="F101" s="3">
-        <v>68200</v>
+        <v>64600</v>
       </c>
       <c r="G101" s="3">
-        <v>-9100</v>
+        <v>-8600</v>
       </c>
       <c r="H101" s="3">
-        <v>-8000</v>
+        <v>-7500</v>
       </c>
       <c r="I101" s="3">
-        <v>-29400</v>
+        <v>-27900</v>
       </c>
       <c r="J101" s="3">
         <v>-800</v>
@@ -4497,25 +4497,25 @@
         <v>90</v>
       </c>
       <c r="D102" s="3">
-        <v>361400</v>
+        <v>342100</v>
       </c>
       <c r="E102" s="3">
-        <v>-121600</v>
+        <v>-115100</v>
       </c>
       <c r="F102" s="3">
-        <v>347200</v>
+        <v>328700</v>
       </c>
       <c r="G102" s="3">
-        <v>175500</v>
+        <v>166100</v>
       </c>
       <c r="H102" s="3">
-        <v>111200</v>
+        <v>105300</v>
       </c>
       <c r="I102" s="3">
-        <v>223700</v>
+        <v>211700</v>
       </c>
       <c r="J102" s="3">
-        <v>-26500</v>
+        <v>-25100</v>
       </c>
       <c r="K102" s="3">
         <v>210500</v>

--- a/AAII_Financials/Yearly/TMICY_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/TMICY_YR_FIN.xlsx
@@ -726,25 +726,25 @@
         <v>3</v>
       </c>
       <c r="D8" s="3">
-        <v>1586600</v>
+        <v>1765700</v>
       </c>
       <c r="E8" s="3">
-        <v>1427800</v>
+        <v>1588900</v>
       </c>
       <c r="F8" s="3">
-        <v>1214500</v>
+        <v>1351500</v>
       </c>
       <c r="G8" s="3">
-        <v>1110500</v>
+        <v>1235800</v>
       </c>
       <c r="H8" s="3">
-        <v>1053900</v>
+        <v>1172900</v>
       </c>
       <c r="I8" s="3">
-        <v>1023400</v>
+        <v>1138900</v>
       </c>
       <c r="J8" s="3">
-        <v>949400</v>
+        <v>1056600</v>
       </c>
       <c r="K8" s="3">
         <v>876100</v>
@@ -771,25 +771,25 @@
         <v>4</v>
       </c>
       <c r="D9" s="3">
-        <v>406200</v>
+        <v>452000</v>
       </c>
       <c r="E9" s="3">
-        <v>346400</v>
+        <v>385500</v>
       </c>
       <c r="F9" s="3">
-        <v>268100</v>
+        <v>298300</v>
       </c>
       <c r="G9" s="3">
-        <v>243500</v>
+        <v>271000</v>
       </c>
       <c r="H9" s="3">
-        <v>206100</v>
+        <v>229300</v>
       </c>
       <c r="I9" s="3">
-        <v>208800</v>
+        <v>232400</v>
       </c>
       <c r="J9" s="3">
-        <v>179500</v>
+        <v>199800</v>
       </c>
       <c r="K9" s="3">
         <v>153000</v>
@@ -816,25 +816,25 @@
         <v>5</v>
       </c>
       <c r="D10" s="3">
-        <v>1180500</v>
+        <v>1313700</v>
       </c>
       <c r="E10" s="3">
-        <v>1081400</v>
+        <v>1203400</v>
       </c>
       <c r="F10" s="3">
-        <v>946400</v>
+        <v>1053200</v>
       </c>
       <c r="G10" s="3">
-        <v>867000</v>
+        <v>964900</v>
       </c>
       <c r="H10" s="3">
-        <v>847900</v>
+        <v>943600</v>
       </c>
       <c r="I10" s="3">
-        <v>814600</v>
+        <v>906500</v>
       </c>
       <c r="J10" s="3">
-        <v>769900</v>
+        <v>856800</v>
       </c>
       <c r="K10" s="3">
         <v>723100</v>
@@ -880,25 +880,25 @@
         <v>7</v>
       </c>
       <c r="D12" s="3">
-        <v>29700</v>
+        <v>33100</v>
       </c>
       <c r="E12" s="3">
-        <v>34500</v>
+        <v>38400</v>
       </c>
       <c r="F12" s="3">
-        <v>29900</v>
+        <v>33200</v>
       </c>
       <c r="G12" s="3">
-        <v>46800</v>
+        <v>52100</v>
       </c>
       <c r="H12" s="3">
-        <v>52500</v>
+        <v>58500</v>
       </c>
       <c r="I12" s="3">
-        <v>47500</v>
+        <v>52900</v>
       </c>
       <c r="J12" s="3">
-        <v>49700</v>
+        <v>55300</v>
       </c>
       <c r="K12" s="3">
         <v>35000</v>
@@ -970,22 +970,22 @@
         <v>9</v>
       </c>
       <c r="D14" s="3">
-        <v>27600</v>
+        <v>30800</v>
       </c>
       <c r="E14" s="3">
-        <v>-2400</v>
+        <v>-2700</v>
       </c>
       <c r="F14" s="3">
+        <v>1600</v>
+      </c>
+      <c r="G14" s="3">
         <v>1400</v>
       </c>
-      <c r="G14" s="3">
-        <v>1300</v>
-      </c>
       <c r="H14" s="3">
-        <v>400</v>
+        <v>500</v>
       </c>
       <c r="I14" s="3">
-        <v>2200</v>
+        <v>2400</v>
       </c>
       <c r="J14" s="3">
         <v>300</v>
@@ -1076,25 +1076,25 @@
         <v>11</v>
       </c>
       <c r="D17" s="3">
-        <v>1406300</v>
+        <v>1565000</v>
       </c>
       <c r="E17" s="3">
-        <v>1225400</v>
+        <v>1363700</v>
       </c>
       <c r="F17" s="3">
-        <v>937500</v>
+        <v>1043300</v>
       </c>
       <c r="G17" s="3">
-        <v>860000</v>
+        <v>957000</v>
       </c>
       <c r="H17" s="3">
-        <v>813900</v>
+        <v>905800</v>
       </c>
       <c r="I17" s="3">
-        <v>796900</v>
+        <v>886900</v>
       </c>
       <c r="J17" s="3">
-        <v>717200</v>
+        <v>798100</v>
       </c>
       <c r="K17" s="3">
         <v>650400</v>
@@ -1121,25 +1121,25 @@
         <v>12</v>
       </c>
       <c r="D18" s="3">
-        <v>180400</v>
+        <v>200700</v>
       </c>
       <c r="E18" s="3">
-        <v>202400</v>
+        <v>225200</v>
       </c>
       <c r="F18" s="3">
-        <v>277000</v>
+        <v>308200</v>
       </c>
       <c r="G18" s="3">
-        <v>250500</v>
+        <v>278800</v>
       </c>
       <c r="H18" s="3">
-        <v>240000</v>
+        <v>267100</v>
       </c>
       <c r="I18" s="3">
-        <v>226500</v>
+        <v>252000</v>
       </c>
       <c r="J18" s="3">
-        <v>232200</v>
+        <v>258400</v>
       </c>
       <c r="K18" s="3">
         <v>225700</v>
@@ -1185,25 +1185,25 @@
         <v>14</v>
       </c>
       <c r="D20" s="3">
-        <v>23700</v>
+        <v>26300</v>
       </c>
       <c r="E20" s="3">
-        <v>65200</v>
+        <v>72600</v>
       </c>
       <c r="F20" s="3">
-        <v>57200</v>
+        <v>63700</v>
       </c>
       <c r="G20" s="3">
-        <v>3700</v>
+        <v>4200</v>
       </c>
       <c r="H20" s="3">
-        <v>9700</v>
+        <v>10800</v>
       </c>
       <c r="I20" s="3">
-        <v>10800</v>
+        <v>12000</v>
       </c>
       <c r="J20" s="3">
-        <v>4500</v>
+        <v>5000</v>
       </c>
       <c r="K20" s="3">
         <v>11500</v>
@@ -1230,25 +1230,25 @@
         <v>15</v>
       </c>
       <c r="D21" s="3">
-        <v>384400</v>
+        <v>426700</v>
       </c>
       <c r="E21" s="3">
-        <v>428000</v>
+        <v>475300</v>
       </c>
       <c r="F21" s="3">
-        <v>467300</v>
+        <v>519200</v>
       </c>
       <c r="G21" s="3">
-        <v>398700</v>
+        <v>442800</v>
       </c>
       <c r="H21" s="3">
-        <v>350500</v>
+        <v>389400</v>
       </c>
       <c r="I21" s="3">
-        <v>338700</v>
+        <v>376300</v>
       </c>
       <c r="J21" s="3">
-        <v>325600</v>
+        <v>361800</v>
       </c>
       <c r="K21" s="3">
         <v>311200</v>
@@ -1320,25 +1320,25 @@
         <v>17</v>
       </c>
       <c r="D23" s="3">
-        <v>204000</v>
+        <v>227000</v>
       </c>
       <c r="E23" s="3">
-        <v>267300</v>
+        <v>297500</v>
       </c>
       <c r="F23" s="3">
-        <v>334100</v>
+        <v>371800</v>
       </c>
       <c r="G23" s="3">
-        <v>254300</v>
+        <v>283000</v>
       </c>
       <c r="H23" s="3">
-        <v>249700</v>
+        <v>277900</v>
       </c>
       <c r="I23" s="3">
-        <v>237300</v>
+        <v>264000</v>
       </c>
       <c r="J23" s="3">
-        <v>236700</v>
+        <v>263400</v>
       </c>
       <c r="K23" s="3">
         <v>237200</v>
@@ -1365,25 +1365,25 @@
         <v>18</v>
       </c>
       <c r="D24" s="3">
-        <v>135400</v>
+        <v>150700</v>
       </c>
       <c r="E24" s="3">
-        <v>82600</v>
+        <v>91900</v>
       </c>
       <c r="F24" s="3">
-        <v>94100</v>
+        <v>104800</v>
       </c>
       <c r="G24" s="3">
-        <v>86000</v>
+        <v>95700</v>
       </c>
       <c r="H24" s="3">
-        <v>72200</v>
+        <v>80400</v>
       </c>
       <c r="I24" s="3">
-        <v>56700</v>
+        <v>63100</v>
       </c>
       <c r="J24" s="3">
-        <v>72800</v>
+        <v>81000</v>
       </c>
       <c r="K24" s="3">
         <v>73500</v>
@@ -1455,25 +1455,25 @@
         <v>20</v>
       </c>
       <c r="D26" s="3">
-        <v>68600</v>
+        <v>76400</v>
       </c>
       <c r="E26" s="3">
-        <v>184700</v>
+        <v>205600</v>
       </c>
       <c r="F26" s="3">
-        <v>240000</v>
+        <v>267100</v>
       </c>
       <c r="G26" s="3">
-        <v>168300</v>
+        <v>187300</v>
       </c>
       <c r="H26" s="3">
-        <v>177500</v>
+        <v>197500</v>
       </c>
       <c r="I26" s="3">
-        <v>180600</v>
+        <v>200900</v>
       </c>
       <c r="J26" s="3">
-        <v>163900</v>
+        <v>182400</v>
       </c>
       <c r="K26" s="3">
         <v>163700</v>
@@ -1500,25 +1500,25 @@
         <v>21</v>
       </c>
       <c r="D27" s="3">
-        <v>68500</v>
+        <v>76200</v>
       </c>
       <c r="E27" s="3">
-        <v>190400</v>
+        <v>211900</v>
       </c>
       <c r="F27" s="3">
-        <v>244800</v>
+        <v>272400</v>
       </c>
       <c r="G27" s="3">
-        <v>171600</v>
+        <v>191000</v>
       </c>
       <c r="H27" s="3">
-        <v>178300</v>
+        <v>198400</v>
       </c>
       <c r="I27" s="3">
-        <v>180600</v>
+        <v>201000</v>
       </c>
       <c r="J27" s="3">
-        <v>163900</v>
+        <v>182400</v>
       </c>
       <c r="K27" s="3">
         <v>163700</v>
@@ -1725,25 +1725,25 @@
         <v>26</v>
       </c>
       <c r="D32" s="3">
-        <v>-23700</v>
+        <v>-26300</v>
       </c>
       <c r="E32" s="3">
-        <v>-65200</v>
+        <v>-72600</v>
       </c>
       <c r="F32" s="3">
-        <v>-57200</v>
+        <v>-63700</v>
       </c>
       <c r="G32" s="3">
-        <v>-3700</v>
+        <v>-4200</v>
       </c>
       <c r="H32" s="3">
-        <v>-9700</v>
+        <v>-10800</v>
       </c>
       <c r="I32" s="3">
-        <v>-10800</v>
+        <v>-12000</v>
       </c>
       <c r="J32" s="3">
-        <v>-4500</v>
+        <v>-5000</v>
       </c>
       <c r="K32" s="3">
         <v>-11500</v>
@@ -1770,25 +1770,25 @@
         <v>27</v>
       </c>
       <c r="D33" s="3">
-        <v>68500</v>
+        <v>76200</v>
       </c>
       <c r="E33" s="3">
-        <v>190400</v>
+        <v>211900</v>
       </c>
       <c r="F33" s="3">
-        <v>244800</v>
+        <v>272400</v>
       </c>
       <c r="G33" s="3">
-        <v>171600</v>
+        <v>191000</v>
       </c>
       <c r="H33" s="3">
-        <v>178300</v>
+        <v>198400</v>
       </c>
       <c r="I33" s="3">
-        <v>180600</v>
+        <v>201000</v>
       </c>
       <c r="J33" s="3">
-        <v>163900</v>
+        <v>182400</v>
       </c>
       <c r="K33" s="3">
         <v>163700</v>
@@ -1860,25 +1860,25 @@
         <v>29</v>
       </c>
       <c r="D35" s="3">
-        <v>68500</v>
+        <v>76200</v>
       </c>
       <c r="E35" s="3">
-        <v>190400</v>
+        <v>211900</v>
       </c>
       <c r="F35" s="3">
-        <v>244800</v>
+        <v>272400</v>
       </c>
       <c r="G35" s="3">
-        <v>171600</v>
+        <v>191000</v>
       </c>
       <c r="H35" s="3">
-        <v>178300</v>
+        <v>198400</v>
       </c>
       <c r="I35" s="3">
-        <v>180600</v>
+        <v>201000</v>
       </c>
       <c r="J35" s="3">
-        <v>163900</v>
+        <v>182400</v>
       </c>
       <c r="K35" s="3">
         <v>163700</v>
@@ -1993,25 +1993,25 @@
         <v>33</v>
       </c>
       <c r="D41" s="3">
-        <v>1581300</v>
+        <v>1759800</v>
       </c>
       <c r="E41" s="3">
-        <v>1222000</v>
+        <v>1359900</v>
       </c>
       <c r="F41" s="3">
-        <v>1261500</v>
+        <v>1403900</v>
       </c>
       <c r="G41" s="3">
-        <v>993600</v>
+        <v>1105800</v>
       </c>
       <c r="H41" s="3">
-        <v>797400</v>
+        <v>887400</v>
       </c>
       <c r="I41" s="3">
-        <v>743200</v>
+        <v>827100</v>
       </c>
       <c r="J41" s="3">
-        <v>548000</v>
+        <v>609900</v>
       </c>
       <c r="K41" s="3">
         <v>561100</v>
@@ -2038,25 +2038,25 @@
         <v>34</v>
       </c>
       <c r="D42" s="3">
-        <v>326500</v>
+        <v>363300</v>
       </c>
       <c r="E42" s="3">
-        <v>327300</v>
+        <v>364300</v>
       </c>
       <c r="F42" s="3">
-        <v>376900</v>
+        <v>419400</v>
       </c>
       <c r="G42" s="3">
-        <v>360600</v>
+        <v>401300</v>
       </c>
       <c r="H42" s="3">
-        <v>303800</v>
+        <v>338100</v>
       </c>
       <c r="I42" s="3">
-        <v>391000</v>
+        <v>435200</v>
       </c>
       <c r="J42" s="3">
-        <v>424500</v>
+        <v>472400</v>
       </c>
       <c r="K42" s="3">
         <v>333000</v>
@@ -2083,25 +2083,25 @@
         <v>35</v>
       </c>
       <c r="D43" s="3">
-        <v>439700</v>
+        <v>489400</v>
       </c>
       <c r="E43" s="3">
-        <v>403800</v>
+        <v>449400</v>
       </c>
       <c r="F43" s="3">
-        <v>339500</v>
+        <v>377800</v>
       </c>
       <c r="G43" s="3">
-        <v>300000</v>
+        <v>333800</v>
       </c>
       <c r="H43" s="3">
-        <v>286700</v>
+        <v>319100</v>
       </c>
       <c r="I43" s="3">
-        <v>248700</v>
+        <v>276800</v>
       </c>
       <c r="J43" s="3">
-        <v>253800</v>
+        <v>282400</v>
       </c>
       <c r="K43" s="3">
         <v>236100</v>
@@ -2128,25 +2128,25 @@
         <v>36</v>
       </c>
       <c r="D44" s="3">
-        <v>42500</v>
+        <v>47300</v>
       </c>
       <c r="E44" s="3">
-        <v>27100</v>
+        <v>30200</v>
       </c>
       <c r="F44" s="3">
-        <v>23600</v>
+        <v>26300</v>
       </c>
       <c r="G44" s="3">
-        <v>21700</v>
+        <v>24200</v>
       </c>
       <c r="H44" s="3">
-        <v>26200</v>
+        <v>29200</v>
       </c>
       <c r="I44" s="3">
-        <v>46900</v>
+        <v>52200</v>
       </c>
       <c r="J44" s="3">
-        <v>19000</v>
+        <v>21200</v>
       </c>
       <c r="K44" s="3">
         <v>11400</v>
@@ -2173,25 +2173,25 @@
         <v>37</v>
       </c>
       <c r="D45" s="3">
-        <v>91100</v>
+        <v>101300</v>
       </c>
       <c r="E45" s="3">
-        <v>60800</v>
+        <v>67700</v>
       </c>
       <c r="F45" s="3">
-        <v>51300</v>
+        <v>57100</v>
       </c>
       <c r="G45" s="3">
-        <v>38000</v>
+        <v>42300</v>
       </c>
       <c r="H45" s="3">
-        <v>36400</v>
+        <v>40500</v>
       </c>
       <c r="I45" s="3">
-        <v>137000</v>
+        <v>152400</v>
       </c>
       <c r="J45" s="3">
-        <v>137800</v>
+        <v>153400</v>
       </c>
       <c r="K45" s="3">
         <v>153400</v>
@@ -2218,25 +2218,25 @@
         <v>38</v>
       </c>
       <c r="D46" s="3">
-        <v>2481100</v>
+        <v>2761100</v>
       </c>
       <c r="E46" s="3">
-        <v>2041200</v>
+        <v>2271500</v>
       </c>
       <c r="F46" s="3">
-        <v>2052800</v>
+        <v>2284400</v>
       </c>
       <c r="G46" s="3">
-        <v>1714000</v>
+        <v>1907400</v>
       </c>
       <c r="H46" s="3">
-        <v>1450500</v>
+        <v>1614200</v>
       </c>
       <c r="I46" s="3">
-        <v>1440400</v>
+        <v>1603000</v>
       </c>
       <c r="J46" s="3">
-        <v>1383100</v>
+        <v>1539200</v>
       </c>
       <c r="K46" s="3">
         <v>1295000</v>
@@ -2263,25 +2263,25 @@
         <v>39</v>
       </c>
       <c r="D47" s="3">
-        <v>117200</v>
+        <v>130500</v>
       </c>
       <c r="E47" s="3">
-        <v>474900</v>
+        <v>528500</v>
       </c>
       <c r="F47" s="3">
-        <v>169000</v>
+        <v>188100</v>
       </c>
       <c r="G47" s="3">
-        <v>231100</v>
+        <v>257100</v>
       </c>
       <c r="H47" s="3">
-        <v>318900</v>
+        <v>354900</v>
       </c>
       <c r="I47" s="3">
-        <v>285400</v>
+        <v>317600</v>
       </c>
       <c r="J47" s="3">
-        <v>334300</v>
+        <v>372000</v>
       </c>
       <c r="K47" s="3">
         <v>336800</v>
@@ -2308,25 +2308,25 @@
         <v>40</v>
       </c>
       <c r="D48" s="3">
-        <v>41400</v>
+        <v>46100</v>
       </c>
       <c r="E48" s="3">
-        <v>45200</v>
+        <v>50300</v>
       </c>
       <c r="F48" s="3">
-        <v>50600</v>
+        <v>56300</v>
       </c>
       <c r="G48" s="3">
-        <v>50900</v>
+        <v>56600</v>
       </c>
       <c r="H48" s="3">
-        <v>62900</v>
+        <v>70000</v>
       </c>
       <c r="I48" s="3">
-        <v>55900</v>
+        <v>62300</v>
       </c>
       <c r="J48" s="3">
-        <v>52500</v>
+        <v>58400</v>
       </c>
       <c r="K48" s="3">
         <v>43500</v>
@@ -2353,25 +2353,25 @@
         <v>41</v>
       </c>
       <c r="D49" s="3">
-        <v>203400</v>
+        <v>226400</v>
       </c>
       <c r="E49" s="3">
-        <v>155000</v>
+        <v>172500</v>
       </c>
       <c r="F49" s="3">
-        <v>162300</v>
+        <v>180600</v>
       </c>
       <c r="G49" s="3">
-        <v>165300</v>
+        <v>183900</v>
       </c>
       <c r="H49" s="3">
-        <v>230800</v>
+        <v>256900</v>
       </c>
       <c r="I49" s="3">
-        <v>224000</v>
+        <v>249300</v>
       </c>
       <c r="J49" s="3">
-        <v>257100</v>
+        <v>286100</v>
       </c>
       <c r="K49" s="3">
         <v>282400</v>
@@ -2488,25 +2488,25 @@
         <v>44</v>
       </c>
       <c r="D52" s="3">
-        <v>299800</v>
+        <v>333700</v>
       </c>
       <c r="E52" s="3">
-        <v>287400</v>
+        <v>319800</v>
       </c>
       <c r="F52" s="3">
-        <v>247900</v>
+        <v>275800</v>
       </c>
       <c r="G52" s="3">
-        <v>242200</v>
+        <v>269500</v>
       </c>
       <c r="H52" s="3">
-        <v>231800</v>
+        <v>258000</v>
       </c>
       <c r="I52" s="3">
-        <v>202700</v>
+        <v>225600</v>
       </c>
       <c r="J52" s="3">
-        <v>85800</v>
+        <v>95500</v>
       </c>
       <c r="K52" s="3">
         <v>90900</v>
@@ -2578,25 +2578,25 @@
         <v>46</v>
       </c>
       <c r="D54" s="3">
-        <v>3143000</v>
+        <v>3497700</v>
       </c>
       <c r="E54" s="3">
-        <v>3003700</v>
+        <v>3342700</v>
       </c>
       <c r="F54" s="3">
-        <v>2682500</v>
+        <v>2985200</v>
       </c>
       <c r="G54" s="3">
-        <v>2403400</v>
+        <v>2674600</v>
       </c>
       <c r="H54" s="3">
-        <v>2294900</v>
+        <v>2553900</v>
       </c>
       <c r="I54" s="3">
-        <v>2208500</v>
+        <v>2457700</v>
       </c>
       <c r="J54" s="3">
-        <v>2112800</v>
+        <v>2351200</v>
       </c>
       <c r="K54" s="3">
         <v>2048700</v>
@@ -2661,25 +2661,25 @@
         <v>49</v>
       </c>
       <c r="D57" s="3">
-        <v>17400</v>
+        <v>19400</v>
       </c>
       <c r="E57" s="3">
-        <v>13800</v>
+        <v>15400</v>
       </c>
       <c r="F57" s="3">
-        <v>7400</v>
+        <v>8300</v>
       </c>
       <c r="G57" s="3">
-        <v>5900</v>
+        <v>6500</v>
       </c>
       <c r="H57" s="3">
-        <v>7700</v>
+        <v>8500</v>
       </c>
       <c r="I57" s="3">
-        <v>10300</v>
+        <v>11500</v>
       </c>
       <c r="J57" s="3">
-        <v>4700</v>
+        <v>5200</v>
       </c>
       <c r="K57" s="3">
         <v>5900</v>
@@ -2751,25 +2751,25 @@
         <v>51</v>
       </c>
       <c r="D59" s="3">
-        <v>1673800</v>
+        <v>1862700</v>
       </c>
       <c r="E59" s="3">
-        <v>1468200</v>
+        <v>1633900</v>
       </c>
       <c r="F59" s="3">
-        <v>845100</v>
+        <v>940500</v>
       </c>
       <c r="G59" s="3">
-        <v>832900</v>
+        <v>926900</v>
       </c>
       <c r="H59" s="3">
-        <v>755100</v>
+        <v>840300</v>
       </c>
       <c r="I59" s="3">
-        <v>700800</v>
+        <v>779900</v>
       </c>
       <c r="J59" s="3">
-        <v>689300</v>
+        <v>767000</v>
       </c>
       <c r="K59" s="3">
         <v>669300</v>
@@ -2796,25 +2796,25 @@
         <v>52</v>
       </c>
       <c r="D60" s="3">
-        <v>1691200</v>
+        <v>1882000</v>
       </c>
       <c r="E60" s="3">
-        <v>1482100</v>
+        <v>1649300</v>
       </c>
       <c r="F60" s="3">
-        <v>852500</v>
+        <v>948700</v>
       </c>
       <c r="G60" s="3">
-        <v>838800</v>
+        <v>933400</v>
       </c>
       <c r="H60" s="3">
-        <v>762800</v>
+        <v>848900</v>
       </c>
       <c r="I60" s="3">
-        <v>711100</v>
+        <v>791400</v>
       </c>
       <c r="J60" s="3">
-        <v>693900</v>
+        <v>772200</v>
       </c>
       <c r="K60" s="3">
         <v>675200</v>
@@ -2886,25 +2886,25 @@
         <v>54</v>
       </c>
       <c r="D62" s="3">
-        <v>83800</v>
+        <v>93200</v>
       </c>
       <c r="E62" s="3">
-        <v>62700</v>
+        <v>69700</v>
       </c>
       <c r="F62" s="3">
-        <v>417200</v>
+        <v>464300</v>
       </c>
       <c r="G62" s="3">
-        <v>356500</v>
+        <v>396700</v>
       </c>
       <c r="H62" s="3">
-        <v>336400</v>
+        <v>374300</v>
       </c>
       <c r="I62" s="3">
-        <v>303800</v>
+        <v>338100</v>
       </c>
       <c r="J62" s="3">
-        <v>289100</v>
+        <v>321700</v>
       </c>
       <c r="K62" s="3">
         <v>268100</v>
@@ -3066,25 +3066,25 @@
         <v>57</v>
       </c>
       <c r="D66" s="3">
-        <v>1775200</v>
+        <v>1975500</v>
       </c>
       <c r="E66" s="3">
-        <v>1544800</v>
+        <v>1719200</v>
       </c>
       <c r="F66" s="3">
-        <v>1274800</v>
+        <v>1418700</v>
       </c>
       <c r="G66" s="3">
-        <v>1200500</v>
+        <v>1336000</v>
       </c>
       <c r="H66" s="3">
-        <v>1100100</v>
+        <v>1224300</v>
       </c>
       <c r="I66" s="3">
-        <v>1015400</v>
+        <v>1130000</v>
       </c>
       <c r="J66" s="3">
-        <v>983100</v>
+        <v>1094000</v>
       </c>
       <c r="K66" s="3">
         <v>943300</v>
@@ -3310,25 +3310,25 @@
         <v>63</v>
       </c>
       <c r="D72" s="3">
-        <v>1012400</v>
+        <v>1126700</v>
       </c>
       <c r="E72" s="3">
-        <v>1075200</v>
+        <v>1196500</v>
       </c>
       <c r="F72" s="3">
-        <v>1129700</v>
+        <v>1257200</v>
       </c>
       <c r="G72" s="3">
-        <v>1018600</v>
+        <v>1133500</v>
       </c>
       <c r="H72" s="3">
-        <v>988200</v>
+        <v>1099700</v>
       </c>
       <c r="I72" s="3">
-        <v>954600</v>
+        <v>1062300</v>
       </c>
       <c r="J72" s="3">
-        <v>908900</v>
+        <v>1011400</v>
       </c>
       <c r="K72" s="3">
         <v>903400</v>
@@ -3490,25 +3490,25 @@
         <v>67</v>
       </c>
       <c r="D76" s="3">
-        <v>1367800</v>
+        <v>1522200</v>
       </c>
       <c r="E76" s="3">
-        <v>1458900</v>
+        <v>1623500</v>
       </c>
       <c r="F76" s="3">
-        <v>1407700</v>
+        <v>1566600</v>
       </c>
       <c r="G76" s="3">
-        <v>1202800</v>
+        <v>1338600</v>
       </c>
       <c r="H76" s="3">
-        <v>1194800</v>
+        <v>1329600</v>
       </c>
       <c r="I76" s="3">
-        <v>1193100</v>
+        <v>1327700</v>
       </c>
       <c r="J76" s="3">
-        <v>1129700</v>
+        <v>1257200</v>
       </c>
       <c r="K76" s="3">
         <v>1105300</v>
@@ -3630,25 +3630,25 @@
         <v>27</v>
       </c>
       <c r="D81" s="3">
-        <v>68500</v>
+        <v>76200</v>
       </c>
       <c r="E81" s="3">
-        <v>190400</v>
+        <v>211900</v>
       </c>
       <c r="F81" s="3">
-        <v>244800</v>
+        <v>272400</v>
       </c>
       <c r="G81" s="3">
-        <v>171600</v>
+        <v>191000</v>
       </c>
       <c r="H81" s="3">
-        <v>178300</v>
+        <v>198400</v>
       </c>
       <c r="I81" s="3">
-        <v>180600</v>
+        <v>201000</v>
       </c>
       <c r="J81" s="3">
-        <v>163900</v>
+        <v>182400</v>
       </c>
       <c r="K81" s="3">
         <v>163700</v>
@@ -3694,25 +3694,25 @@
         <v>71</v>
       </c>
       <c r="D83" s="3">
-        <v>180600</v>
+        <v>201000</v>
       </c>
       <c r="E83" s="3">
-        <v>160700</v>
+        <v>178800</v>
       </c>
       <c r="F83" s="3">
-        <v>133300</v>
+        <v>148300</v>
       </c>
       <c r="G83" s="3">
-        <v>144700</v>
+        <v>161000</v>
       </c>
       <c r="H83" s="3">
-        <v>100900</v>
+        <v>112300</v>
       </c>
       <c r="I83" s="3">
-        <v>101500</v>
+        <v>113000</v>
       </c>
       <c r="J83" s="3">
-        <v>89000</v>
+        <v>99000</v>
       </c>
       <c r="K83" s="3">
         <v>74300</v>
@@ -3964,25 +3964,25 @@
         <v>77</v>
       </c>
       <c r="D89" s="3">
-        <v>365100</v>
+        <v>406300</v>
       </c>
       <c r="E89" s="3">
-        <v>358600</v>
+        <v>399100</v>
       </c>
       <c r="F89" s="3">
-        <v>352600</v>
+        <v>392400</v>
       </c>
       <c r="G89" s="3">
-        <v>346500</v>
+        <v>385600</v>
       </c>
       <c r="H89" s="3">
-        <v>287800</v>
+        <v>320300</v>
       </c>
       <c r="I89" s="3">
-        <v>318700</v>
+        <v>354700</v>
       </c>
       <c r="J89" s="3">
-        <v>299300</v>
+        <v>333100</v>
       </c>
       <c r="K89" s="3">
         <v>222500</v>
@@ -4028,25 +4028,25 @@
         <v>79</v>
       </c>
       <c r="D91" s="3">
-        <v>-13900</v>
+        <v>-15500</v>
       </c>
       <c r="E91" s="3">
-        <v>-8900</v>
+        <v>-10000</v>
       </c>
       <c r="F91" s="3">
-        <v>-13800</v>
+        <v>-15300</v>
       </c>
       <c r="G91" s="3">
-        <v>-9900</v>
+        <v>-11100</v>
       </c>
       <c r="H91" s="3">
-        <v>-25700</v>
+        <v>-28600</v>
       </c>
       <c r="I91" s="3">
-        <v>-22700</v>
+        <v>-25300</v>
       </c>
       <c r="J91" s="3">
-        <v>-29300</v>
+        <v>-32700</v>
       </c>
       <c r="K91" s="3">
         <v>-19800</v>
@@ -4163,25 +4163,25 @@
         <v>82</v>
       </c>
       <c r="D94" s="3">
-        <v>197800</v>
+        <v>220100</v>
       </c>
       <c r="E94" s="3">
-        <v>-432000</v>
+        <v>-480800</v>
       </c>
       <c r="F94" s="3">
-        <v>16400</v>
+        <v>18300</v>
       </c>
       <c r="G94" s="3">
-        <v>-36900</v>
+        <v>-41000</v>
       </c>
       <c r="H94" s="3">
-        <v>-9400</v>
+        <v>-10400</v>
       </c>
       <c r="I94" s="3">
-        <v>5200</v>
+        <v>5800</v>
       </c>
       <c r="J94" s="3">
-        <v>-215800</v>
+        <v>-240100</v>
       </c>
       <c r="K94" s="3">
         <v>85800</v>
@@ -4227,25 +4227,25 @@
         <v>84</v>
       </c>
       <c r="D96" s="3">
-        <v>-129200</v>
+        <v>-143800</v>
       </c>
       <c r="E96" s="3">
-        <v>-169300</v>
+        <v>-188400</v>
       </c>
       <c r="F96" s="3">
-        <v>-132500</v>
+        <v>-147400</v>
       </c>
       <c r="G96" s="3">
-        <v>-138300</v>
+        <v>-153900</v>
       </c>
       <c r="H96" s="3">
-        <v>-140300</v>
+        <v>-156100</v>
       </c>
       <c r="I96" s="3">
-        <v>-126200</v>
+        <v>-140500</v>
       </c>
       <c r="J96" s="3">
-        <v>-119200</v>
+        <v>-132600</v>
       </c>
       <c r="K96" s="3">
         <v>-96200</v>
@@ -4407,25 +4407,25 @@
         <v>88</v>
       </c>
       <c r="D100" s="3">
-        <v>-277100</v>
+        <v>-308400</v>
       </c>
       <c r="E100" s="3">
-        <v>-194200</v>
+        <v>-216100</v>
       </c>
       <c r="F100" s="3">
-        <v>-104900</v>
+        <v>-116800</v>
       </c>
       <c r="G100" s="3">
-        <v>-134900</v>
+        <v>-150100</v>
       </c>
       <c r="H100" s="3">
-        <v>-165600</v>
+        <v>-184300</v>
       </c>
       <c r="I100" s="3">
-        <v>-84400</v>
+        <v>-93900</v>
       </c>
       <c r="J100" s="3">
-        <v>-107900</v>
+        <v>-120000</v>
       </c>
       <c r="K100" s="3">
         <v>-99900</v>
@@ -4452,25 +4452,25 @@
         <v>89</v>
       </c>
       <c r="D101" s="3">
-        <v>56300</v>
+        <v>62700</v>
       </c>
       <c r="E101" s="3">
-        <v>152500</v>
+        <v>169700</v>
       </c>
       <c r="F101" s="3">
-        <v>64600</v>
+        <v>71900</v>
       </c>
       <c r="G101" s="3">
-        <v>-8600</v>
+        <v>-9600</v>
       </c>
       <c r="H101" s="3">
-        <v>-7500</v>
+        <v>-8400</v>
       </c>
       <c r="I101" s="3">
-        <v>-27900</v>
+        <v>-31000</v>
       </c>
       <c r="J101" s="3">
-        <v>-800</v>
+        <v>-900</v>
       </c>
       <c r="K101" s="3">
         <v>2100</v>
@@ -4497,25 +4497,25 @@
         <v>90</v>
       </c>
       <c r="D102" s="3">
-        <v>342100</v>
+        <v>380700</v>
       </c>
       <c r="E102" s="3">
-        <v>-115100</v>
+        <v>-128100</v>
       </c>
       <c r="F102" s="3">
-        <v>328700</v>
+        <v>365800</v>
       </c>
       <c r="G102" s="3">
-        <v>166100</v>
+        <v>184800</v>
       </c>
       <c r="H102" s="3">
-        <v>105300</v>
+        <v>117100</v>
       </c>
       <c r="I102" s="3">
-        <v>211700</v>
+        <v>235600</v>
       </c>
       <c r="J102" s="3">
-        <v>-25100</v>
+        <v>-27900</v>
       </c>
       <c r="K102" s="3">
         <v>210500</v>

--- a/AAII_Financials/Yearly/TMICY_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/TMICY_YR_FIN.xlsx
@@ -726,25 +726,25 @@
         <v>3</v>
       </c>
       <c r="D8" s="3">
-        <v>1765700</v>
+        <v>1764200</v>
       </c>
       <c r="E8" s="3">
-        <v>1588900</v>
+        <v>1697000</v>
       </c>
       <c r="F8" s="3">
-        <v>1351500</v>
+        <v>1653300</v>
       </c>
       <c r="G8" s="3">
-        <v>1235800</v>
+        <v>1686500</v>
       </c>
       <c r="H8" s="3">
-        <v>1172900</v>
+        <v>1520100</v>
       </c>
       <c r="I8" s="3">
-        <v>1138900</v>
+        <v>1462100</v>
       </c>
       <c r="J8" s="3">
-        <v>1056600</v>
+        <v>1321200</v>
       </c>
       <c r="K8" s="3">
         <v>876100</v>
@@ -771,25 +771,25 @@
         <v>4</v>
       </c>
       <c r="D9" s="3">
-        <v>452000</v>
+        <v>451600</v>
       </c>
       <c r="E9" s="3">
-        <v>385500</v>
+        <v>411800</v>
       </c>
       <c r="F9" s="3">
+        <v>364900</v>
+      </c>
+      <c r="G9" s="3">
+        <v>369800</v>
+      </c>
+      <c r="H9" s="3">
+        <v>297200</v>
+      </c>
+      <c r="I9" s="3">
         <v>298300</v>
       </c>
-      <c r="G9" s="3">
-        <v>271000</v>
-      </c>
-      <c r="H9" s="3">
-        <v>229300</v>
-      </c>
-      <c r="I9" s="3">
-        <v>232400</v>
-      </c>
       <c r="J9" s="3">
-        <v>199800</v>
+        <v>249800</v>
       </c>
       <c r="K9" s="3">
         <v>153000</v>
@@ -816,25 +816,25 @@
         <v>5</v>
       </c>
       <c r="D10" s="3">
-        <v>1313700</v>
+        <v>1312600</v>
       </c>
       <c r="E10" s="3">
-        <v>1203400</v>
+        <v>1285300</v>
       </c>
       <c r="F10" s="3">
-        <v>1053200</v>
+        <v>1288400</v>
       </c>
       <c r="G10" s="3">
-        <v>964900</v>
+        <v>1316700</v>
       </c>
       <c r="H10" s="3">
-        <v>943600</v>
+        <v>1222900</v>
       </c>
       <c r="I10" s="3">
-        <v>906500</v>
+        <v>1163800</v>
       </c>
       <c r="J10" s="3">
-        <v>856800</v>
+        <v>1071400</v>
       </c>
       <c r="K10" s="3">
         <v>723100</v>
@@ -883,22 +883,22 @@
         <v>33100</v>
       </c>
       <c r="E12" s="3">
-        <v>38400</v>
+        <v>41000</v>
       </c>
       <c r="F12" s="3">
-        <v>33200</v>
+        <v>40600</v>
       </c>
       <c r="G12" s="3">
-        <v>52100</v>
+        <v>71100</v>
       </c>
       <c r="H12" s="3">
-        <v>58500</v>
+        <v>75800</v>
       </c>
       <c r="I12" s="3">
-        <v>52900</v>
+        <v>67900</v>
       </c>
       <c r="J12" s="3">
-        <v>55300</v>
+        <v>69100</v>
       </c>
       <c r="K12" s="3">
         <v>35000</v>
@@ -970,25 +970,25 @@
         <v>9</v>
       </c>
       <c r="D14" s="3">
-        <v>30800</v>
+        <v>15300</v>
       </c>
       <c r="E14" s="3">
-        <v>-2700</v>
+        <v>-58400</v>
       </c>
       <c r="F14" s="3">
-        <v>1600</v>
+        <v>-79800</v>
       </c>
       <c r="G14" s="3">
+        <v>-9400</v>
+      </c>
+      <c r="H14" s="3">
         <v>1400</v>
       </c>
-      <c r="H14" s="3">
-        <v>500</v>
-      </c>
       <c r="I14" s="3">
-        <v>2400</v>
+        <v>4200</v>
       </c>
       <c r="J14" s="3">
-        <v>300</v>
+        <v>-1100</v>
       </c>
       <c r="K14" s="3">
         <v>2500</v>
@@ -1015,25 +1015,25 @@
         <v>10</v>
       </c>
       <c r="D15" s="3">
-        <v>0</v>
+        <v>200900</v>
       </c>
       <c r="E15" s="3">
-        <v>0</v>
+        <v>191000</v>
       </c>
       <c r="F15" s="3">
-        <v>0</v>
+        <v>181500</v>
       </c>
       <c r="G15" s="3">
-        <v>0</v>
+        <v>219700</v>
       </c>
       <c r="H15" s="3">
-        <v>0</v>
+        <v>145500</v>
       </c>
       <c r="I15" s="3">
-        <v>0</v>
+        <v>145000</v>
       </c>
       <c r="J15" s="3">
-        <v>0</v>
+        <v>123900</v>
       </c>
       <c r="K15" s="3">
         <v>0</v>
@@ -1076,25 +1076,25 @@
         <v>11</v>
       </c>
       <c r="D17" s="3">
-        <v>1565000</v>
+        <v>1533000</v>
       </c>
       <c r="E17" s="3">
-        <v>1363700</v>
+        <v>1459400</v>
       </c>
       <c r="F17" s="3">
-        <v>1043300</v>
+        <v>1274300</v>
       </c>
       <c r="G17" s="3">
-        <v>957000</v>
+        <v>1304100</v>
       </c>
       <c r="H17" s="3">
-        <v>905800</v>
+        <v>1173300</v>
       </c>
       <c r="I17" s="3">
-        <v>886900</v>
+        <v>1135400</v>
       </c>
       <c r="J17" s="3">
-        <v>798100</v>
+        <v>997600</v>
       </c>
       <c r="K17" s="3">
         <v>650400</v>
@@ -1121,25 +1121,25 @@
         <v>12</v>
       </c>
       <c r="D18" s="3">
-        <v>200700</v>
+        <v>231300</v>
       </c>
       <c r="E18" s="3">
-        <v>225200</v>
+        <v>237700</v>
       </c>
       <c r="F18" s="3">
-        <v>308200</v>
+        <v>379000</v>
       </c>
       <c r="G18" s="3">
-        <v>278800</v>
+        <v>382400</v>
       </c>
       <c r="H18" s="3">
-        <v>267100</v>
+        <v>346800</v>
       </c>
       <c r="I18" s="3">
-        <v>252000</v>
+        <v>326600</v>
       </c>
       <c r="J18" s="3">
-        <v>258400</v>
+        <v>323500</v>
       </c>
       <c r="K18" s="3">
         <v>225700</v>
@@ -1185,25 +1185,25 @@
         <v>14</v>
       </c>
       <c r="D20" s="3">
-        <v>26300</v>
+        <v>30600</v>
       </c>
       <c r="E20" s="3">
-        <v>72600</v>
+        <v>-5700</v>
       </c>
       <c r="F20" s="3">
-        <v>63700</v>
+        <v>7500</v>
       </c>
       <c r="G20" s="3">
-        <v>4200</v>
+        <v>12700</v>
       </c>
       <c r="H20" s="3">
-        <v>10800</v>
+        <v>900</v>
       </c>
       <c r="I20" s="3">
-        <v>12000</v>
+        <v>-2700</v>
       </c>
       <c r="J20" s="3">
-        <v>5000</v>
+        <v>6000</v>
       </c>
       <c r="K20" s="3">
         <v>11500</v>
@@ -1230,25 +1230,25 @@
         <v>15</v>
       </c>
       <c r="D21" s="3">
-        <v>426700</v>
+        <v>401500</v>
       </c>
       <c r="E21" s="3">
-        <v>475300</v>
+        <v>434400</v>
       </c>
       <c r="F21" s="3">
-        <v>519200</v>
+        <v>553000</v>
       </c>
       <c r="G21" s="3">
-        <v>442800</v>
+        <v>589400</v>
       </c>
       <c r="H21" s="3">
-        <v>389400</v>
+        <v>491400</v>
       </c>
       <c r="I21" s="3">
-        <v>376300</v>
+        <v>474400</v>
       </c>
       <c r="J21" s="3">
-        <v>361800</v>
+        <v>441400</v>
       </c>
       <c r="K21" s="3">
         <v>311200</v>
@@ -1320,25 +1320,25 @@
         <v>17</v>
       </c>
       <c r="D23" s="3">
-        <v>227000</v>
+        <v>226800</v>
       </c>
       <c r="E23" s="3">
-        <v>297500</v>
+        <v>317700</v>
       </c>
       <c r="F23" s="3">
-        <v>371800</v>
+        <v>454900</v>
       </c>
       <c r="G23" s="3">
-        <v>283000</v>
+        <v>386200</v>
       </c>
       <c r="H23" s="3">
-        <v>277900</v>
+        <v>360100</v>
       </c>
       <c r="I23" s="3">
-        <v>264000</v>
+        <v>339000</v>
       </c>
       <c r="J23" s="3">
-        <v>263400</v>
+        <v>329300</v>
       </c>
       <c r="K23" s="3">
         <v>237200</v>
@@ -1365,25 +1365,25 @@
         <v>18</v>
       </c>
       <c r="D24" s="3">
-        <v>150700</v>
+        <v>150500</v>
       </c>
       <c r="E24" s="3">
-        <v>91900</v>
+        <v>98200</v>
       </c>
       <c r="F24" s="3">
-        <v>104800</v>
+        <v>128200</v>
       </c>
       <c r="G24" s="3">
-        <v>95700</v>
+        <v>130600</v>
       </c>
       <c r="H24" s="3">
-        <v>80400</v>
+        <v>104200</v>
       </c>
       <c r="I24" s="3">
-        <v>63100</v>
+        <v>81000</v>
       </c>
       <c r="J24" s="3">
-        <v>81000</v>
+        <v>101200</v>
       </c>
       <c r="K24" s="3">
         <v>73500</v>
@@ -1455,25 +1455,25 @@
         <v>20</v>
       </c>
       <c r="D26" s="3">
-        <v>76400</v>
+        <v>76300</v>
       </c>
       <c r="E26" s="3">
-        <v>205600</v>
+        <v>219600</v>
       </c>
       <c r="F26" s="3">
-        <v>267100</v>
+        <v>326700</v>
       </c>
       <c r="G26" s="3">
-        <v>187300</v>
+        <v>255600</v>
       </c>
       <c r="H26" s="3">
-        <v>197500</v>
+        <v>256000</v>
       </c>
       <c r="I26" s="3">
-        <v>200900</v>
+        <v>257900</v>
       </c>
       <c r="J26" s="3">
-        <v>182400</v>
+        <v>228100</v>
       </c>
       <c r="K26" s="3">
         <v>163700</v>
@@ -1500,25 +1500,25 @@
         <v>21</v>
       </c>
       <c r="D27" s="3">
-        <v>76200</v>
+        <v>76100</v>
       </c>
       <c r="E27" s="3">
-        <v>211900</v>
+        <v>226300</v>
       </c>
       <c r="F27" s="3">
-        <v>272400</v>
+        <v>333200</v>
       </c>
       <c r="G27" s="3">
-        <v>191000</v>
+        <v>260700</v>
       </c>
       <c r="H27" s="3">
-        <v>198400</v>
+        <v>257100</v>
       </c>
       <c r="I27" s="3">
-        <v>201000</v>
+        <v>258100</v>
       </c>
       <c r="J27" s="3">
-        <v>182400</v>
+        <v>228100</v>
       </c>
       <c r="K27" s="3">
         <v>163700</v>
@@ -1725,25 +1725,25 @@
         <v>26</v>
       </c>
       <c r="D32" s="3">
-        <v>-26300</v>
+        <v>-30600</v>
       </c>
       <c r="E32" s="3">
-        <v>-72600</v>
+        <v>5700</v>
       </c>
       <c r="F32" s="3">
-        <v>-63700</v>
+        <v>-7500</v>
       </c>
       <c r="G32" s="3">
-        <v>-4200</v>
+        <v>-12700</v>
       </c>
       <c r="H32" s="3">
-        <v>-10800</v>
+        <v>-900</v>
       </c>
       <c r="I32" s="3">
-        <v>-12000</v>
+        <v>2700</v>
       </c>
       <c r="J32" s="3">
-        <v>-5000</v>
+        <v>-6000</v>
       </c>
       <c r="K32" s="3">
         <v>-11500</v>
@@ -1770,25 +1770,25 @@
         <v>27</v>
       </c>
       <c r="D33" s="3">
-        <v>76200</v>
+        <v>76100</v>
       </c>
       <c r="E33" s="3">
-        <v>211900</v>
+        <v>226300</v>
       </c>
       <c r="F33" s="3">
-        <v>272400</v>
+        <v>333200</v>
       </c>
       <c r="G33" s="3">
-        <v>191000</v>
+        <v>260700</v>
       </c>
       <c r="H33" s="3">
-        <v>198400</v>
+        <v>257100</v>
       </c>
       <c r="I33" s="3">
-        <v>201000</v>
+        <v>258100</v>
       </c>
       <c r="J33" s="3">
-        <v>182400</v>
+        <v>228100</v>
       </c>
       <c r="K33" s="3">
         <v>163700</v>
@@ -1860,25 +1860,25 @@
         <v>29</v>
       </c>
       <c r="D35" s="3">
-        <v>76200</v>
+        <v>76100</v>
       </c>
       <c r="E35" s="3">
-        <v>211900</v>
+        <v>226300</v>
       </c>
       <c r="F35" s="3">
-        <v>272400</v>
+        <v>333200</v>
       </c>
       <c r="G35" s="3">
-        <v>191000</v>
+        <v>260700</v>
       </c>
       <c r="H35" s="3">
-        <v>198400</v>
+        <v>257100</v>
       </c>
       <c r="I35" s="3">
-        <v>201000</v>
+        <v>258100</v>
       </c>
       <c r="J35" s="3">
-        <v>182400</v>
+        <v>228100</v>
       </c>
       <c r="K35" s="3">
         <v>163700</v>
@@ -1993,25 +1993,25 @@
         <v>33</v>
       </c>
       <c r="D41" s="3">
-        <v>1759800</v>
+        <v>1758300</v>
       </c>
       <c r="E41" s="3">
-        <v>1359900</v>
+        <v>1452500</v>
       </c>
       <c r="F41" s="3">
-        <v>1403900</v>
+        <v>1717300</v>
       </c>
       <c r="G41" s="3">
-        <v>1105800</v>
+        <v>1509000</v>
       </c>
       <c r="H41" s="3">
-        <v>887400</v>
+        <v>1150000</v>
       </c>
       <c r="I41" s="3">
-        <v>827100</v>
+        <v>1061800</v>
       </c>
       <c r="J41" s="3">
-        <v>609900</v>
+        <v>762600</v>
       </c>
       <c r="K41" s="3">
         <v>561100</v>
@@ -2038,25 +2038,25 @@
         <v>34</v>
       </c>
       <c r="D42" s="3">
-        <v>363300</v>
+        <v>363000</v>
       </c>
       <c r="E42" s="3">
-        <v>364300</v>
+        <v>389100</v>
       </c>
       <c r="F42" s="3">
-        <v>419400</v>
+        <v>513100</v>
       </c>
       <c r="G42" s="3">
-        <v>401300</v>
+        <v>547700</v>
       </c>
       <c r="H42" s="3">
-        <v>338100</v>
+        <v>438200</v>
       </c>
       <c r="I42" s="3">
-        <v>435200</v>
+        <v>558600</v>
       </c>
       <c r="J42" s="3">
-        <v>472400</v>
+        <v>590700</v>
       </c>
       <c r="K42" s="3">
         <v>333000</v>
@@ -2083,25 +2083,25 @@
         <v>35</v>
       </c>
       <c r="D43" s="3">
-        <v>489400</v>
+        <v>489000</v>
       </c>
       <c r="E43" s="3">
-        <v>449400</v>
+        <v>480000</v>
       </c>
       <c r="F43" s="3">
-        <v>377800</v>
+        <v>462100</v>
       </c>
       <c r="G43" s="3">
-        <v>333800</v>
+        <v>455600</v>
       </c>
       <c r="H43" s="3">
-        <v>319100</v>
+        <v>413500</v>
       </c>
       <c r="I43" s="3">
-        <v>276800</v>
+        <v>355300</v>
       </c>
       <c r="J43" s="3">
-        <v>282400</v>
+        <v>353200</v>
       </c>
       <c r="K43" s="3">
         <v>236100</v>
@@ -2131,22 +2131,22 @@
         <v>47300</v>
       </c>
       <c r="E44" s="3">
-        <v>30200</v>
+        <v>32300</v>
       </c>
       <c r="F44" s="3">
-        <v>26300</v>
+        <v>32100</v>
       </c>
       <c r="G44" s="3">
-        <v>24200</v>
+        <v>33000</v>
       </c>
       <c r="H44" s="3">
-        <v>29200</v>
+        <v>37800</v>
       </c>
       <c r="I44" s="3">
-        <v>52200</v>
+        <v>33500</v>
       </c>
       <c r="J44" s="3">
-        <v>21200</v>
+        <v>26500</v>
       </c>
       <c r="K44" s="3">
         <v>11400</v>
@@ -2173,25 +2173,25 @@
         <v>37</v>
       </c>
       <c r="D45" s="3">
-        <v>101300</v>
+        <v>101200</v>
       </c>
       <c r="E45" s="3">
-        <v>67700</v>
+        <v>72300</v>
       </c>
       <c r="F45" s="3">
-        <v>57100</v>
+        <v>69800</v>
       </c>
       <c r="G45" s="3">
-        <v>42300</v>
+        <v>57700</v>
       </c>
       <c r="H45" s="3">
-        <v>40500</v>
+        <v>52500</v>
       </c>
       <c r="I45" s="3">
-        <v>152400</v>
+        <v>48600</v>
       </c>
       <c r="J45" s="3">
-        <v>153400</v>
+        <v>51400</v>
       </c>
       <c r="K45" s="3">
         <v>153400</v>
@@ -2218,25 +2218,25 @@
         <v>38</v>
       </c>
       <c r="D46" s="3">
-        <v>2761100</v>
+        <v>2758800</v>
       </c>
       <c r="E46" s="3">
-        <v>2271500</v>
+        <v>2426100</v>
       </c>
       <c r="F46" s="3">
-        <v>2284400</v>
+        <v>2794500</v>
       </c>
       <c r="G46" s="3">
-        <v>1907400</v>
+        <v>2603000</v>
       </c>
       <c r="H46" s="3">
-        <v>1614200</v>
+        <v>2092000</v>
       </c>
       <c r="I46" s="3">
-        <v>1603000</v>
+        <v>2204900</v>
       </c>
       <c r="J46" s="3">
-        <v>1539200</v>
+        <v>1924700</v>
       </c>
       <c r="K46" s="3">
         <v>1295000</v>
@@ -2263,25 +2263,25 @@
         <v>39</v>
       </c>
       <c r="D47" s="3">
-        <v>130500</v>
+        <v>148900</v>
       </c>
       <c r="E47" s="3">
-        <v>528500</v>
+        <v>586700</v>
       </c>
       <c r="F47" s="3">
-        <v>188100</v>
+        <v>250500</v>
       </c>
       <c r="G47" s="3">
-        <v>257100</v>
+        <v>367700</v>
       </c>
       <c r="H47" s="3">
-        <v>354900</v>
+        <v>476900</v>
       </c>
       <c r="I47" s="3">
-        <v>317600</v>
+        <v>422400</v>
       </c>
       <c r="J47" s="3">
-        <v>372000</v>
+        <v>479300</v>
       </c>
       <c r="K47" s="3">
         <v>336800</v>
@@ -2308,25 +2308,25 @@
         <v>40</v>
       </c>
       <c r="D48" s="3">
-        <v>46100</v>
+        <v>46000</v>
       </c>
       <c r="E48" s="3">
-        <v>50300</v>
+        <v>53800</v>
       </c>
       <c r="F48" s="3">
-        <v>56300</v>
+        <v>68900</v>
       </c>
       <c r="G48" s="3">
-        <v>56600</v>
+        <v>77200</v>
       </c>
       <c r="H48" s="3">
-        <v>70000</v>
+        <v>90700</v>
       </c>
       <c r="I48" s="3">
-        <v>62300</v>
+        <v>79900</v>
       </c>
       <c r="J48" s="3">
-        <v>58400</v>
+        <v>73000</v>
       </c>
       <c r="K48" s="3">
         <v>43500</v>
@@ -2353,25 +2353,25 @@
         <v>41</v>
       </c>
       <c r="D49" s="3">
-        <v>226400</v>
+        <v>226200</v>
       </c>
       <c r="E49" s="3">
-        <v>172500</v>
+        <v>184200</v>
       </c>
       <c r="F49" s="3">
-        <v>180600</v>
+        <v>220900</v>
       </c>
       <c r="G49" s="3">
-        <v>183900</v>
+        <v>251000</v>
       </c>
       <c r="H49" s="3">
-        <v>256900</v>
+        <v>332900</v>
       </c>
       <c r="I49" s="3">
-        <v>249300</v>
+        <v>320000</v>
       </c>
       <c r="J49" s="3">
-        <v>286100</v>
+        <v>357700</v>
       </c>
       <c r="K49" s="3">
         <v>282400</v>
@@ -2488,25 +2488,25 @@
         <v>44</v>
       </c>
       <c r="D52" s="3">
-        <v>333700</v>
+        <v>0</v>
       </c>
       <c r="E52" s="3">
-        <v>319800</v>
+        <v>0</v>
       </c>
       <c r="F52" s="3">
-        <v>275800</v>
+        <v>0</v>
       </c>
       <c r="G52" s="3">
-        <v>269500</v>
+        <v>0</v>
       </c>
       <c r="H52" s="3">
-        <v>258000</v>
+        <v>0</v>
       </c>
       <c r="I52" s="3">
-        <v>225600</v>
+        <v>0</v>
       </c>
       <c r="J52" s="3">
-        <v>95500</v>
+        <v>0</v>
       </c>
       <c r="K52" s="3">
         <v>90900</v>
@@ -2578,25 +2578,25 @@
         <v>46</v>
       </c>
       <c r="D54" s="3">
-        <v>3497700</v>
+        <v>3494800</v>
       </c>
       <c r="E54" s="3">
-        <v>3342700</v>
+        <v>3570100</v>
       </c>
       <c r="F54" s="3">
-        <v>2985200</v>
+        <v>3651800</v>
       </c>
       <c r="G54" s="3">
-        <v>2674600</v>
+        <v>3650000</v>
       </c>
       <c r="H54" s="3">
-        <v>2553900</v>
+        <v>3309900</v>
       </c>
       <c r="I54" s="3">
-        <v>2457700</v>
+        <v>3155800</v>
       </c>
       <c r="J54" s="3">
-        <v>2351200</v>
+        <v>2940100</v>
       </c>
       <c r="K54" s="3">
         <v>2048700</v>
@@ -2661,25 +2661,25 @@
         <v>49</v>
       </c>
       <c r="D57" s="3">
-        <v>19400</v>
+        <v>19300</v>
       </c>
       <c r="E57" s="3">
-        <v>15400</v>
+        <v>16400</v>
       </c>
       <c r="F57" s="3">
-        <v>8300</v>
+        <v>10100</v>
       </c>
       <c r="G57" s="3">
+        <v>8900</v>
+      </c>
+      <c r="H57" s="3">
+        <v>11100</v>
+      </c>
+      <c r="I57" s="3">
+        <v>14800</v>
+      </c>
+      <c r="J57" s="3">
         <v>6500</v>
-      </c>
-      <c r="H57" s="3">
-        <v>8500</v>
-      </c>
-      <c r="I57" s="3">
-        <v>11500</v>
-      </c>
-      <c r="J57" s="3">
-        <v>5200</v>
       </c>
       <c r="K57" s="3">
         <v>5900</v>
@@ -2751,25 +2751,25 @@
         <v>51</v>
       </c>
       <c r="D59" s="3">
-        <v>1862700</v>
+        <v>1702500</v>
       </c>
       <c r="E59" s="3">
-        <v>1633900</v>
+        <v>1604900</v>
       </c>
       <c r="F59" s="3">
-        <v>940500</v>
+        <v>1021700</v>
       </c>
       <c r="G59" s="3">
-        <v>926900</v>
+        <v>1149600</v>
       </c>
       <c r="H59" s="3">
-        <v>840300</v>
+        <v>1005500</v>
       </c>
       <c r="I59" s="3">
-        <v>779900</v>
+        <v>934500</v>
       </c>
       <c r="J59" s="3">
-        <v>767000</v>
+        <v>888600</v>
       </c>
       <c r="K59" s="3">
         <v>669300</v>
@@ -2796,25 +2796,25 @@
         <v>52</v>
       </c>
       <c r="D60" s="3">
-        <v>1882000</v>
+        <v>1880500</v>
       </c>
       <c r="E60" s="3">
-        <v>1649300</v>
+        <v>1761500</v>
       </c>
       <c r="F60" s="3">
-        <v>948700</v>
+        <v>1160600</v>
       </c>
       <c r="G60" s="3">
-        <v>933400</v>
+        <v>1273800</v>
       </c>
       <c r="H60" s="3">
-        <v>848900</v>
+        <v>1100100</v>
       </c>
       <c r="I60" s="3">
-        <v>791400</v>
+        <v>1017100</v>
       </c>
       <c r="J60" s="3">
-        <v>772200</v>
+        <v>965600</v>
       </c>
       <c r="K60" s="3">
         <v>675200</v>
@@ -2886,25 +2886,25 @@
         <v>54</v>
       </c>
       <c r="D62" s="3">
-        <v>93200</v>
+        <v>35900</v>
       </c>
       <c r="E62" s="3">
-        <v>69700</v>
+        <v>18300</v>
       </c>
       <c r="F62" s="3">
-        <v>464300</v>
+        <v>499300</v>
       </c>
       <c r="G62" s="3">
-        <v>396700</v>
+        <v>470900</v>
       </c>
       <c r="H62" s="3">
-        <v>374300</v>
+        <v>428100</v>
       </c>
       <c r="I62" s="3">
-        <v>338100</v>
+        <v>380100</v>
       </c>
       <c r="J62" s="3">
-        <v>321700</v>
+        <v>358800</v>
       </c>
       <c r="K62" s="3">
         <v>268100</v>
@@ -3066,25 +3066,25 @@
         <v>57</v>
       </c>
       <c r="D66" s="3">
-        <v>1975500</v>
+        <v>1973600</v>
       </c>
       <c r="E66" s="3">
-        <v>1719200</v>
+        <v>1836000</v>
       </c>
       <c r="F66" s="3">
-        <v>1418700</v>
+        <v>1728600</v>
       </c>
       <c r="G66" s="3">
-        <v>1336000</v>
+        <v>1815200</v>
       </c>
       <c r="H66" s="3">
-        <v>1224300</v>
+        <v>1585300</v>
       </c>
       <c r="I66" s="3">
-        <v>1130000</v>
+        <v>1450700</v>
       </c>
       <c r="J66" s="3">
-        <v>1094000</v>
+        <v>1368000</v>
       </c>
       <c r="K66" s="3">
         <v>943300</v>
@@ -3310,25 +3310,25 @@
         <v>63</v>
       </c>
       <c r="D72" s="3">
-        <v>1126700</v>
+        <v>1108800</v>
       </c>
       <c r="E72" s="3">
-        <v>1196500</v>
+        <v>1263600</v>
       </c>
       <c r="F72" s="3">
-        <v>1257200</v>
+        <v>1524300</v>
       </c>
       <c r="G72" s="3">
-        <v>1133500</v>
+        <v>1535100</v>
       </c>
       <c r="H72" s="3">
-        <v>1099700</v>
+        <v>1415100</v>
       </c>
       <c r="I72" s="3">
-        <v>1062300</v>
+        <v>1354400</v>
       </c>
       <c r="J72" s="3">
-        <v>1011400</v>
+        <v>1250000</v>
       </c>
       <c r="K72" s="3">
         <v>903400</v>
@@ -3490,25 +3490,25 @@
         <v>67</v>
       </c>
       <c r="D76" s="3">
-        <v>1522200</v>
+        <v>1520900</v>
       </c>
       <c r="E76" s="3">
-        <v>1623500</v>
+        <v>1733900</v>
       </c>
       <c r="F76" s="3">
-        <v>1566600</v>
+        <v>1916300</v>
       </c>
       <c r="G76" s="3">
-        <v>1338600</v>
+        <v>1826700</v>
       </c>
       <c r="H76" s="3">
-        <v>1329600</v>
+        <v>1723200</v>
       </c>
       <c r="I76" s="3">
-        <v>1327700</v>
+        <v>1704500</v>
       </c>
       <c r="J76" s="3">
-        <v>1257200</v>
+        <v>1572100</v>
       </c>
       <c r="K76" s="3">
         <v>1105300</v>
@@ -3630,25 +3630,25 @@
         <v>27</v>
       </c>
       <c r="D81" s="3">
-        <v>76200</v>
+        <v>76100</v>
       </c>
       <c r="E81" s="3">
-        <v>211900</v>
+        <v>226300</v>
       </c>
       <c r="F81" s="3">
-        <v>272400</v>
+        <v>333200</v>
       </c>
       <c r="G81" s="3">
-        <v>191000</v>
+        <v>260700</v>
       </c>
       <c r="H81" s="3">
-        <v>198400</v>
+        <v>257100</v>
       </c>
       <c r="I81" s="3">
-        <v>201000</v>
+        <v>258100</v>
       </c>
       <c r="J81" s="3">
-        <v>182400</v>
+        <v>228100</v>
       </c>
       <c r="K81" s="3">
         <v>163700</v>
@@ -3694,25 +3694,25 @@
         <v>71</v>
       </c>
       <c r="D83" s="3">
-        <v>201000</v>
+        <v>188500</v>
       </c>
       <c r="E83" s="3">
-        <v>178800</v>
+        <v>180400</v>
       </c>
       <c r="F83" s="3">
-        <v>148300</v>
+        <v>165400</v>
       </c>
       <c r="G83" s="3">
-        <v>161000</v>
+        <v>169500</v>
       </c>
       <c r="H83" s="3">
-        <v>112300</v>
+        <v>104700</v>
       </c>
       <c r="I83" s="3">
-        <v>113000</v>
+        <v>104600</v>
       </c>
       <c r="J83" s="3">
-        <v>99000</v>
+        <v>85600</v>
       </c>
       <c r="K83" s="3">
         <v>74300</v>
@@ -3964,25 +3964,25 @@
         <v>77</v>
       </c>
       <c r="D89" s="3">
-        <v>406300</v>
+        <v>406000</v>
       </c>
       <c r="E89" s="3">
-        <v>399100</v>
+        <v>431500</v>
       </c>
       <c r="F89" s="3">
-        <v>392400</v>
+        <v>480000</v>
       </c>
       <c r="G89" s="3">
-        <v>385600</v>
+        <v>526200</v>
       </c>
       <c r="H89" s="3">
-        <v>320300</v>
+        <v>415100</v>
       </c>
       <c r="I89" s="3">
-        <v>354700</v>
+        <v>455400</v>
       </c>
       <c r="J89" s="3">
-        <v>333100</v>
+        <v>416500</v>
       </c>
       <c r="K89" s="3">
         <v>222500</v>
@@ -4031,22 +4031,22 @@
         <v>-15500</v>
       </c>
       <c r="E91" s="3">
-        <v>-10000</v>
+        <v>-10600</v>
       </c>
       <c r="F91" s="3">
-        <v>-15300</v>
+        <v>-18700</v>
       </c>
       <c r="G91" s="3">
-        <v>-11100</v>
+        <v>-15100</v>
       </c>
       <c r="H91" s="3">
-        <v>-28600</v>
+        <v>-37100</v>
       </c>
       <c r="I91" s="3">
-        <v>-25300</v>
+        <v>-32400</v>
       </c>
       <c r="J91" s="3">
-        <v>-32700</v>
+        <v>-40800</v>
       </c>
       <c r="K91" s="3">
         <v>-19800</v>
@@ -4163,25 +4163,25 @@
         <v>82</v>
       </c>
       <c r="D94" s="3">
-        <v>220100</v>
+        <v>219900</v>
       </c>
       <c r="E94" s="3">
-        <v>-480800</v>
+        <v>-513500</v>
       </c>
       <c r="F94" s="3">
-        <v>18300</v>
+        <v>22400</v>
       </c>
       <c r="G94" s="3">
-        <v>-41000</v>
+        <v>-56000</v>
       </c>
       <c r="H94" s="3">
-        <v>-10400</v>
+        <v>-13500</v>
       </c>
       <c r="I94" s="3">
-        <v>5800</v>
+        <v>7500</v>
       </c>
       <c r="J94" s="3">
-        <v>-240100</v>
+        <v>-300200</v>
       </c>
       <c r="K94" s="3">
         <v>85800</v>
@@ -4227,25 +4227,25 @@
         <v>84</v>
       </c>
       <c r="D96" s="3">
-        <v>-143800</v>
+        <v>0</v>
       </c>
       <c r="E96" s="3">
-        <v>-188400</v>
+        <v>0</v>
       </c>
       <c r="F96" s="3">
-        <v>-147400</v>
+        <v>0</v>
       </c>
       <c r="G96" s="3">
-        <v>-153900</v>
+        <v>0</v>
       </c>
       <c r="H96" s="3">
-        <v>-156100</v>
+        <v>0</v>
       </c>
       <c r="I96" s="3">
-        <v>-140500</v>
+        <v>0</v>
       </c>
       <c r="J96" s="3">
-        <v>-132600</v>
+        <v>0</v>
       </c>
       <c r="K96" s="3">
         <v>-96200</v>
@@ -4407,25 +4407,25 @@
         <v>88</v>
       </c>
       <c r="D100" s="3">
-        <v>-308400</v>
+        <v>-308100</v>
       </c>
       <c r="E100" s="3">
-        <v>-216100</v>
+        <v>-230800</v>
       </c>
       <c r="F100" s="3">
-        <v>-116800</v>
+        <v>-142800</v>
       </c>
       <c r="G100" s="3">
+        <v>-204900</v>
+      </c>
+      <c r="H100" s="3">
+        <v>-238900</v>
+      </c>
+      <c r="I100" s="3">
+        <v>-120500</v>
+      </c>
+      <c r="J100" s="3">
         <v>-150100</v>
-      </c>
-      <c r="H100" s="3">
-        <v>-184300</v>
-      </c>
-      <c r="I100" s="3">
-        <v>-93900</v>
-      </c>
-      <c r="J100" s="3">
-        <v>-120000</v>
       </c>
       <c r="K100" s="3">
         <v>-99900</v>
@@ -4452,25 +4452,25 @@
         <v>89</v>
       </c>
       <c r="D101" s="3">
-        <v>62700</v>
+        <v>62600</v>
       </c>
       <c r="E101" s="3">
-        <v>169700</v>
+        <v>181300</v>
       </c>
       <c r="F101" s="3">
-        <v>71900</v>
+        <v>87900</v>
       </c>
       <c r="G101" s="3">
-        <v>-9600</v>
+        <v>-13100</v>
       </c>
       <c r="H101" s="3">
-        <v>-8400</v>
+        <v>-10900</v>
       </c>
       <c r="I101" s="3">
-        <v>-31000</v>
+        <v>-39800</v>
       </c>
       <c r="J101" s="3">
-        <v>-900</v>
+        <v>-1100</v>
       </c>
       <c r="K101" s="3">
         <v>2100</v>
@@ -4497,25 +4497,25 @@
         <v>90</v>
       </c>
       <c r="D102" s="3">
-        <v>380700</v>
+        <v>380400</v>
       </c>
       <c r="E102" s="3">
-        <v>-128100</v>
+        <v>-131500</v>
       </c>
       <c r="F102" s="3">
-        <v>365800</v>
+        <v>447400</v>
       </c>
       <c r="G102" s="3">
-        <v>184800</v>
+        <v>252300</v>
       </c>
       <c r="H102" s="3">
-        <v>117100</v>
+        <v>151800</v>
       </c>
       <c r="I102" s="3">
-        <v>235600</v>
+        <v>302500</v>
       </c>
       <c r="J102" s="3">
-        <v>-27900</v>
+        <v>-34900</v>
       </c>
       <c r="K102" s="3">
         <v>210500</v>

--- a/AAII_Financials/Yearly/TMICY_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/TMICY_YR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="98" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="100" uniqueCount="92">
   <si>
     <t>TMICY</t>
   </si>
@@ -656,207 +656,219 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:Q102"/>
+  <dimension ref="A5:R102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="8.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:18" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E7" s="2">
         <v>45291</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>44926</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>44561</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>44196</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>43830</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>43465</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>43100</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>42735</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>42369</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>42004</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>41639</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>41274</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>40908</v>
       </c>
-      <c r="Q7" s="2"/>
-    </row>
-    <row r="8" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R7" s="2"/>
+    </row>
+    <row r="8" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>1734100</v>
+      </c>
+      <c r="E8" s="3">
         <v>1764200</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>1697000</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>1653300</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>1686500</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>1520100</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>1462100</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>1321200</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>876100</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>881400</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>1015000</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>1040900</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>853000</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>855000</v>
       </c>
-      <c r="Q8" s="3"/>
-    </row>
-    <row r="9" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R8" s="3"/>
+    </row>
+    <row r="9" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>413300</v>
+      </c>
+      <c r="E9" s="3">
         <v>451600</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>411800</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>364900</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>369800</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>297200</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>298300</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>249800</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>153000</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>150800</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>180000</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>186200</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>159200</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>158700</v>
       </c>
-      <c r="Q9" s="3"/>
-    </row>
-    <row r="10" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R9" s="3"/>
+    </row>
+    <row r="10" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>1320800</v>
+      </c>
+      <c r="E10" s="3">
         <v>1312600</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>1285300</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>1288400</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>1316700</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>1222900</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>1163800</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>1071400</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>723100</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>730600</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>835000</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>854700</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>693800</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>696300</v>
       </c>
-      <c r="Q10" s="3"/>
-    </row>
-    <row r="11" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R10" s="3"/>
+    </row>
+    <row r="11" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -874,53 +886,57 @@
       <c r="O11" s="3"/>
       <c r="P11" s="3"/>
       <c r="Q11" s="3"/>
-    </row>
-    <row r="12" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R11" s="3"/>
+    </row>
+    <row r="12" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="D12" s="3">
+      <c r="D12" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="E12" s="3">
         <v>33100</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>41000</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>40600</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>71100</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>75800</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>67900</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>69100</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>35000</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>26800</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>25800</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>40200</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>34400</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>30800</v>
       </c>
-      <c r="Q12" s="3"/>
-    </row>
-    <row r="13" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R12" s="3"/>
+    </row>
+    <row r="13" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>8</v>
       </c>
@@ -963,81 +979,87 @@
       <c r="P13" s="3">
         <v>0</v>
       </c>
-      <c r="Q13" s="3"/>
-    </row>
-    <row r="14" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="Q13" s="3">
+        <v>0</v>
+      </c>
+      <c r="R13" s="3"/>
+    </row>
+    <row r="14" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>9</v>
       </c>
       <c r="D14" s="3">
+        <v>-18900</v>
+      </c>
+      <c r="E14" s="3">
         <v>15300</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>-58400</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>-79800</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>-9400</v>
       </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
         <v>1400</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>4200</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>-1100</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>2500</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>5300</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>2000</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>8200</v>
       </c>
-      <c r="O14" s="3">
+      <c r="P14" s="3">
         <v>-31300</v>
       </c>
-      <c r="P14" s="3">
+      <c r="Q14" s="3">
         <v>-42100</v>
       </c>
-      <c r="Q14" s="3"/>
-    </row>
-    <row r="15" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R14" s="3"/>
+    </row>
+    <row r="15" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D15" s="3">
+        <v>184000</v>
+      </c>
+      <c r="E15" s="3">
         <v>200900</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>191000</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>181500</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>219700</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>145500</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>145000</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>123900</v>
       </c>
-      <c r="K15" s="3">
-        <v>0</v>
-      </c>
       <c r="L15" s="3">
         <v>0</v>
       </c>
@@ -1053,9 +1075,12 @@
       <c r="P15" s="3">
         <v>0</v>
       </c>
-      <c r="Q15" s="3"/>
-    </row>
-    <row r="16" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="Q15" s="3">
+        <v>0</v>
+      </c>
+      <c r="R15" s="3"/>
+    </row>
+    <row r="16" spans="1:18" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1070,98 +1095,105 @@
       <c r="O16" s="3"/>
       <c r="P16" s="3"/>
       <c r="Q16" s="3"/>
-    </row>
-    <row r="17" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R16" s="3"/>
+    </row>
+    <row r="17" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D17" s="3">
+        <v>1428100</v>
+      </c>
+      <c r="E17" s="3">
         <v>1533000</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>1459400</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>1274300</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>1304100</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>1173300</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>1135400</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>997600</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>650400</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>667100</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>720500</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>766100</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>618000</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>579000</v>
       </c>
-      <c r="Q17" s="3"/>
-    </row>
-    <row r="18" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R17" s="3"/>
+    </row>
+    <row r="18" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D18" s="3">
+        <v>306000</v>
+      </c>
+      <c r="E18" s="3">
         <v>231300</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>237700</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>379000</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>382400</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>346800</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>326600</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>323500</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>225700</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>214300</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>294500</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>274800</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>235000</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>276000</v>
       </c>
-      <c r="Q18" s="3"/>
-    </row>
-    <row r="19" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R18" s="3"/>
+    </row>
+    <row r="19" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>13</v>
       </c>
@@ -1179,118 +1211,125 @@
       <c r="O19" s="3"/>
       <c r="P19" s="3"/>
       <c r="Q19" s="3"/>
-    </row>
-    <row r="20" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R19" s="3"/>
+    </row>
+    <row r="20" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>14</v>
       </c>
       <c r="D20" s="3">
+        <v>-12000</v>
+      </c>
+      <c r="E20" s="3">
         <v>30600</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>-5700</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>7500</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>12700</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>900</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>-2700</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>6000</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>11500</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>27000</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>23100</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>32800</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>-13100</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>-22100</v>
       </c>
-      <c r="Q20" s="3"/>
-    </row>
-    <row r="21" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R20" s="3"/>
+    </row>
+    <row r="21" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D21" s="3">
+        <v>502000</v>
+      </c>
+      <c r="E21" s="3">
         <v>401500</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>434400</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>553000</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>589400</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>491400</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>474400</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>441400</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>311200</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>297700</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>384800</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>377100</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>290200</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>319000</v>
       </c>
-      <c r="Q21" s="3"/>
-    </row>
-    <row r="22" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R21" s="3"/>
+    </row>
+    <row r="22" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D22" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="E22" s="3">
+      <c r="E22" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="F22" s="3">
         <v>300</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>100</v>
-      </c>
-      <c r="G22" s="3" t="s">
-        <v>91</v>
       </c>
       <c r="H22" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="I22" s="3">
-        <v>0</v>
+      <c r="I22" s="3" t="s">
+        <v>91</v>
       </c>
       <c r="J22" s="3">
         <v>0</v>
@@ -1302,110 +1341,119 @@
         <v>0</v>
       </c>
       <c r="M22" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="N22" s="3">
         <v>100</v>
       </c>
       <c r="O22" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="P22" s="3">
         <v>0</v>
       </c>
-      <c r="Q22" s="3"/>
-    </row>
-    <row r="23" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q22" s="3">
+        <v>0</v>
+      </c>
+      <c r="R22" s="3"/>
+    </row>
+    <row r="23" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D23" s="3">
+        <v>353500</v>
+      </c>
+      <c r="E23" s="3">
         <v>226800</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>317700</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>454900</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>386200</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>360100</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>339000</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>329300</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>237200</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>241300</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>317400</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>307600</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>221800</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>253900</v>
       </c>
-      <c r="Q23" s="3"/>
-    </row>
-    <row r="24" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R23" s="3"/>
+    </row>
+    <row r="24" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D24" s="3">
+        <v>133900</v>
+      </c>
+      <c r="E24" s="3">
         <v>150500</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>98200</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>128200</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>130600</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>104200</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>81000</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>101200</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>73500</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>89300</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>120900</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>119300</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>99600</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>100000</v>
       </c>
-      <c r="Q24" s="3"/>
-    </row>
-    <row r="25" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R24" s="3"/>
+    </row>
+    <row r="25" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>19</v>
       </c>
@@ -1448,99 +1496,108 @@
       <c r="P25" s="3">
         <v>0</v>
       </c>
-      <c r="Q25" s="3"/>
-    </row>
-    <row r="26" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q25" s="3">
+        <v>0</v>
+      </c>
+      <c r="R25" s="3"/>
+    </row>
+    <row r="26" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>20</v>
       </c>
       <c r="D26" s="3">
+        <v>219600</v>
+      </c>
+      <c r="E26" s="3">
         <v>76300</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>219600</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>326700</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>255600</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>256000</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>257900</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>228100</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>163700</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>152000</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>196500</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>188300</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>122200</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>153900</v>
       </c>
-      <c r="Q26" s="3"/>
-    </row>
-    <row r="27" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R26" s="3"/>
+    </row>
+    <row r="27" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D27" s="3">
+        <v>218500</v>
+      </c>
+      <c r="E27" s="3">
         <v>76100</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>226300</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>333200</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>260700</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>257100</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>258100</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>228100</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>163700</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>152000</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>196500</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>188300</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>122200</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>153800</v>
       </c>
-      <c r="Q27" s="3"/>
-    </row>
-    <row r="28" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R27" s="3"/>
+    </row>
+    <row r="28" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>22</v>
       </c>
@@ -1583,9 +1640,12 @@
       <c r="P28" s="3">
         <v>0</v>
       </c>
-      <c r="Q28" s="3"/>
-    </row>
-    <row r="29" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q28" s="3">
+        <v>0</v>
+      </c>
+      <c r="R28" s="3"/>
+    </row>
+    <row r="29" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>23</v>
       </c>
@@ -1628,9 +1688,12 @@
       <c r="P29" s="3">
         <v>0</v>
       </c>
-      <c r="Q29" s="3"/>
-    </row>
-    <row r="30" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q29" s="3">
+        <v>0</v>
+      </c>
+      <c r="R29" s="3"/>
+    </row>
+    <row r="30" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>24</v>
       </c>
@@ -1673,9 +1736,12 @@
       <c r="P30" s="3">
         <v>0</v>
       </c>
-      <c r="Q30" s="3"/>
-    </row>
-    <row r="31" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q30" s="3">
+        <v>0</v>
+      </c>
+      <c r="R30" s="3"/>
+    </row>
+    <row r="31" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>25</v>
       </c>
@@ -1718,99 +1784,108 @@
       <c r="P31" s="3">
         <v>0</v>
       </c>
-      <c r="Q31" s="3"/>
-    </row>
-    <row r="32" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q31" s="3">
+        <v>0</v>
+      </c>
+      <c r="R31" s="3"/>
+    </row>
+    <row r="32" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>26</v>
       </c>
       <c r="D32" s="3">
+        <v>12000</v>
+      </c>
+      <c r="E32" s="3">
         <v>-30600</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>5700</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>-7500</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>-12700</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>-900</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>2700</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>-6000</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-11500</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-27000</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-23100</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-32800</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>13100</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>22100</v>
       </c>
-      <c r="Q32" s="3"/>
-    </row>
-    <row r="33" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R32" s="3"/>
+    </row>
+    <row r="33" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D33" s="3">
+        <v>218500</v>
+      </c>
+      <c r="E33" s="3">
         <v>76100</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>226300</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>333200</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>260700</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>257100</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>258100</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>228100</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>163700</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>152000</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>196500</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>188300</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>122200</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>153800</v>
       </c>
-      <c r="Q33" s="3"/>
-    </row>
-    <row r="34" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R33" s="3"/>
+    </row>
+    <row r="34" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>28</v>
       </c>
@@ -1853,104 +1928,113 @@
       <c r="P34" s="3">
         <v>0</v>
       </c>
-      <c r="Q34" s="3"/>
-    </row>
-    <row r="35" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q34" s="3">
+        <v>0</v>
+      </c>
+      <c r="R34" s="3"/>
+    </row>
+    <row r="35" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>29</v>
       </c>
       <c r="D35" s="3">
+        <v>218500</v>
+      </c>
+      <c r="E35" s="3">
         <v>76100</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>226300</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>333200</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>260700</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>257100</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>258100</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>228100</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>163700</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>152000</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>196500</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>188300</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>122200</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>153800</v>
       </c>
-      <c r="Q35" s="3"/>
-    </row>
-    <row r="37" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R35" s="3"/>
+    </row>
+    <row r="37" spans="2:18" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="38" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E38" s="2">
         <v>45291</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>44926</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>44561</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>44196</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>43830</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>43465</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>43100</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>42735</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>42369</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>42004</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>41639</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>41274</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>40908</v>
       </c>
-      <c r="Q38" s="2"/>
-    </row>
-    <row r="39" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R38" s="2"/>
+    </row>
+    <row r="39" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>31</v>
       </c>
@@ -1968,8 +2052,9 @@
       <c r="O39" s="3"/>
       <c r="P39" s="3"/>
       <c r="Q39" s="3"/>
-    </row>
-    <row r="40" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R39" s="3"/>
+    </row>
+    <row r="40" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>32</v>
       </c>
@@ -1987,413 +2072,441 @@
       <c r="O40" s="3"/>
       <c r="P40" s="3"/>
       <c r="Q40" s="3"/>
-    </row>
-    <row r="41" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R40" s="3"/>
+    </row>
+    <row r="41" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>33</v>
       </c>
       <c r="D41" s="3">
+        <v>1081600</v>
+      </c>
+      <c r="E41" s="3">
         <v>1758300</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>1452500</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>1717300</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>1509000</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>1150000</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>1061800</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>762600</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>561100</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>523500</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>556000</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>765300</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>497500</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>637600</v>
       </c>
-      <c r="Q41" s="3"/>
-    </row>
-    <row r="42" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R41" s="3"/>
+    </row>
+    <row r="42" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D42" s="3">
+        <v>259800</v>
+      </c>
+      <c r="E42" s="3">
         <v>363000</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>389100</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>513100</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>547700</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>438200</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>558600</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>590700</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>333000</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>509900</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>654800</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>585800</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>582800</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>334700</v>
       </c>
-      <c r="Q42" s="3"/>
-    </row>
-    <row r="43" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R42" s="3"/>
+    </row>
+    <row r="43" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D43" s="3">
+        <v>474000</v>
+      </c>
+      <c r="E43" s="3">
         <v>489000</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>480000</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>462100</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>455600</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>413500</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>355300</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>353200</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>236100</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>212500</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>229700</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>233800</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>189900</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>185900</v>
       </c>
-      <c r="Q43" s="3"/>
-    </row>
-    <row r="44" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R43" s="3"/>
+    </row>
+    <row r="44" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D44" s="3">
+        <v>53800</v>
+      </c>
+      <c r="E44" s="3">
         <v>47300</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>32300</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>32100</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>33000</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>37800</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>33500</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>26500</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>11400</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>5700</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>4600</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>3900</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>3400</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>3800</v>
       </c>
-      <c r="Q44" s="3"/>
-    </row>
-    <row r="45" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R44" s="3"/>
+    </row>
+    <row r="45" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D45" s="3">
+        <v>88700</v>
+      </c>
+      <c r="E45" s="3">
         <v>101200</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>72300</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>69800</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>57700</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>52500</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>48600</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>51400</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>153400</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>176900</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>174100</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>185300</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>174100</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>179300</v>
       </c>
-      <c r="Q45" s="3"/>
-    </row>
-    <row r="46" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R45" s="3"/>
+    </row>
+    <row r="46" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D46" s="3">
+        <v>1958000</v>
+      </c>
+      <c r="E46" s="3">
         <v>2758800</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>2426100</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>2794500</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>2603000</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>2092000</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>2204900</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>1924700</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>1295000</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>1428500</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>1619300</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>1774100</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>1447700</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>1341300</v>
       </c>
-      <c r="Q46" s="3"/>
-    </row>
-    <row r="47" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R46" s="3"/>
+    </row>
+    <row r="47" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D47" s="3">
+        <v>36600</v>
+      </c>
+      <c r="E47" s="3">
         <v>148900</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>586700</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>250500</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>367700</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>476900</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>422400</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>479300</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>336800</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>445300</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>608300</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>491400</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>322500</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>208300</v>
       </c>
-      <c r="Q47" s="3"/>
-    </row>
-    <row r="48" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R47" s="3"/>
+    </row>
+    <row r="48" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D48" s="3">
+        <v>35300</v>
+      </c>
+      <c r="E48" s="3">
         <v>46000</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>53800</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>68900</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>77200</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>90700</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>79900</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>73000</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>43500</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>41000</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>43600</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>44000</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>40300</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>45700</v>
       </c>
-      <c r="Q48" s="3"/>
-    </row>
-    <row r="49" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R48" s="3"/>
+    </row>
+    <row r="49" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D49" s="3">
+        <v>199700</v>
+      </c>
+      <c r="E49" s="3">
         <v>226200</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>184200</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>220900</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>251000</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>332900</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>320000</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>357700</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>282400</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>58200</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>83100</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>88000</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>71500</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>84400</v>
       </c>
-      <c r="Q49" s="3"/>
-    </row>
-    <row r="50" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R49" s="3"/>
+    </row>
+    <row r="50" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>42</v>
       </c>
@@ -2436,9 +2549,12 @@
       <c r="P50" s="3">
         <v>0</v>
       </c>
-      <c r="Q50" s="3"/>
-    </row>
-    <row r="51" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q50" s="3">
+        <v>0</v>
+      </c>
+      <c r="R50" s="3"/>
+    </row>
+    <row r="51" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>43</v>
       </c>
@@ -2481,14 +2597,17 @@
       <c r="P51" s="3">
         <v>0</v>
       </c>
-      <c r="Q51" s="3"/>
-    </row>
-    <row r="52" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q51" s="3">
+        <v>0</v>
+      </c>
+      <c r="R51" s="3"/>
+    </row>
+    <row r="52" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>44</v>
       </c>
       <c r="D52" s="3">
-        <v>0</v>
+        <v>13700</v>
       </c>
       <c r="E52" s="3">
         <v>0</v>
@@ -2509,26 +2628,29 @@
         <v>0</v>
       </c>
       <c r="K52" s="3">
+        <v>0</v>
+      </c>
+      <c r="L52" s="3">
         <v>90900</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>86700</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>112000</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>115400</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>108700</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>109900</v>
       </c>
-      <c r="Q52" s="3"/>
-    </row>
-    <row r="53" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R52" s="3"/>
+    </row>
+    <row r="53" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>45</v>
       </c>
@@ -2571,54 +2693,60 @@
       <c r="P53" s="3">
         <v>0</v>
       </c>
-      <c r="Q53" s="3"/>
-    </row>
-    <row r="54" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q53" s="3">
+        <v>0</v>
+      </c>
+      <c r="R53" s="3"/>
+    </row>
+    <row r="54" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>46</v>
       </c>
       <c r="D54" s="3">
+        <v>2546200</v>
+      </c>
+      <c r="E54" s="3">
         <v>3494800</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>3570100</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>3651800</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>3650000</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>3309900</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>3155800</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>2940100</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>2048700</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>2059800</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>2466300</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>2512900</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>1990800</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>1789600</v>
       </c>
-      <c r="Q54" s="3"/>
-    </row>
-    <row r="55" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R54" s="3"/>
+    </row>
+    <row r="55" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>47</v>
       </c>
@@ -2636,8 +2764,9 @@
       <c r="O55" s="3"/>
       <c r="P55" s="3"/>
       <c r="Q55" s="3"/>
-    </row>
-    <row r="56" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R55" s="3"/>
+    </row>
+    <row r="56" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>48</v>
       </c>
@@ -2655,53 +2784,57 @@
       <c r="O56" s="3"/>
       <c r="P56" s="3"/>
       <c r="Q56" s="3"/>
-    </row>
-    <row r="57" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R56" s="3"/>
+    </row>
+    <row r="57" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>49</v>
       </c>
       <c r="D57" s="3">
+        <v>23100</v>
+      </c>
+      <c r="E57" s="3">
         <v>19300</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>16400</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>10100</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>8900</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>11100</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>14800</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>6500</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>5900</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>4000</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>5900</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>4700</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>6600</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>7900</v>
       </c>
-      <c r="Q57" s="3"/>
-    </row>
-    <row r="58" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R57" s="3"/>
+    </row>
+    <row r="58" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>50</v>
       </c>
@@ -2744,99 +2877,108 @@
       <c r="P58" s="3">
         <v>0</v>
       </c>
-      <c r="Q58" s="3"/>
-    </row>
-    <row r="59" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q58" s="3">
+        <v>0</v>
+      </c>
+      <c r="R58" s="3"/>
+    </row>
+    <row r="59" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D59" s="3">
+        <v>1558000</v>
+      </c>
+      <c r="E59" s="3">
         <v>1702500</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>1604900</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>1021700</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>1149600</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>1005500</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>934500</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>888600</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>669300</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>666300</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>811500</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>832000</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>702800</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>625500</v>
       </c>
-      <c r="Q59" s="3"/>
-    </row>
-    <row r="60" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R59" s="3"/>
+    </row>
+    <row r="60" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D60" s="3">
+        <v>1700000</v>
+      </c>
+      <c r="E60" s="3">
         <v>1880500</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>1761500</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>1160600</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>1273800</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>1100100</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>1017100</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>965600</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>675200</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>670300</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>817400</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>836700</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>709400</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>633300</v>
       </c>
-      <c r="Q60" s="3"/>
-    </row>
-    <row r="61" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R60" s="3"/>
+    </row>
+    <row r="61" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>53</v>
       </c>
@@ -2879,54 +3021,60 @@
       <c r="P61" s="3">
         <v>0</v>
       </c>
-      <c r="Q61" s="3"/>
-    </row>
-    <row r="62" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q61" s="3">
+        <v>0</v>
+      </c>
+      <c r="R61" s="3"/>
+    </row>
+    <row r="62" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D62" s="3">
+        <v>37700</v>
+      </c>
+      <c r="E62" s="3">
         <v>35900</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>18300</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>499300</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>470900</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>428100</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>380100</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>358800</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>268100</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>257300</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>300100</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>306400</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>249700</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>204000</v>
       </c>
-      <c r="Q62" s="3"/>
-    </row>
-    <row r="63" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R62" s="3"/>
+    </row>
+    <row r="63" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>55</v>
       </c>
@@ -2969,9 +3117,12 @@
       <c r="P63" s="3">
         <v>0</v>
       </c>
-      <c r="Q63" s="3"/>
-    </row>
-    <row r="64" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q63" s="3">
+        <v>0</v>
+      </c>
+      <c r="R63" s="3"/>
+    </row>
+    <row r="64" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>19</v>
       </c>
@@ -3014,9 +3165,12 @@
       <c r="P64" s="3">
         <v>0</v>
       </c>
-      <c r="Q64" s="3"/>
-    </row>
-    <row r="65" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q64" s="3">
+        <v>0</v>
+      </c>
+      <c r="R64" s="3"/>
+    </row>
+    <row r="65" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>56</v>
       </c>
@@ -3059,54 +3213,60 @@
       <c r="P65" s="3">
         <v>0</v>
       </c>
-      <c r="Q65" s="3"/>
-    </row>
-    <row r="66" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q65" s="3">
+        <v>0</v>
+      </c>
+      <c r="R65" s="3"/>
+    </row>
+    <row r="66" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>57</v>
       </c>
       <c r="D66" s="3">
+        <v>1786500</v>
+      </c>
+      <c r="E66" s="3">
         <v>1973600</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>1836000</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>1728600</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>1815200</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>1585300</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>1450700</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>1368000</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>943300</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>927600</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>1117600</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>1143200</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>959200</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>837800</v>
       </c>
-      <c r="Q66" s="3"/>
-    </row>
-    <row r="67" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R66" s="3"/>
+    </row>
+    <row r="67" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>58</v>
       </c>
@@ -3124,8 +3284,9 @@
       <c r="O67" s="3"/>
       <c r="P67" s="3"/>
       <c r="Q67" s="3"/>
-    </row>
-    <row r="68" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R67" s="3"/>
+    </row>
+    <row r="68" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>59</v>
       </c>
@@ -3168,9 +3329,12 @@
       <c r="P68" s="3">
         <v>0</v>
       </c>
-      <c r="Q68" s="3"/>
-    </row>
-    <row r="69" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q68" s="3">
+        <v>0</v>
+      </c>
+      <c r="R68" s="3"/>
+    </row>
+    <row r="69" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>60</v>
       </c>
@@ -3213,9 +3377,12 @@
       <c r="P69" s="3">
         <v>0</v>
       </c>
-      <c r="Q69" s="3"/>
-    </row>
-    <row r="70" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q69" s="3">
+        <v>0</v>
+      </c>
+      <c r="R69" s="3"/>
+    </row>
+    <row r="70" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>61</v>
       </c>
@@ -3258,9 +3425,12 @@
       <c r="P70" s="3">
         <v>0</v>
       </c>
-      <c r="Q70" s="3"/>
-    </row>
-    <row r="71" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q70" s="3">
+        <v>0</v>
+      </c>
+      <c r="R70" s="3"/>
+    </row>
+    <row r="71" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>62</v>
       </c>
@@ -3303,54 +3473,60 @@
       <c r="P71" s="3">
         <v>0</v>
       </c>
-      <c r="Q71" s="3"/>
-    </row>
-    <row r="72" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q71" s="3">
+        <v>0</v>
+      </c>
+      <c r="R71" s="3"/>
+    </row>
+    <row r="72" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>63</v>
       </c>
       <c r="D72" s="3">
+        <v>575900</v>
+      </c>
+      <c r="E72" s="3">
         <v>1108800</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>1263600</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>1524300</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>1535100</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>1415100</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>1354400</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>1250000</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>903400</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>897200</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>1070500</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>1113200</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>969600</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>889800</v>
       </c>
-      <c r="Q72" s="3"/>
-    </row>
-    <row r="73" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R72" s="3"/>
+    </row>
+    <row r="73" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>64</v>
       </c>
@@ -3393,9 +3569,12 @@
       <c r="P73" s="3">
         <v>0</v>
       </c>
-      <c r="Q73" s="3"/>
-    </row>
-    <row r="74" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q73" s="3">
+        <v>0</v>
+      </c>
+      <c r="R73" s="3"/>
+    </row>
+    <row r="74" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>65</v>
       </c>
@@ -3438,9 +3617,12 @@
       <c r="P74" s="3">
         <v>0</v>
       </c>
-      <c r="Q74" s="3"/>
-    </row>
-    <row r="75" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q74" s="3">
+        <v>0</v>
+      </c>
+      <c r="R74" s="3"/>
+    </row>
+    <row r="75" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>66</v>
       </c>
@@ -3483,54 +3665,60 @@
       <c r="P75" s="3">
         <v>0</v>
       </c>
-      <c r="Q75" s="3"/>
-    </row>
-    <row r="76" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q75" s="3">
+        <v>0</v>
+      </c>
+      <c r="R75" s="3"/>
+    </row>
+    <row r="76" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>67</v>
       </c>
       <c r="D76" s="3">
+        <v>759700</v>
+      </c>
+      <c r="E76" s="3">
         <v>1520900</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>1733900</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>1916300</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>1826700</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>1723200</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>1704500</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>1572100</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>1105300</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>1132200</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>1348700</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>1369700</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>1031600</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>951800</v>
       </c>
-      <c r="Q76" s="3"/>
-    </row>
-    <row r="77" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R76" s="3"/>
+    </row>
+    <row r="77" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>68</v>
       </c>
@@ -3573,104 +3761,113 @@
       <c r="P77" s="3">
         <v>0</v>
       </c>
-      <c r="Q77" s="3"/>
-    </row>
-    <row r="79" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q77" s="3">
+        <v>0</v>
+      </c>
+      <c r="R77" s="3"/>
+    </row>
+    <row r="79" spans="2:18" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="80" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E80" s="2">
         <v>45291</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>44926</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>44561</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>44196</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>43830</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>43465</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>43100</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>42735</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>42369</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>42004</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>41639</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>41274</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>40908</v>
       </c>
-      <c r="Q80" s="2"/>
-    </row>
-    <row r="81" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R80" s="2"/>
+    </row>
+    <row r="81" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D81" s="3">
+        <v>218500</v>
+      </c>
+      <c r="E81" s="3">
         <v>76100</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>226300</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>333200</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>260700</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>257100</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>258100</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>228100</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>163700</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>152000</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>196500</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>188300</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>122200</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>153800</v>
       </c>
-      <c r="Q81" s="3"/>
-    </row>
-    <row r="82" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R81" s="3"/>
+    </row>
+    <row r="82" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>70</v>
       </c>
@@ -3688,53 +3885,57 @@
       <c r="O82" s="3"/>
       <c r="P82" s="3"/>
       <c r="Q82" s="3"/>
-    </row>
-    <row r="83" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R82" s="3"/>
+    </row>
+    <row r="83" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>71</v>
       </c>
       <c r="D83" s="3">
+        <v>172900</v>
+      </c>
+      <c r="E83" s="3">
         <v>188500</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>180400</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>165400</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>169500</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>104700</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>104600</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>85600</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>74300</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>58500</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>67100</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>69600</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>68100</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>65100</v>
       </c>
-      <c r="Q83" s="3"/>
-    </row>
-    <row r="84" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R83" s="3"/>
+    </row>
+    <row r="84" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>72</v>
       </c>
@@ -3777,9 +3978,12 @@
       <c r="P84" s="3">
         <v>0</v>
       </c>
-      <c r="Q84" s="3"/>
-    </row>
-    <row r="85" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q84" s="3">
+        <v>0</v>
+      </c>
+      <c r="R84" s="3"/>
+    </row>
+    <row r="85" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>73</v>
       </c>
@@ -3822,9 +4026,12 @@
       <c r="P85" s="3">
         <v>0</v>
       </c>
-      <c r="Q85" s="3"/>
-    </row>
-    <row r="86" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q85" s="3">
+        <v>0</v>
+      </c>
+      <c r="R85" s="3"/>
+    </row>
+    <row r="86" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>74</v>
       </c>
@@ -3867,9 +4074,12 @@
       <c r="P86" s="3">
         <v>0</v>
       </c>
-      <c r="Q86" s="3"/>
-    </row>
-    <row r="87" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q86" s="3">
+        <v>0</v>
+      </c>
+      <c r="R86" s="3"/>
+    </row>
+    <row r="87" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>75</v>
       </c>
@@ -3912,9 +4122,12 @@
       <c r="P87" s="3">
         <v>0</v>
       </c>
-      <c r="Q87" s="3"/>
-    </row>
-    <row r="88" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q87" s="3">
+        <v>0</v>
+      </c>
+      <c r="R87" s="3"/>
+    </row>
+    <row r="88" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>76</v>
       </c>
@@ -3957,54 +4170,60 @@
       <c r="P88" s="3">
         <v>0</v>
       </c>
-      <c r="Q88" s="3"/>
-    </row>
-    <row r="89" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q88" s="3">
+        <v>0</v>
+      </c>
+      <c r="R88" s="3"/>
+    </row>
+    <row r="89" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>77</v>
       </c>
       <c r="D89" s="3">
+        <v>297600</v>
+      </c>
+      <c r="E89" s="3">
         <v>406000</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>431500</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>480000</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>526200</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>415100</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>455400</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>416500</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>222500</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>216200</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>281400</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>295400</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>286600</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>231700</v>
       </c>
-      <c r="Q89" s="3"/>
-    </row>
-    <row r="90" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R89" s="3"/>
+    </row>
+    <row r="90" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>78</v>
       </c>
@@ -4022,53 +4241,57 @@
       <c r="O90" s="3"/>
       <c r="P90" s="3"/>
       <c r="Q90" s="3"/>
-    </row>
-    <row r="91" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R90" s="3"/>
+    </row>
+    <row r="91" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>79</v>
       </c>
       <c r="D91" s="3">
+        <v>-7800</v>
+      </c>
+      <c r="E91" s="3">
         <v>-15500</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-10600</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-18700</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-15100</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-37100</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-32400</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-40800</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-19800</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-25000</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-18000</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-17600</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-10800</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-61900</v>
       </c>
-      <c r="Q91" s="3"/>
-    </row>
-    <row r="92" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R91" s="3"/>
+    </row>
+    <row r="92" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>80</v>
       </c>
@@ -4111,9 +4334,12 @@
       <c r="P92" s="3">
         <v>0</v>
       </c>
-      <c r="Q92" s="3"/>
-    </row>
-    <row r="93" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q92" s="3">
+        <v>0</v>
+      </c>
+      <c r="R92" s="3"/>
+    </row>
+    <row r="93" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>81</v>
       </c>
@@ -4156,54 +4382,60 @@
       <c r="P93" s="3">
         <v>0</v>
       </c>
-      <c r="Q93" s="3"/>
-    </row>
-    <row r="94" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q93" s="3">
+        <v>0</v>
+      </c>
+      <c r="R93" s="3"/>
+    </row>
+    <row r="94" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>82</v>
       </c>
       <c r="D94" s="3">
+        <v>32100</v>
+      </c>
+      <c r="E94" s="3">
         <v>219900</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-513500</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>22400</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-56000</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-13500</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>7500</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-300200</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>85800</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-34900</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-290000</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-155200</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-414900</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-23200</v>
       </c>
-      <c r="Q94" s="3"/>
-    </row>
-    <row r="95" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R94" s="3"/>
+    </row>
+    <row r="95" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>83</v>
       </c>
@@ -4221,13 +4453,14 @@
       <c r="O95" s="3"/>
       <c r="P95" s="3"/>
       <c r="Q95" s="3"/>
-    </row>
-    <row r="96" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R95" s="3"/>
+    </row>
+    <row r="96" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>84</v>
       </c>
       <c r="D96" s="3">
-        <v>0</v>
+        <v>612400</v>
       </c>
       <c r="E96" s="3">
         <v>0</v>
@@ -4248,26 +4481,29 @@
         <v>0</v>
       </c>
       <c r="K96" s="3">
+        <v>0</v>
+      </c>
+      <c r="L96" s="3">
         <v>-96200</v>
       </c>
-      <c r="L96" s="3">
+      <c r="M96" s="3">
         <v>-105200</v>
       </c>
-      <c r="M96" s="3">
+      <c r="N96" s="3">
         <v>-138900</v>
       </c>
-      <c r="N96" s="3">
+      <c r="O96" s="3">
         <v>-80800</v>
       </c>
-      <c r="O96" s="3">
+      <c r="P96" s="3">
         <v>-98200</v>
       </c>
-      <c r="P96" s="3">
+      <c r="Q96" s="3">
         <v>-79200</v>
       </c>
-      <c r="Q96" s="3"/>
-    </row>
-    <row r="97" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R96" s="3"/>
+    </row>
+    <row r="97" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>85</v>
       </c>
@@ -4310,9 +4546,12 @@
       <c r="P97" s="3">
         <v>0</v>
       </c>
-      <c r="Q97" s="3"/>
-    </row>
-    <row r="98" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q97" s="3">
+        <v>0</v>
+      </c>
+      <c r="R97" s="3"/>
+    </row>
+    <row r="98" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>86</v>
       </c>
@@ -4355,9 +4594,12 @@
       <c r="P98" s="3">
         <v>0</v>
       </c>
-      <c r="Q98" s="3"/>
-    </row>
-    <row r="99" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q98" s="3">
+        <v>0</v>
+      </c>
+      <c r="R98" s="3"/>
+    </row>
+    <row r="99" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>87</v>
       </c>
@@ -4400,142 +4642,154 @@
       <c r="P99" s="3">
         <v>0</v>
       </c>
-      <c r="Q99" s="3"/>
-    </row>
-    <row r="100" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q99" s="3">
+        <v>0</v>
+      </c>
+      <c r="R99" s="3"/>
+    </row>
+    <row r="100" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>88</v>
       </c>
       <c r="D100" s="3">
+        <v>-832600</v>
+      </c>
+      <c r="E100" s="3">
         <v>-308100</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-230800</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-142800</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-204900</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-238900</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-120500</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-150100</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-99900</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-66100</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-148800</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-2000</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-101200</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-120300</v>
       </c>
-      <c r="Q100" s="3"/>
-    </row>
-    <row r="101" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R100" s="3"/>
+    </row>
+    <row r="101" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D101" s="3">
+        <v>33100</v>
+      </c>
+      <c r="E101" s="3">
         <v>62600</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>181300</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>87900</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>-13100</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>-10900</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>-39800</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>-1100</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>2100</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>-30000</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>22700</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>87700</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>41100</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>-25800</v>
       </c>
-      <c r="Q101" s="3"/>
-    </row>
-    <row r="102" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R101" s="3"/>
+    </row>
+    <row r="102" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D102" s="3">
+        <v>-469900</v>
+      </c>
+      <c r="E102" s="3">
         <v>380400</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-131500</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>447400</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>252300</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>151800</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>302500</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-34900</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>210500</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>85200</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-134700</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>225900</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-188400</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>62400</v>
       </c>
-      <c r="Q102" s="3"/>
+      <c r="R102" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/AAII_Financials/Yearly/TMICY_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/TMICY_YR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="100" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="99" uniqueCount="92">
   <si>
     <t>TMICY</t>
   </si>
@@ -892,8 +892,8 @@
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="D12" s="3" t="s">
-        <v>91</v>
+      <c r="D12" s="3">
+        <v>37200</v>
       </c>
       <c r="E12" s="3">
         <v>33100</v>
@@ -2367,7 +2367,7 @@
         <v>39</v>
       </c>
       <c r="D47" s="3">
-        <v>36600</v>
+        <v>50300</v>
       </c>
       <c r="E47" s="3">
         <v>148900</v>
@@ -2607,7 +2607,7 @@
         <v>44</v>
       </c>
       <c r="D52" s="3">
-        <v>13700</v>
+        <v>0</v>
       </c>
       <c r="E52" s="3">
         <v>0</v>
@@ -4460,7 +4460,7 @@
         <v>84</v>
       </c>
       <c r="D96" s="3">
-        <v>612400</v>
+        <v>0</v>
       </c>
       <c r="E96" s="3">
         <v>0</v>

--- a/AAII_Financials/Yearly/TMICY_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/TMICY_YR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="99" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="107" uniqueCount="92">
   <si>
     <t>TMICY</t>
   </si>
@@ -656,219 +656,231 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:R102"/>
+  <dimension ref="A5:S102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="8.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:19" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E7" s="2">
         <v>45657</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45291</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>44926</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>44561</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>44196</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>43830</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>43465</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>43100</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>42735</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>42369</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>42004</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>41639</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>41274</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>40908</v>
       </c>
-      <c r="R7" s="2"/>
-    </row>
-    <row r="8" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S7" s="2"/>
+    </row>
+    <row r="8" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>1760200</v>
+      </c>
+      <c r="E8" s="3">
         <v>1734100</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>1764200</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>1697000</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>1653300</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>1686500</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>1520100</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>1462100</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>1321200</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>876100</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>881400</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>1015000</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>1040900</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>853000</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>855000</v>
       </c>
-      <c r="R8" s="3"/>
-    </row>
-    <row r="9" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S8" s="3"/>
+    </row>
+    <row r="9" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>406400</v>
+      </c>
+      <c r="E9" s="3">
         <v>413300</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>451600</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>411800</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>364900</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>369800</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>297200</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>298300</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>249800</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>153000</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>150800</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>180000</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>186200</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>159200</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>158700</v>
       </c>
-      <c r="R9" s="3"/>
-    </row>
-    <row r="10" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S9" s="3"/>
+    </row>
+    <row r="10" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>1353800</v>
+      </c>
+      <c r="E10" s="3">
         <v>1320800</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>1312600</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>1285300</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>1288400</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>1316700</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>1222900</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>1163800</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>1071400</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>723100</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>730600</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>835000</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>854700</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>693800</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>696300</v>
       </c>
-      <c r="R10" s="3"/>
-    </row>
-    <row r="11" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S10" s="3"/>
+    </row>
+    <row r="11" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -887,56 +899,60 @@
       <c r="P11" s="3"/>
       <c r="Q11" s="3"/>
       <c r="R11" s="3"/>
-    </row>
-    <row r="12" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S11" s="3"/>
+    </row>
+    <row r="12" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="D12" s="3">
+      <c r="D12" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="E12" s="3">
         <v>37200</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>33100</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>41000</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>40600</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>71100</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>75800</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>67900</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>69100</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>35000</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>26800</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>25800</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>40200</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>34400</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="R12" s="3">
         <v>30800</v>
       </c>
-      <c r="R12" s="3"/>
-    </row>
-    <row r="13" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S12" s="3"/>
+    </row>
+    <row r="13" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>8</v>
       </c>
@@ -982,87 +998,93 @@
       <c r="Q13" s="3">
         <v>0</v>
       </c>
-      <c r="R13" s="3"/>
-    </row>
-    <row r="14" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="R13" s="3">
+        <v>0</v>
+      </c>
+      <c r="S13" s="3"/>
+    </row>
+    <row r="14" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>9</v>
       </c>
       <c r="D14" s="3">
+        <v>10500</v>
+      </c>
+      <c r="E14" s="3">
         <v>-18900</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>15300</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>-58400</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>-79800</v>
       </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
         <v>-9400</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>1400</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>4200</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>-1100</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>2500</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>5300</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>2000</v>
       </c>
-      <c r="O14" s="3">
+      <c r="P14" s="3">
         <v>8200</v>
       </c>
-      <c r="P14" s="3">
+      <c r="Q14" s="3">
         <v>-31300</v>
       </c>
-      <c r="Q14" s="3">
+      <c r="R14" s="3">
         <v>-42100</v>
       </c>
-      <c r="R14" s="3"/>
-    </row>
-    <row r="15" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S14" s="3"/>
+    </row>
+    <row r="15" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D15" s="3">
+        <v>172600</v>
+      </c>
+      <c r="E15" s="3">
         <v>184000</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>200900</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>191000</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>181500</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>219700</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>145500</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>145000</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>123900</v>
       </c>
-      <c r="L15" s="3">
-        <v>0</v>
-      </c>
       <c r="M15" s="3">
         <v>0</v>
       </c>
@@ -1078,9 +1100,12 @@
       <c r="Q15" s="3">
         <v>0</v>
       </c>
-      <c r="R15" s="3"/>
-    </row>
-    <row r="16" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="R15" s="3">
+        <v>0</v>
+      </c>
+      <c r="S15" s="3"/>
+    </row>
+    <row r="16" spans="1:19" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1096,104 +1121,111 @@
       <c r="P16" s="3"/>
       <c r="Q16" s="3"/>
       <c r="R16" s="3"/>
-    </row>
-    <row r="17" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S16" s="3"/>
+    </row>
+    <row r="17" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D17" s="3">
+        <v>1391700</v>
+      </c>
+      <c r="E17" s="3">
         <v>1428100</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>1533000</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>1459400</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>1274300</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>1304100</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>1173300</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>1135400</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>997600</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>650400</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>667100</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>720500</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>766100</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>618000</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>579000</v>
       </c>
-      <c r="R17" s="3"/>
-    </row>
-    <row r="18" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S17" s="3"/>
+    </row>
+    <row r="18" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D18" s="3">
+        <v>368500</v>
+      </c>
+      <c r="E18" s="3">
         <v>306000</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>231300</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>237700</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>379000</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>382400</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>346800</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>326600</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>323500</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>225700</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>214300</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>294500</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>274800</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>235000</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>276000</v>
       </c>
-      <c r="R18" s="3"/>
-    </row>
-    <row r="19" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S18" s="3"/>
+    </row>
+    <row r="19" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>13</v>
       </c>
@@ -1212,104 +1244,111 @@
       <c r="P19" s="3"/>
       <c r="Q19" s="3"/>
       <c r="R19" s="3"/>
-    </row>
-    <row r="20" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S19" s="3"/>
+    </row>
+    <row r="20" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>14</v>
       </c>
       <c r="D20" s="3">
+        <v>46700</v>
+      </c>
+      <c r="E20" s="3">
         <v>-12000</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>30600</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>-5700</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>7500</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>12700</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>900</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>-2700</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>6000</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>11500</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>27000</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>23100</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>32800</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>-13100</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>-22100</v>
       </c>
-      <c r="R20" s="3"/>
-    </row>
-    <row r="21" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S20" s="3"/>
+    </row>
+    <row r="21" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D21" s="3">
+        <v>494400</v>
+      </c>
+      <c r="E21" s="3">
         <v>502000</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>401500</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>434400</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>553000</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>589400</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>491400</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>474400</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>441400</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>311200</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>297700</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>384800</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>377100</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>290200</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>319000</v>
       </c>
-      <c r="R21" s="3"/>
-    </row>
-    <row r="22" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S21" s="3"/>
+    </row>
+    <row r="22" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>16</v>
       </c>
@@ -1319,20 +1358,20 @@
       <c r="E22" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="F22" s="3">
+      <c r="F22" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="G22" s="3">
         <v>300</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>100</v>
-      </c>
-      <c r="H22" s="3" t="s">
-        <v>91</v>
       </c>
       <c r="I22" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="J22" s="3">
-        <v>0</v>
+      <c r="J22" s="3" t="s">
+        <v>91</v>
       </c>
       <c r="K22" s="3">
         <v>0</v>
@@ -1344,116 +1383,125 @@
         <v>0</v>
       </c>
       <c r="N22" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="O22" s="3">
         <v>100</v>
       </c>
       <c r="P22" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Q22" s="3">
         <v>0</v>
       </c>
-      <c r="R22" s="3"/>
-    </row>
-    <row r="23" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R22" s="3">
+        <v>0</v>
+      </c>
+      <c r="S22" s="3"/>
+    </row>
+    <row r="23" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D23" s="3">
+        <v>333800</v>
+      </c>
+      <c r="E23" s="3">
         <v>353500</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>226800</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>317700</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>454900</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>386200</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>360100</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>339000</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>329300</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>237200</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>241300</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>317400</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>307600</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>221800</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>253900</v>
       </c>
-      <c r="R23" s="3"/>
-    </row>
-    <row r="24" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S23" s="3"/>
+    </row>
+    <row r="24" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D24" s="3">
+        <v>116300</v>
+      </c>
+      <c r="E24" s="3">
         <v>133900</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>150500</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>98200</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>128200</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>130600</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>104200</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>81000</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>101200</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>73500</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>89300</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>120900</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>119300</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>99600</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>100000</v>
       </c>
-      <c r="R24" s="3"/>
-    </row>
-    <row r="25" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S24" s="3"/>
+    </row>
+    <row r="25" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>19</v>
       </c>
@@ -1499,105 +1547,114 @@
       <c r="Q25" s="3">
         <v>0</v>
       </c>
-      <c r="R25" s="3"/>
-    </row>
-    <row r="26" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R25" s="3">
+        <v>0</v>
+      </c>
+      <c r="S25" s="3"/>
+    </row>
+    <row r="26" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>20</v>
       </c>
       <c r="D26" s="3">
+        <v>217500</v>
+      </c>
+      <c r="E26" s="3">
         <v>219600</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>76300</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>219600</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>326700</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>255600</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>256000</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>257900</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>228100</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>163700</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>152000</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>196500</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>188300</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>122200</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>153900</v>
       </c>
-      <c r="R26" s="3"/>
-    </row>
-    <row r="27" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S26" s="3"/>
+    </row>
+    <row r="27" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D27" s="3">
+        <v>220200</v>
+      </c>
+      <c r="E27" s="3">
         <v>218500</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>76100</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>226300</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>333200</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>260700</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>257100</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>258100</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>228100</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>163700</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>152000</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>196500</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>188300</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>122200</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>153800</v>
       </c>
-      <c r="R27" s="3"/>
-    </row>
-    <row r="28" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S27" s="3"/>
+    </row>
+    <row r="28" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>22</v>
       </c>
@@ -1643,9 +1700,12 @@
       <c r="Q28" s="3">
         <v>0</v>
       </c>
-      <c r="R28" s="3"/>
-    </row>
-    <row r="29" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R28" s="3">
+        <v>0</v>
+      </c>
+      <c r="S28" s="3"/>
+    </row>
+    <row r="29" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>23</v>
       </c>
@@ -1691,9 +1751,12 @@
       <c r="Q29" s="3">
         <v>0</v>
       </c>
-      <c r="R29" s="3"/>
-    </row>
-    <row r="30" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R29" s="3">
+        <v>0</v>
+      </c>
+      <c r="S29" s="3"/>
+    </row>
+    <row r="30" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>24</v>
       </c>
@@ -1739,9 +1802,12 @@
       <c r="Q30" s="3">
         <v>0</v>
       </c>
-      <c r="R30" s="3"/>
-    </row>
-    <row r="31" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R30" s="3">
+        <v>0</v>
+      </c>
+      <c r="S30" s="3"/>
+    </row>
+    <row r="31" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>25</v>
       </c>
@@ -1787,105 +1853,114 @@
       <c r="Q31" s="3">
         <v>0</v>
       </c>
-      <c r="R31" s="3"/>
-    </row>
-    <row r="32" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R31" s="3">
+        <v>0</v>
+      </c>
+      <c r="S31" s="3"/>
+    </row>
+    <row r="32" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>26</v>
       </c>
       <c r="D32" s="3">
+        <v>-46700</v>
+      </c>
+      <c r="E32" s="3">
         <v>12000</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>-30600</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>5700</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>-7500</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>-12700</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>-900</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>2700</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-6000</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-11500</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-27000</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-23100</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-32800</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>13100</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>22100</v>
       </c>
-      <c r="R32" s="3"/>
-    </row>
-    <row r="33" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S32" s="3"/>
+    </row>
+    <row r="33" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D33" s="3">
+        <v>220200</v>
+      </c>
+      <c r="E33" s="3">
         <v>218500</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>76100</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>226300</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>333200</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>260700</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>257100</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>258100</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>228100</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>163700</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>152000</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>196500</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>188300</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>122200</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>153800</v>
       </c>
-      <c r="R33" s="3"/>
-    </row>
-    <row r="34" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S33" s="3"/>
+    </row>
+    <row r="34" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>28</v>
       </c>
@@ -1931,110 +2006,119 @@
       <c r="Q34" s="3">
         <v>0</v>
       </c>
-      <c r="R34" s="3"/>
-    </row>
-    <row r="35" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R34" s="3">
+        <v>0</v>
+      </c>
+      <c r="S34" s="3"/>
+    </row>
+    <row r="35" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>29</v>
       </c>
       <c r="D35" s="3">
+        <v>220200</v>
+      </c>
+      <c r="E35" s="3">
         <v>218500</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>76100</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>226300</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>333200</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>260700</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>257100</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>258100</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>228100</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>163700</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>152000</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>196500</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>188300</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>122200</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>153800</v>
       </c>
-      <c r="R35" s="3"/>
-    </row>
-    <row r="37" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S35" s="3"/>
+    </row>
+    <row r="37" spans="2:19" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="38" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E38" s="2">
         <v>45657</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45291</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>44926</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>44561</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>44196</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>43830</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>43465</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>43100</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>42735</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>42369</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>42004</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>41639</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>41274</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>40908</v>
       </c>
-      <c r="R38" s="2"/>
-    </row>
-    <row r="39" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S38" s="2"/>
+    </row>
+    <row r="39" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>31</v>
       </c>
@@ -2053,8 +2137,9 @@
       <c r="P39" s="3"/>
       <c r="Q39" s="3"/>
       <c r="R39" s="3"/>
-    </row>
-    <row r="40" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S39" s="3"/>
+    </row>
+    <row r="40" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>32</v>
       </c>
@@ -2073,440 +2158,468 @@
       <c r="P40" s="3"/>
       <c r="Q40" s="3"/>
       <c r="R40" s="3"/>
-    </row>
-    <row r="41" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S40" s="3"/>
+    </row>
+    <row r="41" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>33</v>
       </c>
       <c r="D41" s="3">
+        <v>1403800</v>
+      </c>
+      <c r="E41" s="3">
         <v>1081600</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>1758300</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>1452500</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>1717300</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>1509000</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>1150000</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>1061800</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>762600</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>561100</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>523500</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>556000</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>765300</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>497500</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>637600</v>
       </c>
-      <c r="R41" s="3"/>
-    </row>
-    <row r="42" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S41" s="3"/>
+    </row>
+    <row r="42" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D42" s="3">
+        <v>69800</v>
+      </c>
+      <c r="E42" s="3">
         <v>259800</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>363000</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>389100</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>513100</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>547700</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>438200</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>558600</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>590700</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>333000</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>509900</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>654800</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>585800</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>582800</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="R42" s="3">
         <v>334700</v>
       </c>
-      <c r="R42" s="3"/>
-    </row>
-    <row r="43" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S42" s="3"/>
+    </row>
+    <row r="43" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D43" s="3">
+        <v>485500</v>
+      </c>
+      <c r="E43" s="3">
         <v>474000</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>489000</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>480000</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>462100</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>455600</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>413500</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>355300</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>353200</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>236100</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>212500</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>229700</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>233800</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>189900</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>185900</v>
       </c>
-      <c r="R43" s="3"/>
-    </row>
-    <row r="44" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S43" s="3"/>
+    </row>
+    <row r="44" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D44" s="3">
+        <v>64100</v>
+      </c>
+      <c r="E44" s="3">
         <v>53800</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>47300</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>32300</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>32100</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>33000</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>37800</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>33500</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>26500</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>11400</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>5700</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>4600</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>3900</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>3400</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>3800</v>
       </c>
-      <c r="R44" s="3"/>
-    </row>
-    <row r="45" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S44" s="3"/>
+    </row>
+    <row r="45" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D45" s="3">
+        <v>98800</v>
+      </c>
+      <c r="E45" s="3">
         <v>88700</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>101200</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>72300</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>69800</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>57700</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>52500</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>48600</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>51400</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>153400</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>176900</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>174100</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>185300</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>174100</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>179300</v>
       </c>
-      <c r="R45" s="3"/>
-    </row>
-    <row r="46" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S45" s="3"/>
+    </row>
+    <row r="46" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D46" s="3">
+        <v>2121900</v>
+      </c>
+      <c r="E46" s="3">
         <v>1958000</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>2758800</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>2426100</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>2794500</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>2603000</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>2092000</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>2204900</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>1924700</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>1295000</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>1428500</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>1619300</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>1774100</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>1447700</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>1341300</v>
       </c>
-      <c r="R46" s="3"/>
-    </row>
-    <row r="47" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S46" s="3"/>
+    </row>
+    <row r="47" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D47" s="3">
+        <v>30300</v>
+      </c>
+      <c r="E47" s="3">
         <v>50300</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>148900</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>586700</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>250500</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>367700</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>476900</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>422400</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>479300</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>336800</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>445300</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>608300</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>491400</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>322500</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>208300</v>
       </c>
-      <c r="R47" s="3"/>
-    </row>
-    <row r="48" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S47" s="3"/>
+    </row>
+    <row r="48" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D48" s="3">
+        <v>30600</v>
+      </c>
+      <c r="E48" s="3">
         <v>35300</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>46000</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>53800</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>68900</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>77200</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>90700</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>79900</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>73000</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>43500</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>41000</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>43600</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>44000</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>40300</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>45700</v>
       </c>
-      <c r="R48" s="3"/>
-    </row>
-    <row r="49" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S48" s="3"/>
+    </row>
+    <row r="49" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D49" s="3">
+        <v>178800</v>
+      </c>
+      <c r="E49" s="3">
         <v>199700</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>226200</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>184200</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>220900</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>251000</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>332900</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>320000</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>357700</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>282400</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>58200</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>83100</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>88000</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>71500</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>84400</v>
       </c>
-      <c r="R49" s="3"/>
-    </row>
-    <row r="50" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S49" s="3"/>
+    </row>
+    <row r="50" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>42</v>
       </c>
@@ -2552,9 +2665,12 @@
       <c r="Q50" s="3">
         <v>0</v>
       </c>
-      <c r="R50" s="3"/>
-    </row>
-    <row r="51" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R50" s="3">
+        <v>0</v>
+      </c>
+      <c r="S50" s="3"/>
+    </row>
+    <row r="51" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>43</v>
       </c>
@@ -2600,14 +2716,17 @@
       <c r="Q51" s="3">
         <v>0</v>
       </c>
-      <c r="R51" s="3"/>
-    </row>
-    <row r="52" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R51" s="3">
+        <v>0</v>
+      </c>
+      <c r="S51" s="3"/>
+    </row>
+    <row r="52" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>44</v>
       </c>
       <c r="D52" s="3">
-        <v>0</v>
+        <v>27400</v>
       </c>
       <c r="E52" s="3">
         <v>0</v>
@@ -2631,26 +2750,29 @@
         <v>0</v>
       </c>
       <c r="L52" s="3">
+        <v>0</v>
+      </c>
+      <c r="M52" s="3">
         <v>90900</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>86700</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>112000</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>115400</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>108700</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>109900</v>
       </c>
-      <c r="R52" s="3"/>
-    </row>
-    <row r="53" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S52" s="3"/>
+    </row>
+    <row r="53" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>45</v>
       </c>
@@ -2696,57 +2818,63 @@
       <c r="Q53" s="3">
         <v>0</v>
       </c>
-      <c r="R53" s="3"/>
-    </row>
-    <row r="54" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R53" s="3">
+        <v>0</v>
+      </c>
+      <c r="S53" s="3"/>
+    </row>
+    <row r="54" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>46</v>
       </c>
       <c r="D54" s="3">
+        <v>2693100</v>
+      </c>
+      <c r="E54" s="3">
         <v>2546200</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>3494800</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>3570100</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>3651800</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>3650000</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>3309900</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>3155800</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>2940100</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>2048700</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>2059800</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>2466300</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>2512900</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>1990800</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>1789600</v>
       </c>
-      <c r="R54" s="3"/>
-    </row>
-    <row r="55" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S54" s="3"/>
+    </row>
+    <row r="55" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>47</v>
       </c>
@@ -2765,8 +2893,9 @@
       <c r="P55" s="3"/>
       <c r="Q55" s="3"/>
       <c r="R55" s="3"/>
-    </row>
-    <row r="56" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S55" s="3"/>
+    </row>
+    <row r="56" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>48</v>
       </c>
@@ -2785,56 +2914,60 @@
       <c r="P56" s="3"/>
       <c r="Q56" s="3"/>
       <c r="R56" s="3"/>
-    </row>
-    <row r="57" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S56" s="3"/>
+    </row>
+    <row r="57" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>49</v>
       </c>
       <c r="D57" s="3">
+        <v>19000</v>
+      </c>
+      <c r="E57" s="3">
         <v>23100</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>19300</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>16400</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>10100</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>8900</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>11100</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>14800</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>6500</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>5900</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>4000</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>5900</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>4700</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>6600</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>7900</v>
       </c>
-      <c r="R57" s="3"/>
-    </row>
-    <row r="58" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S57" s="3"/>
+    </row>
+    <row r="58" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>50</v>
       </c>
@@ -2880,105 +3013,114 @@
       <c r="Q58" s="3">
         <v>0</v>
       </c>
-      <c r="R58" s="3"/>
-    </row>
-    <row r="59" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R58" s="3">
+        <v>0</v>
+      </c>
+      <c r="S58" s="3"/>
+    </row>
+    <row r="59" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D59" s="3">
+        <v>1662900</v>
+      </c>
+      <c r="E59" s="3">
         <v>1558000</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>1702500</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>1604900</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>1021700</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>1149600</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>1005500</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>934500</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>888600</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>669300</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>666300</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>811500</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>832000</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>702800</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>625500</v>
       </c>
-      <c r="R59" s="3"/>
-    </row>
-    <row r="60" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S59" s="3"/>
+    </row>
+    <row r="60" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D60" s="3">
+        <v>1776100</v>
+      </c>
+      <c r="E60" s="3">
         <v>1700000</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>1880500</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>1761500</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>1160600</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>1273800</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>1100100</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>1017100</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>965600</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>675200</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>670300</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>817400</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>836700</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>709400</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>633300</v>
       </c>
-      <c r="R60" s="3"/>
-    </row>
-    <row r="61" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S60" s="3"/>
+    </row>
+    <row r="61" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>53</v>
       </c>
@@ -3024,57 +3166,63 @@
       <c r="Q61" s="3">
         <v>0</v>
       </c>
-      <c r="R61" s="3"/>
-    </row>
-    <row r="62" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R61" s="3">
+        <v>0</v>
+      </c>
+      <c r="S61" s="3"/>
+    </row>
+    <row r="62" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D62" s="3">
+        <v>39300</v>
+      </c>
+      <c r="E62" s="3">
         <v>37700</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>35900</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>18300</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>499300</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>470900</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>428100</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>380100</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>358800</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>268100</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>257300</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>300100</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>306400</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>249700</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>204000</v>
       </c>
-      <c r="R62" s="3"/>
-    </row>
-    <row r="63" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S62" s="3"/>
+    </row>
+    <row r="63" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>55</v>
       </c>
@@ -3120,9 +3268,12 @@
       <c r="Q63" s="3">
         <v>0</v>
       </c>
-      <c r="R63" s="3"/>
-    </row>
-    <row r="64" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R63" s="3">
+        <v>0</v>
+      </c>
+      <c r="S63" s="3"/>
+    </row>
+    <row r="64" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>19</v>
       </c>
@@ -3168,9 +3319,12 @@
       <c r="Q64" s="3">
         <v>0</v>
       </c>
-      <c r="R64" s="3"/>
-    </row>
-    <row r="65" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R64" s="3">
+        <v>0</v>
+      </c>
+      <c r="S64" s="3"/>
+    </row>
+    <row r="65" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>56</v>
       </c>
@@ -3216,57 +3370,63 @@
       <c r="Q65" s="3">
         <v>0</v>
       </c>
-      <c r="R65" s="3"/>
-    </row>
-    <row r="66" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R65" s="3">
+        <v>0</v>
+      </c>
+      <c r="S65" s="3"/>
+    </row>
+    <row r="66" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>57</v>
       </c>
       <c r="D66" s="3">
+        <v>1856700</v>
+      </c>
+      <c r="E66" s="3">
         <v>1786500</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>1973600</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>1836000</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>1728600</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>1815200</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>1585300</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>1450700</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>1368000</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>943300</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>927600</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>1117600</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>1143200</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>959200</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>837800</v>
       </c>
-      <c r="R66" s="3"/>
-    </row>
-    <row r="67" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S66" s="3"/>
+    </row>
+    <row r="67" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>58</v>
       </c>
@@ -3285,8 +3445,9 @@
       <c r="P67" s="3"/>
       <c r="Q67" s="3"/>
       <c r="R67" s="3"/>
-    </row>
-    <row r="68" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S67" s="3"/>
+    </row>
+    <row r="68" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>59</v>
       </c>
@@ -3332,9 +3493,12 @@
       <c r="Q68" s="3">
         <v>0</v>
       </c>
-      <c r="R68" s="3"/>
-    </row>
-    <row r="69" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R68" s="3">
+        <v>0</v>
+      </c>
+      <c r="S68" s="3"/>
+    </row>
+    <row r="69" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>60</v>
       </c>
@@ -3380,9 +3544,12 @@
       <c r="Q69" s="3">
         <v>0</v>
       </c>
-      <c r="R69" s="3"/>
-    </row>
-    <row r="70" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R69" s="3">
+        <v>0</v>
+      </c>
+      <c r="S69" s="3"/>
+    </row>
+    <row r="70" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>61</v>
       </c>
@@ -3428,9 +3595,12 @@
       <c r="Q70" s="3">
         <v>0</v>
       </c>
-      <c r="R70" s="3"/>
-    </row>
-    <row r="71" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R70" s="3">
+        <v>0</v>
+      </c>
+      <c r="S70" s="3"/>
+    </row>
+    <row r="71" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>62</v>
       </c>
@@ -3476,57 +3646,63 @@
       <c r="Q71" s="3">
         <v>0</v>
       </c>
-      <c r="R71" s="3"/>
-    </row>
-    <row r="72" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R71" s="3">
+        <v>0</v>
+      </c>
+      <c r="S71" s="3"/>
+    </row>
+    <row r="72" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>63</v>
       </c>
       <c r="D72" s="3">
+        <v>643600</v>
+      </c>
+      <c r="E72" s="3">
         <v>575900</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>1108800</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>1263600</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>1524300</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>1535100</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>1415100</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>1354400</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>1250000</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>903400</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>897200</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>1070500</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>1113200</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>969600</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>889800</v>
       </c>
-      <c r="R72" s="3"/>
-    </row>
-    <row r="73" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S72" s="3"/>
+    </row>
+    <row r="73" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>64</v>
       </c>
@@ -3572,9 +3748,12 @@
       <c r="Q73" s="3">
         <v>0</v>
       </c>
-      <c r="R73" s="3"/>
-    </row>
-    <row r="74" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R73" s="3">
+        <v>0</v>
+      </c>
+      <c r="S73" s="3"/>
+    </row>
+    <row r="74" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>65</v>
       </c>
@@ -3620,9 +3799,12 @@
       <c r="Q74" s="3">
         <v>0</v>
       </c>
-      <c r="R74" s="3"/>
-    </row>
-    <row r="75" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R74" s="3">
+        <v>0</v>
+      </c>
+      <c r="S74" s="3"/>
+    </row>
+    <row r="75" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>66</v>
       </c>
@@ -3668,57 +3850,63 @@
       <c r="Q75" s="3">
         <v>0</v>
       </c>
-      <c r="R75" s="3"/>
-    </row>
-    <row r="76" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R75" s="3">
+        <v>0</v>
+      </c>
+      <c r="S75" s="3"/>
+    </row>
+    <row r="76" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>67</v>
       </c>
       <c r="D76" s="3">
+        <v>833100</v>
+      </c>
+      <c r="E76" s="3">
         <v>759700</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>1520900</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>1733900</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>1916300</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>1826700</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>1723200</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>1704500</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>1572100</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>1105300</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>1132200</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>1348700</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>1369700</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>1031600</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>951800</v>
       </c>
-      <c r="R76" s="3"/>
-    </row>
-    <row r="77" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S76" s="3"/>
+    </row>
+    <row r="77" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>68</v>
       </c>
@@ -3764,110 +3952,119 @@
       <c r="Q77" s="3">
         <v>0</v>
       </c>
-      <c r="R77" s="3"/>
-    </row>
-    <row r="79" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R77" s="3">
+        <v>0</v>
+      </c>
+      <c r="S77" s="3"/>
+    </row>
+    <row r="79" spans="2:19" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="80" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E80" s="2">
         <v>45657</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45291</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>44926</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>44561</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>44196</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>43830</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>43465</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>43100</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>42735</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>42369</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>42004</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>41639</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>41274</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>40908</v>
       </c>
-      <c r="R80" s="2"/>
-    </row>
-    <row r="81" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S80" s="2"/>
+    </row>
+    <row r="81" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D81" s="3">
+        <v>220200</v>
+      </c>
+      <c r="E81" s="3">
         <v>218500</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>76100</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>226300</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>333200</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>260700</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>257100</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>258100</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>228100</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>163700</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>152000</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>196500</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>188300</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>122200</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>153800</v>
       </c>
-      <c r="R81" s="3"/>
-    </row>
-    <row r="82" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S81" s="3"/>
+    </row>
+    <row r="82" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>70</v>
       </c>
@@ -3886,56 +4083,60 @@
       <c r="P82" s="3"/>
       <c r="Q82" s="3"/>
       <c r="R82" s="3"/>
-    </row>
-    <row r="83" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S82" s="3"/>
+    </row>
+    <row r="83" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>71</v>
       </c>
-      <c r="D83" s="3">
+      <c r="D83" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="E83" s="3">
         <v>172900</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>188500</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>180400</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>165400</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>169500</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>104700</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>104600</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>85600</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>74300</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>58500</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>67100</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>69600</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>68100</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>65100</v>
       </c>
-      <c r="R83" s="3"/>
-    </row>
-    <row r="84" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S83" s="3"/>
+    </row>
+    <row r="84" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>72</v>
       </c>
@@ -3981,9 +4182,12 @@
       <c r="Q84" s="3">
         <v>0</v>
       </c>
-      <c r="R84" s="3"/>
-    </row>
-    <row r="85" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R84" s="3">
+        <v>0</v>
+      </c>
+      <c r="S84" s="3"/>
+    </row>
+    <row r="85" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>73</v>
       </c>
@@ -4029,9 +4233,12 @@
       <c r="Q85" s="3">
         <v>0</v>
       </c>
-      <c r="R85" s="3"/>
-    </row>
-    <row r="86" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R85" s="3">
+        <v>0</v>
+      </c>
+      <c r="S85" s="3"/>
+    </row>
+    <row r="86" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>74</v>
       </c>
@@ -4077,9 +4284,12 @@
       <c r="Q86" s="3">
         <v>0</v>
       </c>
-      <c r="R86" s="3"/>
-    </row>
-    <row r="87" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R86" s="3">
+        <v>0</v>
+      </c>
+      <c r="S86" s="3"/>
+    </row>
+    <row r="87" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>75</v>
       </c>
@@ -4125,9 +4335,12 @@
       <c r="Q87" s="3">
         <v>0</v>
       </c>
-      <c r="R87" s="3"/>
-    </row>
-    <row r="88" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R87" s="3">
+        <v>0</v>
+      </c>
+      <c r="S87" s="3"/>
+    </row>
+    <row r="88" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>76</v>
       </c>
@@ -4173,57 +4386,63 @@
       <c r="Q88" s="3">
         <v>0</v>
       </c>
-      <c r="R88" s="3"/>
-    </row>
-    <row r="89" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R88" s="3">
+        <v>0</v>
+      </c>
+      <c r="S88" s="3"/>
+    </row>
+    <row r="89" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>77</v>
       </c>
-      <c r="D89" s="3">
+      <c r="D89" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="E89" s="3">
         <v>297600</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>406000</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>431500</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>480000</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>526200</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>415100</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>455400</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>416500</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>222500</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>216200</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>281400</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>295400</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>286600</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>231700</v>
       </c>
-      <c r="R89" s="3"/>
-    </row>
-    <row r="90" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S89" s="3"/>
+    </row>
+    <row r="90" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>78</v>
       </c>
@@ -4242,56 +4461,60 @@
       <c r="P90" s="3"/>
       <c r="Q90" s="3"/>
       <c r="R90" s="3"/>
-    </row>
-    <row r="91" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S90" s="3"/>
+    </row>
+    <row r="91" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>79</v>
       </c>
-      <c r="D91" s="3">
+      <c r="D91" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="E91" s="3">
         <v>-7800</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-15500</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-10600</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-18700</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-15100</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-37100</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-32400</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-40800</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-19800</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-25000</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-18000</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-17600</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-10800</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-61900</v>
       </c>
-      <c r="R91" s="3"/>
-    </row>
-    <row r="92" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S91" s="3"/>
+    </row>
+    <row r="92" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>80</v>
       </c>
@@ -4337,9 +4560,12 @@
       <c r="Q92" s="3">
         <v>0</v>
       </c>
-      <c r="R92" s="3"/>
-    </row>
-    <row r="93" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R92" s="3">
+        <v>0</v>
+      </c>
+      <c r="S92" s="3"/>
+    </row>
+    <row r="93" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>81</v>
       </c>
@@ -4385,57 +4611,63 @@
       <c r="Q93" s="3">
         <v>0</v>
       </c>
-      <c r="R93" s="3"/>
-    </row>
-    <row r="94" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R93" s="3">
+        <v>0</v>
+      </c>
+      <c r="S93" s="3"/>
+    </row>
+    <row r="94" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>82</v>
       </c>
-      <c r="D94" s="3">
+      <c r="D94" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="E94" s="3">
         <v>32100</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>219900</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-513500</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>22400</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-56000</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-13500</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>7500</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-300200</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>85800</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-34900</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-290000</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-155200</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-414900</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-23200</v>
       </c>
-      <c r="R94" s="3"/>
-    </row>
-    <row r="95" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S94" s="3"/>
+    </row>
+    <row r="95" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>83</v>
       </c>
@@ -4454,56 +4686,60 @@
       <c r="P95" s="3"/>
       <c r="Q95" s="3"/>
       <c r="R95" s="3"/>
-    </row>
-    <row r="96" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S95" s="3"/>
+    </row>
+    <row r="96" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>84</v>
       </c>
       <c r="D96" s="3">
+        <v>0</v>
+      </c>
+      <c r="E96" s="3">
         <v>612400</v>
       </c>
-      <c r="E96" s="3">
+      <c r="F96" s="3">
         <v>143700</v>
       </c>
-      <c r="F96" s="3">
+      <c r="G96" s="3">
         <v>201300</v>
       </c>
-      <c r="G96" s="3">
+      <c r="H96" s="3">
         <v>180400</v>
       </c>
-      <c r="H96" s="3">
+      <c r="I96" s="3">
         <v>210100</v>
       </c>
-      <c r="I96" s="3">
+      <c r="J96" s="3">
         <v>202400</v>
       </c>
-      <c r="J96" s="3">
+      <c r="K96" s="3">
         <v>180400</v>
       </c>
-      <c r="K96" s="3">
-        <v>0</v>
-      </c>
       <c r="L96" s="3">
+        <v>0</v>
+      </c>
+      <c r="M96" s="3">
         <v>-96200</v>
       </c>
-      <c r="M96" s="3">
+      <c r="N96" s="3">
         <v>-105200</v>
       </c>
-      <c r="N96" s="3">
+      <c r="O96" s="3">
         <v>-138900</v>
       </c>
-      <c r="O96" s="3">
+      <c r="P96" s="3">
         <v>-80800</v>
       </c>
-      <c r="P96" s="3">
+      <c r="Q96" s="3">
         <v>-98200</v>
       </c>
-      <c r="Q96" s="3">
+      <c r="R96" s="3">
         <v>-79200</v>
       </c>
-      <c r="R96" s="3"/>
-    </row>
-    <row r="97" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S96" s="3"/>
+    </row>
+    <row r="97" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>85</v>
       </c>
@@ -4549,9 +4785,12 @@
       <c r="Q97" s="3">
         <v>0</v>
       </c>
-      <c r="R97" s="3"/>
-    </row>
-    <row r="98" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R97" s="3">
+        <v>0</v>
+      </c>
+      <c r="S97" s="3"/>
+    </row>
+    <row r="98" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>86</v>
       </c>
@@ -4597,9 +4836,12 @@
       <c r="Q98" s="3">
         <v>0</v>
       </c>
-      <c r="R98" s="3"/>
-    </row>
-    <row r="99" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R98" s="3">
+        <v>0</v>
+      </c>
+      <c r="S98" s="3"/>
+    </row>
+    <row r="99" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>87</v>
       </c>
@@ -4645,151 +4887,163 @@
       <c r="Q99" s="3">
         <v>0</v>
       </c>
-      <c r="R99" s="3"/>
-    </row>
-    <row r="100" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R99" s="3">
+        <v>0</v>
+      </c>
+      <c r="S99" s="3"/>
+    </row>
+    <row r="100" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>88</v>
       </c>
-      <c r="D100" s="3">
+      <c r="D100" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="E100" s="3">
         <v>-832600</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-308100</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-230800</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-142800</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-204900</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-238900</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-120500</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-150100</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-99900</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-66100</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-148800</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-2000</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-101200</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-120300</v>
       </c>
-      <c r="R100" s="3"/>
-    </row>
-    <row r="101" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S100" s="3"/>
+    </row>
+    <row r="101" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>89</v>
       </c>
-      <c r="D101" s="3">
+      <c r="D101" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="E101" s="3">
         <v>33100</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>62600</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>181300</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>87900</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>-13100</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>-10900</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>-39800</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>-1100</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>2100</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>-30000</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>22700</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>87700</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>41100</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>-25800</v>
       </c>
-      <c r="R101" s="3"/>
-    </row>
-    <row r="102" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S101" s="3"/>
+    </row>
+    <row r="102" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D102" s="3">
+        <v>0</v>
+      </c>
+      <c r="E102" s="3">
         <v>-469900</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>380400</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-131500</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>447400</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>252300</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>151800</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>302500</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-34900</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>210500</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>85200</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-134700</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>225900</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-188400</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>62400</v>
       </c>
-      <c r="R102" s="3"/>
+      <c r="S102" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
